--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -10,8 +10,9 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Monthly Attendance - February" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ANDRE_MARQUEZA" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="LAURA_MARCIA" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="RICARDO_DINIS_LANGA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="INÁCIO_RODRIGUES" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LAURA_MARCIA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="RICARDO_DINIS_LANGA" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -606,14 +607,14 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Did Not Use App</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
@@ -726,14 +727,14 @@
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>INÁCIO RODRIGUES</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>No attendance on date: 2</t>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Perfect attendance ✓</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1390,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 00 Mins</t>
+          <t>Time Spent: 00 Hrs 23 Mins</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr"/>
@@ -1429,6 +1430,71 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="23.6" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM JAIME ELIAS MABOXE (visited)</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 00 Mins</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr"/>
+      <c r="D1" s="6" t="inlineStr"/>
+      <c r="E1" s="6" t="inlineStr"/>
+      <c r="F1" s="6" t="inlineStr"/>
+      <c r="G1" s="6" t="inlineStr"/>
+    </row>
+    <row r="2" ht="23.6" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="11" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1677,7 +1743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="23.6" customHeight="1">
+    <row r="3" ht="39.2" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>FRANCISCO DO ROSARIO TOMAS</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -603,25 +603,25 @@
     <row r="4" ht="23.6" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>INÁCIO RODRIGUES</t>
+          <t>HENRIQUE BERTUR MARCO</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Used App</t>
+          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
     <row r="5" ht="23.6" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -639,14 +639,14 @@
     <row r="6" ht="23.6" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>LAURA MARCIA</t>
+          <t>INÁCIO RODRIGUES</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -657,18 +657,108 @@
     <row r="7" ht="23.6" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>ITO BEDITO</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Did Not Use App</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="23.6" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>KUMAR CHAMPAKLAL</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Did Not Use App</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="23.6" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>LAURA MARCIA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Used App</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="23.6" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" s="3" t="n">
+      <c r="B10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Used App</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="23.6" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Did Not Use App</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="39.2" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA JAUHAR SAIDE</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
@@ -683,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -717,7 +807,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>FRANCISCO DO ROSARIO TOMAS</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -727,21 +817,21 @@
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>INÁCIO RODRIGUES</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Perfect attendance ✓</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>HENRIQUE BERTUR MARCO</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>No attendance on date: 2</t>
         </is>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -753,24 +843,84 @@
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>INÁCIO RODRIGUES</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Perfect attendance ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>ITO BEDITO</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>No attendance on date: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>KUMAR CHAMPAKLAL</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>No attendance on date: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>LAURA MARCIA</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Perfect attendance ✓</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Perfect attendance ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>No attendance on date: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA JAUHAR SAIDE</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>No attendance on date: 2</t>
         </is>
       </c>
     </row>
@@ -785,7 +935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1421,9 +1571,129 @@
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
     </row>
+    <row r="29" ht="23.6" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM 1º DE MAIO (visited)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 34 Mins</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr"/>
+      <c r="D29" s="6" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="23.6" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="8" t="n"/>
+    </row>
+    <row r="32" ht="23.6" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>UNIAO COMERCIAL ZANDA (visited)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 17 Mins</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr"/>
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr"/>
+      <c r="G32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33" ht="23.6" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="11" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+    </row>
+    <row r="35" ht="23.6" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>KADI COMERCIAL (visited)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 41 Mins</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr"/>
+      <c r="D35" s="6" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr"/>
+      <c r="G35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36" ht="23.6" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="8" t="n"/>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="n"/>
+      <c r="G37" s="8" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A33:G33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1435,7 +1705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1455,7 +1725,7 @@
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 00 Mins</t>
+          <t>Time Spent: 01 Hrs 06 Mins</t>
         </is>
       </c>
       <c r="C1" s="6" t="inlineStr"/>
@@ -1486,9 +1756,49 @@
       <c r="F3" s="8" t="n"/>
       <c r="G3" s="8" t="n"/>
     </row>
+    <row r="4" ht="23.6" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM ACACIAS (visited)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 01 Hrs 05 Mins</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="23.6" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1749,7 +2059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1886,7 +2196,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 00 Mins</t>
+          <t>Time Spent: 02 Hrs 05 Mins</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr"/>
@@ -1917,13 +2227,17 @@
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
     </row>
-    <row r="13" ht="23.6" customHeight="1">
+    <row r="13" ht="39.2" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>MAKATE METALOMECANICA, LDA (called)</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr"/>
+          <t>FERRAGEM AIYAKENE, SOCIEDADE UNIPESSOAL, LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 09 Mins</t>
+        </is>
+      </c>
       <c r="C13" s="6" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr"/>
       <c r="E13" s="6" t="inlineStr"/>
@@ -1931,124 +2245,160 @@
       <c r="G13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="23.6" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="23.6" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>MAKATE METALOMECANICA, LDA (called)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr"/>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="23.6" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Product ID</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Product Description</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr"/>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>Sold Qty</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>Order Value</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="39.2" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="39.2" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>ENDURRECEDOR PARA POLIURETANO PREMIUM 5L - 015-001</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="n">
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E18" s="2" t="n">
         <v>3842.76</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>15,371.04</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16" ht="39.2" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="39.2" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>DILUENTE PARA POLIURETANO PREMIUM 5L - 015-001</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="n">
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E19" s="2" t="n">
         <v>1800.69</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>18,006.90</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="39.2" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="39.2" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>710</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>TINTA POLIURETANO 2K PREMIUM 20L - DARK SERIES</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="n">
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E20" s="2" t="n">
         <v>17863.51</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>35,727.02</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
+      <c r="G20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -439,7 +439,7 @@
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🎉 PUBLIC HOLIDAY - Tuesday, February 03, 2026</t>
+          <t xml:space="preserve"> PUBLIC HOLIDAY - Tuesday, February 03, 2026</t>
         </is>
       </c>
     </row>
@@ -449,7 +449,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>No business activities recorded on this date</t>
+          <t>No CSFA activities recorded on this date</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -7,7 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Holiday Notice" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Monthly Attendance - February" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ANDRE_MARQUEZA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="INÁCIO_RODRIGUES" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="RICARDO_DINIS_LANGA" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,24 +32,64 @@
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="00FF0000"/>
-      <sz val="18"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Times New Roman"/>
-      <i val="1"/>
-      <sz val="14"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F81BD"/>
+        <bgColor rgb="004F81BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004BACC6"/>
+        <bgColor rgb="004BACC6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092D050"/>
+        <bgColor rgb="0092D050"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -53,18 +97,73 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,33 +529,2015 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PUBLIC HOLIDAY - Tuesday, February 03, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
+          <t>SALESPERSON</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>CUSTOMERS VISITED</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CUSTOMERS CALLED</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>APP USAGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="23.6" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ANDRE MARQUEZA</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Used App</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="23.6" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>No CSFA activities recorded on this date</t>
+          <t>IMRAN AHMED</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Did Not Use App</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="23.6" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>INÁCIO RODRIGUES</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Used App</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="23.6" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>KUMAR CHAMPAKLAL</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Did Not Use App</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="23.6" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>LAURA MARCIA</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Did Not Use App</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="23.6" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Used App</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Salesperson</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ANDRE MARQUEZA</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Perfect attendance ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>IMRAN AHMED</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>No attendance on dates: 2, 4 (2 days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>INÁCIO RODRIGUES</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Perfect attendance ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>KUMAR CHAMPAKLAL</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>No attendance on dates: 2, 4 (2 days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>LAURA MARCIA</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>No attendance on dates: 2, 4 (2 days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Perfect attendance ✓</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="23.6" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM 1º DE MAIO (visited)</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 22 Mins</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr"/>
+      <c r="D1" s="6" t="inlineStr"/>
+      <c r="E1" s="6" t="inlineStr"/>
+      <c r="F1" s="6" t="inlineStr"/>
+      <c r="G1" s="6" t="inlineStr"/>
+    </row>
+    <row r="2" ht="23.6" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr"/>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="23.6" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 5L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1347</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>8,082.00</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4" ht="23.6" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15,840.00</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="23.6" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11,040.00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="23.6" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 20L - 015-001</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1088</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>32,640.00</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="23.6" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>MASSANGO PAINTS, EI (visited)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 03 Mins</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="23.6" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="39.2" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CROWN ECO VESTA ECONOMY 20L - 015-001</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1333</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15,996.00</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="23.6" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 5L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1333</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10,664.00</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="23.6" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15,840.00</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+    </row>
+    <row r="14" ht="23.6" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>A.M POWER TRADING LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 19 Mins</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15" ht="23.6" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="11" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="39.2" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>ELECTRO FERRAGEM MASTER SOLUTIONS (visited)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 30 Mins</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18" ht="23.6" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+    </row>
+    <row r="20" ht="23.6" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>SAAK INTERNACIONAL, LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 21 Mins</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="23.6" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="11" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="23.6" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>SOLECTRIC, LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 20 Mins</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr"/>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="23.6" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25" ht="23.6" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>BERGER EXPERT ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>377</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7,917.00</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="39.2" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>358.9</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>12,920.40</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="39.2" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>NATION ESMALTE ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>920.63</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>9,206.30</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="39.2" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 5L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>1175.49</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>11,754.90</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="39.2" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>1175.49</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>11,754.90</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="39.2" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>1329.3</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>13,293.00</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="23.6" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>18,400.00</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="39.2" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>206-0001-020 - Nation PVA Branco 20L</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>521,040.00</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="8" t="n"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="8" t="n"/>
+    </row>
+    <row r="34" ht="23.6" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>CONSTRUA BUILD IT (visited)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 01 Hrs 25 Mins</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="23.6" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
+    </row>
+    <row r="37" ht="23.6" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM NHAMPIMBE, EI (called)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr"/>
+      <c r="C37" s="6" t="inlineStr"/>
+      <c r="D37" s="6" t="inlineStr"/>
+      <c r="E37" s="6" t="inlineStr"/>
+      <c r="F37" s="6" t="inlineStr"/>
+      <c r="G37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="23.6" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr"/>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39" ht="39.2" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>1443</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>11,544.00</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A18:G18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="23.6" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>AUTO FERRAGEM NELCIA, EI (visited)</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 07 Mins</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr"/>
+      <c r="D1" s="6" t="inlineStr"/>
+      <c r="E1" s="6" t="inlineStr"/>
+      <c r="F1" s="6" t="inlineStr"/>
+      <c r="G1" s="6" t="inlineStr"/>
+    </row>
+    <row r="2" ht="23.6" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="11" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="39.2" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>J. ELECTRO FERRAGEM SOC. UNIP. LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 11 Mins</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="23.6" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="39.2" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>BLESSED MIKO IMPORT AND EXPORT, EI (visited)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 06 Mins</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="23.6" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="23.6" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>JKAS COMERCIAL, LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 11 Mins</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="23.6" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="11" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="23.6" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM ABAB LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 07 Mins</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="23.6" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="23.6" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>DHP LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 05 Mins</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="23.6" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="11" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="23.6" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>MODALAND INTERPRICES (visited)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 08 Mins</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="23.6" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="23.6" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>ARIMEK COMERCIAL EI (visited)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 06 Mins</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="23.6" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="11" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+    </row>
+    <row r="25" ht="23.6" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM MUIZ, EI (visited)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 39 Mins</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr"/>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="23.6" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="11" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+    </row>
+    <row r="28" ht="23.6" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>ELECTRO FERRAGEM REAL (called)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr"/>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="23.6" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30" ht="39.2" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>NATION ESMALTE ECONOMY 20L - 015-001</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>1056</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>106,656.00</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="8" t="n"/>
+    </row>
+    <row r="32" ht="39.2" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>MACOMAT MAT. CONSTRUCAO DE MOC. (called)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="inlineStr"/>
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr"/>
+      <c r="G32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33" ht="23.6" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34" ht="23.6" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SUBCAPA PREMIUM 1L  - 015-001</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>307.35</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>5,532.30</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="39.2" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>1289</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>5,156.00</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="39.2" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>DILUENTE LAQUER THINNER PREMIUM 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>866.9400000000001</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>3,467.76</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="39.2" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>10276 - DILUENTE SINTETICO ECONOMY 5L</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>642.27</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2,569.08</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="23.6" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>DILUENTE LAQUER THINNER 750ml</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>6,210.00</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="39.2" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>10275 - DILUENTE SINTETICO ECONOMY 1L</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>5,964.00</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A23:G23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="23.6" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>TINTAS BERGER MAPUTO OFFICE (visited)</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 02 Hrs 19 Mins</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr"/>
+      <c r="D1" s="6" t="inlineStr"/>
+      <c r="E1" s="6" t="inlineStr"/>
+      <c r="F1" s="6" t="inlineStr"/>
+      <c r="G1" s="6" t="inlineStr"/>
+    </row>
+    <row r="2" ht="23.6" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="11" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="39.2" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>ELECTRO FERRAGEM UNIVERSO,  E.I (visited)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 15 Mins</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="23.6" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="23.6" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>ELECTRO FERRAGEM MATOLA (visited)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 00 Mins</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="23.6" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="39.2" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>ELECTRO FERRAGEM KISHOSSA,LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 00 Mins</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="23.6" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="11" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="23.6" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>MINI FERRAGEM CHIPEMBELE (visited)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 00 Mins</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="23.6" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="23.6" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>JAIME NAFTAL MAIBASSE (visited)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 00 Mins</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="23.6" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="11" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="23.6" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>MOBILITY INVESTIMENTO,  EI (visited)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 38 Mins</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="23.6" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -155,15 +155,15 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>No attendance on dates: 2, 4 (2 days)</t>
+          <t>No attendance on dates: 2, 4, 6 (3 days)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>No attendance on dates: 2, 4 (2 days)</t>
+          <t>No attendance on dates: 2, 4, 6 (3 days)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>No attendance on dates: 2, 4 (2 days)</t>
+          <t>No attendance on dates: 2, 4, 6 (3 days)</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,152 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="39.2" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>OUSAF INTERNATIONAL TRADING LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 27 Mins</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr"/>
+      <c r="D1" s="6" t="inlineStr"/>
+      <c r="E1" s="6" t="inlineStr"/>
+      <c r="F1" s="6" t="inlineStr"/>
+      <c r="G1" s="6" t="inlineStr"/>
+    </row>
+    <row r="2" ht="23.6" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="9" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="23.6" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>FIVE STAR COMERCIAL, EI (visited)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 14 Mins</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="23.6" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="9" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="23.6" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM SABHA, LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 29 Mins</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="23.6" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="9" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -796,12 +941,12 @@
     <row r="1" ht="23.6" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>FERRAGEM 1º DE MAIO (visited)</t>
+          <t>Z.K FERRAGEM, E.I (visited)</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 22 Mins</t>
+          <t>Time Spent: 00 Hrs 10 Mins</t>
         </is>
       </c>
       <c r="C1" s="6" t="inlineStr"/>
@@ -813,150 +958,114 @@
     <row r="2" ht="23.6" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="9" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="23.6" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>GHORI COMERCIAL, EI (visited)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 04 Mins</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="23.6" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
           <t>Product ID</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Product Description</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr"/>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr"/>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Sold Qty</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Order Value</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr"/>
-    </row>
-    <row r="3" ht="23.6" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>CHARME ECONOMY 5L - DARK SERIES</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1347</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>8,082.00</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="23.6" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>CHARME ECONOMY 5L - 015-001</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15,840.00</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="23.6" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>NATION PVA ECONOMY 5L - 015-001</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>368</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11,040.00</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="11" t="inlineStr"/>
     </row>
     <row r="6" ht="23.6" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>NATION PVA ECONOMY 20L - 015-001</t>
+          <t>10274 - wallplast  25kgs</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1088</v>
+        <v>776</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32,640.00</t>
+          <t>39,576.00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="8" t="n"/>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="n"/>
-    </row>
-    <row r="8" ht="23.6" customHeight="1">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="39.2" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>MASSANGO PAINTS, EI (visited)</t>
+          <t>FERMAR - FERRAGENS MARRACUENE (visited)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 03 Mins</t>
+          <t>Time Spent: 00 Hrs 05 Mins</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr"/>
@@ -968,127 +1077,71 @@
     <row r="9" ht="23.6" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Sold Qty</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Order Value</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="39.2" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>CROWN ECO VESTA ECONOMY 20L - 015-001</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>1333</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15,996.00</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="9" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
     </row>
     <row r="11" ht="23.6" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>CHARME ECONOMY 5L - DARK SERIES</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>1333</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10,664.00</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>DHP LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 14 Mins</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="23.6" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>CHARME ECONOMY 5L - 015-001</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15,840.00</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="9" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
     </row>
     <row r="14" ht="23.6" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>A.M POWER TRADING LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 19 Mins</t>
-        </is>
-      </c>
+          <t>JKAS COMERCIAL, LDA (called)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr"/>
       <c r="E14" s="6" t="inlineStr"/>
@@ -1096,197 +1149,281 @@
       <c r="G14" s="6" t="inlineStr"/>
     </row>
     <row r="15" ht="23.6" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="11" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16" ht="39.2" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 5L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1289</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6,445.00</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="39.2" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>ELECTRO FERRAGEM MASTER SOLUTIONS (visited)</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 30 Mins</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18" ht="23.6" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="11" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-    </row>
-    <row r="20" ht="23.6" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>SAAK INTERNACIONAL, LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 21 Mins</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-    </row>
-    <row r="21" ht="23.6" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="11" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-    </row>
-    <row r="23" ht="23.6" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>SOLECTRIC, LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 20 Mins</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr"/>
-      <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
-      <c r="G23" s="6" t="inlineStr"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>25,440.00</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="39.2" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>25,440.00</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="39.2" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - LIGHT SERIES</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>397.56</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>14,312.16</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="39.2" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>397.56</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14,312.16</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="39.2" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM ACCELERADO/QD PREMIUM 5L - LIGHT SERIES</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1472.46</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>7,362.30</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="39.2" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 5L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1472.46</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7,362.30</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
     </row>
     <row r="24" ht="23.6" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM KULSOOM LDA (called)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr"/>
+      <c r="C24" s="6" t="inlineStr"/>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="23.6" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Product ID</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Product Description</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr"/>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr"/>
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Sold Qty</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Order Value</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25" ht="23.6" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>BERGER EXPERT ECONOMY 5L - 015-001</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>377</v>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7,917.00</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="11" t="inlineStr"/>
     </row>
     <row r="26" ht="39.2" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 5L - 015-001</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>358.9</v>
+        <v>1289</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12,920.40</t>
+          <t>6,445.00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1294,124 +1431,100 @@
     <row r="27" ht="39.2" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>772</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>NATION ESMALTE ECONOMY 5L - 015-001</t>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 5L - DARK SERIES</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>920.63</v>
+        <v>1276</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9,206.30</t>
+          <t>25,520.00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
     </row>
-    <row r="28" ht="39.2" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 5L - DARK SERIES</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>1175.49</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>11,754.90</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="39.2" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 5L - 015-001</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>1175.49</v>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>11,754.90</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30" ht="39.2" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>ZARCAO SECAGEM NORMAL TRADE 5L - 015-001</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>1329.3</v>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>13,293.00</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="23.6" customHeight="1">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="23.6" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM AUTO GEMO (called)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr"/>
+      <c r="C29" s="6" t="inlineStr"/>
+      <c r="D29" s="6" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="23.6" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr"/>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="39.2" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>650</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>NATION PVA ECONOMY 5L - 015-001</t>
+          <t>NATION ESMALTE ECONOMY 5L - DARK SERIES</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>368</v>
+        <v>1187</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18,400.00</t>
+          <t>18,992.00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1419,170 +1532,355 @@
     <row r="32" ht="39.2" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>206-0001-020 - Nation PVA Branco 20L</t>
+          <t>NATION ESMALTE ECONOMY 5L - 015-001</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>501</v>
+        <v>20</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1040</v>
+        <v>999</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>521,040.00</t>
+          <t>19,980.00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="8" t="n"/>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
+    <row r="33" ht="23.6" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Nation Esmalte 1L</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>321</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>5,778.00</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
     </row>
     <row r="34" ht="23.6" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>CONSTRUA BUILD IT (visited)</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 01 Hrs 25 Mins</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr"/>
-      <c r="D34" s="6" t="inlineStr"/>
-      <c r="E34" s="6" t="inlineStr"/>
-      <c r="F34" s="6" t="inlineStr"/>
-      <c r="G34" s="6" t="inlineStr"/>
-    </row>
-    <row r="35" ht="23.6" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Nation Esmalte 1L</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>321</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>11,556.00</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="10" t="n"/>
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="10" t="n"/>
       <c r="E35" s="10" t="n"/>
       <c r="F35" s="10" t="n"/>
-      <c r="G35" s="11" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="8" t="n"/>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
+      <c r="G35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="23.6" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>GOD WIN FERRAGEM (called)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr"/>
+      <c r="C36" s="6" t="inlineStr"/>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr"/>
+      <c r="F36" s="6" t="inlineStr"/>
+      <c r="G36" s="6" t="inlineStr"/>
     </row>
     <row r="37" ht="23.6" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>FERRAGEM NHAMPIMBE, EI (called)</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr"/>
-      <c r="C37" s="6" t="inlineStr"/>
-      <c r="D37" s="6" t="inlineStr"/>
-      <c r="E37" s="6" t="inlineStr"/>
-      <c r="F37" s="6" t="inlineStr"/>
-      <c r="G37" s="6" t="inlineStr"/>
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr"/>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr"/>
     </row>
     <row r="38" ht="23.6" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr"/>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Sold Qty</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>Order Value</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39" ht="39.2" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>1333</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>10,664.00</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="23.6" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ZARCAO SECAGEM NORMAL TRADE 5L - 015-001</t>
+          <t>CHARME ECONOMY 1L - 015-001</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1443</v>
+        <v>356</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>11,544.00</t>
+          <t>14,240.00</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="8" t="n"/>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="8" t="n"/>
+    <row r="40" ht="39.2" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>18,564.00</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="39.2" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>19,300.00</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="39.2" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>8,050.00</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="39.2" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>8,050.00</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="39.2" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 0.5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2,670.00</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="39.2" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 0.5L - MEDIUM SERIES</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>3,560.00</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="10" t="n"/>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A18:G18"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1597,12 +1895,12 @@
     <row r="1" ht="23.6" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>AUTO FERRAGEM NELCIA, EI (visited)</t>
+          <t>TINTAS BERGER MAPUTO OFFICE (visited)</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 07 Mins</t>
+          <t>Time Spent: 00 Hrs 35 Mins</t>
         </is>
       </c>
       <c r="C1" s="6" t="inlineStr"/>
@@ -1612,36 +1910,36 @@
       <c r="G1" s="6" t="inlineStr"/>
     </row>
     <row r="2" ht="23.6" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="11" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="9" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="n"/>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
-    </row>
-    <row r="4" ht="39.2" customHeight="1">
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="23.6" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>J. ELECTRO FERRAGEM SOC. UNIP. LDA (visited)</t>
+          <t>FERRAGEM SERGIO E.I (visited)</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 11 Mins</t>
+          <t>Time Spent: 00 Hrs 21 Mins</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr"/>
@@ -1651,36 +1949,36 @@
       <c r="G4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="23.6" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n"/>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="11" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="9" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="39.2" customHeight="1">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="23.6" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>BLESSED MIKO IMPORT AND EXPORT, EI (visited)</t>
+          <t>VIDRIOFER, LDA (visited)</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 06 Mins</t>
+          <t>Time Spent: 00 Hrs 13 Mins</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr"/>
@@ -1690,36 +1988,36 @@
       <c r="G7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="23.6" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="9" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-    </row>
-    <row r="10" ht="23.6" customHeight="1">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="39.2" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>JKAS COMERCIAL, LDA (visited)</t>
+          <t>FERRAGEM ALMADINA SOC.UNIP,LDA (visited)</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 11 Mins</t>
+          <t>Time Spent: 00 Hrs 00 Mins</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr"/>
@@ -1729,36 +2027,36 @@
       <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="23.6" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="10" t="n"/>
-      <c r="G11" s="11" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="9" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
     </row>
     <row r="13" ht="23.6" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>FERRAGEM ABAB LDA (visited)</t>
+          <t>MOZAMBIQUE OASIS, LDA (visited)</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 07 Mins</t>
+          <t>Time Spent: 00 Hrs 15 Mins</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr"/>
@@ -1768,36 +2066,36 @@
       <c r="G13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="23.6" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="9" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
     </row>
     <row r="16" ht="23.6" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>DHP LDA (visited)</t>
+          <t>STEEL TRADE, LDA (visited)</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 05 Mins</t>
+          <t>Time Spent: 00 Hrs 29 Mins</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr"/>
@@ -1807,36 +2105,36 @@
       <c r="G16" s="6" t="inlineStr"/>
     </row>
     <row r="17" ht="23.6" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="11" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
     </row>
     <row r="19" ht="23.6" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>MODALAND INTERPRICES (visited)</t>
+          <t>PAK-MOZ FERRAGEM (visited)</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 08 Mins</t>
+          <t>Time Spent: 00 Hrs 20 Mins</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr"/>
@@ -1846,36 +2144,36 @@
       <c r="G19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="23.6" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
     </row>
     <row r="22" ht="23.6" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>ARIMEK COMERCIAL EI (visited)</t>
+          <t>A.F. FERRAGEM (visited)</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 06 Mins</t>
+          <t>Time Spent: 00 Hrs 00 Mins</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr"/>
@@ -1885,36 +2183,36 @@
       <c r="G22" s="6" t="inlineStr"/>
     </row>
     <row r="23" ht="23.6" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="11" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
     </row>
     <row r="25" ht="23.6" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>FERRAGEM MUIZ, EI (visited)</t>
+          <t>FERRAGEM INDICO (visited)</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 39 Mins</t>
+          <t>Time Spent: 00 Hrs 01 Mins</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr"/>
@@ -1924,31 +2222,31 @@
       <c r="G25" s="6" t="inlineStr"/>
     </row>
     <row r="26" ht="23.6" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="11" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="8" t="n"/>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
     </row>
     <row r="28" ht="23.6" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>ELECTRO FERRAGEM REAL (called)</t>
+          <t>GAYE GROUP FERRAGEM,  LDA (called)</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr"/>
@@ -1959,131 +2257,155 @@
       <c r="G28" s="6" t="inlineStr"/>
     </row>
     <row r="29" ht="23.6" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Product ID</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Product Description</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr"/>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr"/>
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Sold Qty</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Order Value</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30" ht="39.2" customHeight="1">
+      <c r="G29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="23.6" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>NATION ESMALTE ECONOMY 20L - 015-001</t>
+          <t>CHARME ECONOMY 5L - 015-001</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="n">
-        <v>101</v>
+        <v>6</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1056</v>
+        <v>1347</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>106,656.00</t>
+          <t>8,082.00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="8" t="n"/>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
+    <row r="31" ht="23.6" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>6,552.00</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
     </row>
     <row r="32" ht="39.2" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>MACOMAT MAT. CONSTRUCAO DE MOC. (called)</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr"/>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-    </row>
-    <row r="33" ht="23.6" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Sold Qty</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>Order Value</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34" ht="23.6" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>10276 - DILUENTE SINTETICO ECONOMY 5L</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>6,290.00</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="39.2" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>DILUENTE SINTETICO ECONOMY 0.75L - 015-001</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>12,400.00</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="39.2" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SUBCAPA PREMIUM 1L  - 015-001</t>
+          <t>ZARCAO SECAGEM NORMAL TRADE 5L - 015-001</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>307.35</v>
+        <v>1458</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5,532.30</t>
+          <t>8,748.00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -2091,136 +2413,289 @@
     <row r="35" ht="39.2" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 5L - 015-001</t>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1289</v>
+        <v>386</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5,156.00</t>
+          <t>27,792.00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
     </row>
-    <row r="36" ht="39.2" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>DILUENTE LAQUER THINNER PREMIUM 5L - 015-001</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>866.9400000000001</v>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>3,467.76</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="39.2" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>1025</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>10276 - DILUENTE SINTETICO ECONOMY 5L</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>642.27</v>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>2,569.08</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="23.6" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>MAKATE METALOMECANICA, LDA (called)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr"/>
+      <c r="C37" s="6" t="inlineStr"/>
+      <c r="D37" s="6" t="inlineStr"/>
+      <c r="E37" s="6" t="inlineStr"/>
+      <c r="F37" s="6" t="inlineStr"/>
+      <c r="G37" s="6" t="inlineStr"/>
     </row>
     <row r="38" ht="23.6" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>1038</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>DILUENTE LAQUER THINNER 750ml</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>6,210.00</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="39.2" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr"/>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="23.6" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>443</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>10275 - DILUENTE SINTETICO ECONOMY 1L</t>
+          <t>SMP PREMIUM 5L  - LIGHT SERIES</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>142</v>
+        <v>2176.53</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5,964.00</t>
+          <t>8,706.12</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="8" t="n"/>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="8" t="n"/>
+    <row r="40" ht="23.6" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SMP PREMIUM 5L  - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>2176.53</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>17,412.24</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+    </row>
+    <row r="42" ht="39.2" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM CALISTO MAHALAMBA E.I (called)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr"/>
+      <c r="C42" s="6" t="inlineStr"/>
+      <c r="D42" s="6" t="inlineStr"/>
+      <c r="E42" s="6" t="inlineStr"/>
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="23.6" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr"/>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="23.6" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>15,840.00</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="10" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="10" t="n"/>
+    </row>
+    <row r="46" ht="23.6" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>SIMBA HOME CARE, SU,LDA (called)</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr"/>
+      <c r="C46" s="6" t="inlineStr"/>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="23.6" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr"/>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="23.6" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>10274 - wallplast  25kgs</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>755</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>83,050.00</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="10" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2236,309 +2711,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="23.6" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>TINTAS BERGER MAPUTO OFFICE (visited)</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 02 Hrs 19 Mins</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr"/>
-      <c r="D1" s="6" t="inlineStr"/>
-      <c r="E1" s="6" t="inlineStr"/>
-      <c r="F1" s="6" t="inlineStr"/>
-      <c r="G1" s="6" t="inlineStr"/>
-    </row>
-    <row r="2" ht="23.6" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="11" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="n"/>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
-    </row>
-    <row r="4" ht="39.2" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>ELECTRO FERRAGEM UNIVERSO,  E.I (visited)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 15 Mins</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr"/>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="23.6" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="n"/>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="11" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="23.6" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>ELECTRO FERRAGEM MATOLA (visited)</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 00 Mins</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="23.6" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="11" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-    </row>
-    <row r="10" ht="39.2" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>ELECTRO FERRAGEM KISHOSSA,LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 00 Mins</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr"/>
-      <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr"/>
-      <c r="G10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11" ht="23.6" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="10" t="n"/>
-      <c r="G11" s="11" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-    </row>
-    <row r="13" ht="23.6" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>MINI FERRAGEM CHIPEMBELE (visited)</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 00 Mins</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14" ht="23.6" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="11" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-    </row>
-    <row r="16" ht="23.6" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>JAIME NAFTAL MAIBASSE (visited)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 00 Mins</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="6" t="inlineStr"/>
-      <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17" ht="23.6" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="11" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-    </row>
-    <row r="19" ht="23.6" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>MOBILITY INVESTIMENTO,  EI (visited)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 38 Mins</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20" ht="23.6" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="11" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A5:G5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -128,27 +125,27 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -514,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -552,7 +549,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -588,10 +585,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -624,14 +621,32 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Used App</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="23.6" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Used App</t>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
@@ -646,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -709,7 +724,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 2, 4, 6, 9, 10 (5 days)</t>
+          <t>No attendance on dates: 2, 4, 6, 9, 10, 12 (6 days)</t>
         </is>
       </c>
     </row>
@@ -722,6 +737,18 @@
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Perfect attendance</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>No attendance on dates: 10, 12 (2 days)</t>
         </is>
       </c>
     </row>
@@ -736,7 +763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -751,12 +778,12 @@
     <row r="1" ht="23.6" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>FERRAGEM SABHA, LDA (visited)</t>
+          <t>FERRAGEM MUNHISSE MNISI, E.I (visited)</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 44 Mins</t>
+          <t>Time Spent: 00 Hrs 12 Mins</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr"/>
@@ -768,239 +795,219 @@
     <row r="2" ht="23.6" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="7" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="23.6" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ZANG FERRAGEM (visited)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 38 Mins</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="23.6" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
           <t>Product ID</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Product Description</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr"/>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Sold Qty</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Order Value</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3" ht="39.2" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 5L - DARK SERIES</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1263</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>31,575.00</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="39.2" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - DARK SERIES</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>318</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31,800.00</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="39.2" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - 015-001</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>318</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>31,800.00</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6" ht="39.2" customHeight="1">
+      <c r="G5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6" ht="23.6" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 0.5L - DARK SERIES</t>
+          <t>SILK VELVETO PREMIUM 5L</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>174</v>
+        <v>1140.88</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,050.00</t>
+          <t>1,140.88</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
-    <row r="7" ht="39.2" customHeight="1">
+    <row r="7" ht="23.6" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 0.5L - 015-001</t>
+          <t>SILK VELVETO PREMIUM 20L</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>174</v>
+        <v>4480.01</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,050.00</t>
+          <t>4,480.01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
     </row>
-    <row r="8" ht="23.6" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>NATION PVA ECONOMY 5L - 015-001</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>352</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>70,400.00</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+    </row>
+    <row r="9" ht="23.6" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>FERRAGEM MAHNOOR (visited)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 01 Hrs 01 Mins</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="23.6" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>KUSHI MAPUTO LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 22 Mins</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11" ht="23.6" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="9" t="n"/>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr"/>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr"/>
+    </row>
+    <row r="11" ht="39.2" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>358.9</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12,920.40</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="39.2" customHeight="1">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="23.6" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>MALABAR MATERIAL DE CONSTRUCAO SOCIEDADE UNIPESSOAL, LD (visited)</t>
+          <t>FERRAGEM ZINTAVA SOC UNP LDA (visited)</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 29 Mins</t>
+          <t>Time Spent: 00 Hrs 23 Mins</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -1010,36 +1017,36 @@
       <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="23.6" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="9" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="7" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
     </row>
     <row r="16" ht="23.6" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>FERRAGEM VAVA, EI (visited)</t>
+          <t>CONSTRUA BUILD IT (visited)</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 15 Mins</t>
+          <t>Time Spent: 00 Hrs 44 Mins</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -1049,112 +1056,32 @@
       <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="23.6" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="9" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="7" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="23.6" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>FAZAL COMERCIAL, EI (visited)</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 27 Mins</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20" ht="23.6" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="23.6" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>UNIAO COMERCIAL ZANDA (visited)</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 59 Mins</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="23.6" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="9" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="3">
     <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1166,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1181,12 +1108,12 @@
     <row r="1" ht="23.6" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>FERRAGEM ACACIAS (visited)</t>
+          <t>FERRAGEM SORTHIA, LDA (visited)</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 02 Hrs 06 Mins</t>
+          <t>Time Spent: 01 Hrs 41 Mins</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr"/>
@@ -1196,36 +1123,36 @@
       <c r="G1" s="4" t="inlineStr"/>
     </row>
     <row r="2" ht="23.6" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="9" t="n"/>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="7" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="6" t="n"/>
-      <c r="B3" s="6" t="n"/>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="23.6" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="39.2" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>FERRAGEM JAIME ELIAS MABOXE (visited)</t>
+          <t>ESTÊVÃO BAPTISTA MUNGUAMBE AUTO FERRAGEM (visited)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 00 Mins</t>
+          <t>Time Spent: 02 Hrs 29 Mins</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -1235,30 +1162,451 @@
       <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="23.6" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="9" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="7" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="23.6" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>MT COMERCIAL, E.I (visited)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 06 Mins</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="23.6" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="39.2" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MBFL FERRAGENS - SOC. UNIP. LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 16 Mins</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11" ht="23.6" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="23.6" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>AUTO FERRAGEM NELCIA, EI (visited)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 05 Mins</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="23.6" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="23.6" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>GHORI COMERCIAL, EI (called)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17" ht="23.6" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr"/>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18" ht="39.2" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>10275 - DILUENTE SINTETICO ECONOMY 1L</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3,575.00</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="23.6" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 1L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7,200.00</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="23.6" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7,200.00</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="39.2" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>NATION ESMALTE ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>15,984.00</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="39.2" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 5L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1289</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6,445.00</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="39.2" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>10276 - DILUENTE SINTETICO ECONOMY 5L</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>629</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4,403.00</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="39.2" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>7,800.00</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="39.2" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 0.5L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8,800.00</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="23.6" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>9,200.00</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="23.6" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 20L - 015-001</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>1088</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>22,848.00</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1271,7 +1619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1291,7 +1639,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 09 Mins</t>
+          <t>Time Spent: 01 Hrs 01 Mins</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr"/>
@@ -1301,36 +1649,36 @@
       <c r="G1" s="4" t="inlineStr"/>
     </row>
     <row r="2" ht="23.6" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="9" t="n"/>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="7" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="6" t="n"/>
-      <c r="B3" s="6" t="n"/>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="23.6" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="39.2" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>JILANI COMERCIAL, EI (visited)</t>
+          <t>MAKARAN COMERCIAL-SOCIEDADE UNIPESSOAL, LIMITADA (visited)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 04 Mins</t>
+          <t>Time Spent: 00 Hrs 00 Mins</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -1340,36 +1688,36 @@
       <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="23.6" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="9" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="7" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="39.2" customHeight="1">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="23.6" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>FERRAGEM ALI, SOCIEDADE UNIPESSOAL, LIMITADA (visited)</t>
+          <t>VIDRIOFER, LDA (visited)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 00 Mins</t>
+          <t>Time Spent: 00 Hrs 14 Mins</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -1379,36 +1727,36 @@
       <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="23.6" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="9" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="7" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="23.6" customHeight="1">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="39.2" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>IFRESH, LDA (visited)</t>
+          <t>PRÓSPERO COMERCIAL SOC.UNIP LDA (visited)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 10 Mins</t>
+          <t>Time Spent: 00 Hrs 01 Mins</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -1418,112 +1766,664 @@
       <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="23.6" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Product ID</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Product Description</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr"/>
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Sold Qty</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>Order Value</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="23.6" customHeight="1">
+      <c r="G11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12" ht="39.2" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>254</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>NATION PVA ECONOMY 20L - 015-001</t>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - MEDIUM SERIES</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1056</v>
+        <v>397.56</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105,600.00</t>
+          <t>14,312.16</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="23.6" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>FANTASTIC INDUSTRIES, LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 00 Mins</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15" ht="23.6" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="13" ht="39.2" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14,040.00</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+    </row>
+    <row r="15" ht="39.2" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MOZ INVESTIMENT &amp;amp; SERVICES, LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 01 Hrs 03 Mins</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="23.6" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="9" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
+      <c r="G16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+    </row>
+    <row r="18" ht="23.6" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>MINI FERRAGEM CHIPEMBELE (visited)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 17 Mins</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="23.6" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+    </row>
+    <row r="21" ht="39.2" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>ELECTRO FERRAGEM KISHOSSA,LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 05 Mins</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="23.6" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="7" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+    </row>
+    <row r="24" ht="23.6" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>JAIME NAFTAL MAIBASSE (visited)</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 00 Mins</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25" ht="23.6" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+    </row>
+    <row r="27" ht="39.2" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>ELECTRO FERRAGEM UNIVERSO,  E.I (visited)</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 23 Mins</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="23.6" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="7" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="8" t="n"/>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
+    </row>
+    <row r="30" ht="23.6" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>ELECTRO FERRAGEM MATOLA (visited)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 07 Mins</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31" ht="23.6" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="7" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+    </row>
+    <row r="33" ht="23.6" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>FERRAGEM POSTOS SOC.UNIP. LDA (called)</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="23.6" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr"/>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr"/>
+    </row>
+    <row r="35" ht="23.6" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>15,840.00</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="23.6" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>10274 - wallplast  25kgs</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>808</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>8,080.00</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="39.2" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>6,500.00</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="23.6" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 1L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>6,552.00</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="23.6" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>6,552.00</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="23.6" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 5L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>15,840.00</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="39.2" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>17,136.00</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="23.6" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 20L - 015-001</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1056</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>105,600.00</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="8" t="n"/>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+    </row>
+    <row r="44" ht="23.6" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>FERRAGEM NATAL (called)</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr"/>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45" ht="23.6" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr"/>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr"/>
+    </row>
+    <row r="46" ht="23.6" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 20L - 015-001</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>1088</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>27,200.00</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="8" t="n"/>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="9">
     <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Monthly Attendance - February" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ANDRE_MARQUEZA" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="INÁCIO_RODRIGUES" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ITO_BENEDITO" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="RICARDO_DINIS_LANGA" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -137,15 +137,15 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
@@ -585,66 +585,84 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Used App</t>
+          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
     <row r="5" ht="23.6" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Did Not Use App</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23.6" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Used App</t>
+          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
     <row r="7" ht="23.6" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Used App</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="23.6" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>RICARDO MACUACUA</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Did Not Use App</t>
         </is>
@@ -661,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -712,43 +730,55 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>No attendance on date: 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ITO BENEDITO</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>Perfect attendance</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="39.2" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6" ht="39.2" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>No attendance on dates: 2, 4, 6, 9, 10, 12, 13 (7 days)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Perfect attendance</t>
+          <t>No attendance on dates: 2, 4, 6, 9, 10, 12, 13, 16 (8 days)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Perfect attendance</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>RICARDO MACUACUA</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>No attendance on dates: 10, 12, 13 (3 days)</t>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>No attendance on dates: 10, 12, 13, 16 (4 days)</t>
         </is>
       </c>
     </row>
@@ -763,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -775,15 +805,15 @@
     <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="39.2" customHeight="1">
+    <row r="1" ht="23.6" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>MALABAR MATERIAL DE CONSTRUCAO SOCIEDADE UNIPESSOAL, LD (visited)</t>
+          <t>5 ESTRELAS FERRAGEM (visited)</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 19 Mins</t>
+          <t>Time Spent: 00 Hrs 57 Mins</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr"/>
@@ -795,390 +825,860 @@
     <row r="2" ht="23.6" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr"/>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="23.6" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SUBCAPA PREMIUM 1L  - 015-001</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>306.72</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>16,562.88</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4" ht="23.6" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SUBCAPA PREMIUM 5L  - 015-001</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1499.76</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17,997.12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="39.2" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>63,600.00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="39.2" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>63,600.00</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="39.2" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>69,480.00</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="39.2" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>142,800.00</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="39.2" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>NATION ESMALTE ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>979</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>48,950.00</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="23.6" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>66,000.00</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="23.6" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 1L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>64,080.00</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="39.2" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>DILUENTE LAQUER THINNER PREMIUM 1L -015-001</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>80,400.00</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="23.6" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>DILUENTE LAQUER THINNER 750ml</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>67,500.00</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="39.2" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>10275 - DILUENTE SINTETICO ECONOMY 1L</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>56,800.00</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="39.2" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>DILUENTE SINTETICO ECONOMY 0.75L - 015-001</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>62,000.00</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="23.6" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>KHENSANY FERRAGEM, LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 17 Mins</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="23.6" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="6" t="n"/>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="6" t="n"/>
-      <c r="G2" s="7" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="n"/>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
-    </row>
-    <row r="4" ht="23.6" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>FERRAGEM KAMAL (visited)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 31 Mins</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="23.6" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="39.2" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>FUXIN MATERIAL DE CONSTRUCAO TRADING, LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 15 Mins</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="23.6" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="23.6" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>R.V ELECTRO FERRAGEM LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 29 Mins</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="23.6" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="23.6" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ZANG FERRAGEM (visited)</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 14 Mins</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="23.6" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-    </row>
-    <row r="10" ht="23.6" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>FERRAGEM NHAMPIMBE, EI (visited)</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 15 Mins</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11" ht="23.6" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="23.6" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>FERRAGEM 1º DE MAIO (visited)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 17 Mins</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27" ht="23.6" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="7" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-    </row>
-    <row r="13" ht="23.6" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>ELECTRO FERRAGEM AFRICA, LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="23.6" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>QUATRO ESTRELAS FERRAGENS (visited)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Time Spent: 00 Hrs 19 Mins</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14" ht="23.6" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="23.6" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-    </row>
-    <row r="16" ht="39.2" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>ELECTRO FERRAGEM MASTER SOLUTIONS (called)</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17" ht="23.6" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="23.6" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>FERRAGEM PONTE, LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 22 Mins</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33" ht="23.6" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="9" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="23.6" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>LIMPOPO TRADING, LDA (called)</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="23.6" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Product ID</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Product Description</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr"/>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Sold Qty</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Order Value</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr"/>
-    </row>
-    <row r="18" ht="23.6" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>RUFF N TUFF PREMIUM 30KG - 015-001</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>1735.82</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3,471.64</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="23.6" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SILKY SMOOTH PREMIUM 20L - 015-001</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>3256</v>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>65,120.00</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="8" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-    </row>
-    <row r="21" ht="23.6" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>A.M POWER TRADING LDA (called)</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr"/>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22" ht="23.6" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="23.6" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>DILUENTE LAQUER THINNER 750ml</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>15,500.00</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="23.6" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>64,080.00</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="23.6" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 1L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>32,040.00</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="23.6" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>352</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>105,600.00</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="23.6" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 20L - 015-001</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>521,040.00</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="6" t="n"/>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="n"/>
+    </row>
+    <row r="43" ht="23.6" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>FERRAGEM MAHNOOR (called)</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr"/>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44" ht="23.6" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Product ID</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Product Description</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr"/>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Sold Qty</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>Order Value</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr"/>
-    </row>
-    <row r="23" ht="23.6" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>1023</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>10274 - wallplast  25kgs</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr"/>
-      <c r="D23" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>755</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>83,050.00</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24" ht="39.2" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>206-0001-020 - Nation PVA Branco 20L</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="n">
-        <v>501</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>1040</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>521,040.00</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="8" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
+      <c r="G44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45" ht="23.6" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>11,040.00</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A5:G5"/>
+  <mergeCells count="6">
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A33:G33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1202,15 +1702,15 @@
     <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.6" customHeight="1">
+    <row r="1" ht="39.2" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>FERRAGEM KULSOOM LDA (visited)</t>
+          <t>FERRAGEM HUSSAIN E.I AV ANGOLA 2216 (visited)</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 01 Hrs 04 Mins</t>
+          <t>Time Spent: 00 Hrs 08 Mins</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr"/>
@@ -1220,36 +1720,36 @@
       <c r="G1" s="4" t="inlineStr"/>
     </row>
     <row r="2" ht="23.6" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="6" t="n"/>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="6" t="n"/>
-      <c r="G2" s="7" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="9" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="n"/>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
-    </row>
-    <row r="4" ht="39.2" customHeight="1">
+      <c r="A3" s="6" t="n"/>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="23.6" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>FERRAGEM HUSSAIN E.I AV ANGOLA 2216 (visited)</t>
+          <t>GOD WIN FERRAGEM (visited)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 05 Mins</t>
+          <t>Time Spent: 00 Hrs 17 Mins</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -1259,36 +1759,36 @@
       <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="23.6" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="7" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="9" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
     </row>
     <row r="7" ht="23.6" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>FERRAGEM MUIZ, EI (visited)</t>
+          <t>FERRAGEM EXCLUSIVO (visited)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 11 Mins</t>
+          <t>Time Spent: 00 Hrs 17 Mins</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -1298,36 +1798,36 @@
       <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="23.6" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="9" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10" ht="23.6" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>FARZANA SERVICES (visited)</t>
+          <t>FERRAGEM MUIZ, EI (visited)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 12 Mins</t>
+          <t>Time Spent: 00 Hrs 18 Mins</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -1337,36 +1837,36 @@
       <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="23.6" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="7" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="9" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
     </row>
     <row r="13" ht="23.6" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Z.K FERRAGEM, E.I (visited)</t>
+          <t>FERRAGEM AFRIPAK TRADING EI (visited)</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 19 Mins</t>
+          <t>Time Spent: 00 Hrs 00 Mins</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -1376,26 +1876,26 @@
       <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="23.6" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="7" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="9" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1415,7 +1915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1430,12 +1930,12 @@
     <row r="1" ht="23.6" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO AAA (visited)</t>
+          <t>TINTAS BERGER MAPUTO OFFICE (visited)</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 01 Hrs 00 Mins</t>
+          <t>Time Spent: 00 Hrs 00 Mins</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr"/>
@@ -1445,36 +1945,36 @@
       <c r="G1" s="4" t="inlineStr"/>
     </row>
     <row r="2" ht="23.6" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="6" t="n"/>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="6" t="n"/>
-      <c r="G2" s="7" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="9" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="n"/>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
-    </row>
-    <row r="4" ht="23.6" customHeight="1">
+      <c r="A3" s="6" t="n"/>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="39.2" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>FANTASTIC INDUSTRIES, LDA (visited)</t>
+          <t>MOZ INVESTIMENT &amp;amp; SERVICES, LDA (visited)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 00 Mins</t>
+          <t>Time Spent: 00 Hrs 14 Mins</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -1484,36 +1984,36 @@
       <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="23.6" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="7" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="9" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
     </row>
     <row r="7" ht="23.6" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TINTAS BERGER MAPUTO OFFICE (visited)</t>
+          <t>IR SERVIÇOS LIMITADA (visited)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 04 Mins</t>
+          <t>Time Spent: 00 Hrs 00 Mins</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -1523,36 +2023,36 @@
       <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="23.6" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="9" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10" ht="23.6" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SIMBA HOME CARE, SU,LDA (visited)</t>
+          <t>IFRESH, LDA (visited)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 58 Mins</t>
+          <t>Time Spent: 00 Hrs 11 Mins</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -1562,31 +2062,31 @@
       <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="23.6" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="7" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="9" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
     </row>
     <row r="13" ht="39.2" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>FERRAGEM AIYAKENE, SOCIEDADE UNIPESSOAL, LDA (visited)</t>
+          <t>FERRAGEM ALI, SOCIEDADE UNIPESSOAL, LIMITADA (visited)</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1601,31 +2101,31 @@
       <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="23.6" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>No orders</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="7" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="9" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
     </row>
     <row r="16" ht="23.6" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>HANANA STEELS, LDA (visited)</t>
+          <t>INTERMETAL, SA (visited)</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1640,324 +2140,280 @@
       <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="23.6" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="23.6" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>VIDRIOFER, LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 24 Mins</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="23.6" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="23.6" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>AUTRASE, LDA (called)</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr"/>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="23.6" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Product ID</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Product Description</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr"/>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Sold Qty</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Order Value</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr"/>
-    </row>
-    <row r="18" ht="39.2" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>MASSA ROBBIFILLA ECONOMY FILLER/ PUTTY 1KG - 015-001</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>128.62</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,431.00</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="39.2" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - DARK SERIES</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>325</v>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6,500.00</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20" ht="39.2" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - 015-001</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>325</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6,500.00</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="39.2" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>DILUENTE SINTETICO ECONOMY 0.75L - 015-001</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>6,250.00</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22" ht="39.2" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>390</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>14,040.00</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="39.2" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>NATION PVA ECONOMY 5L - MEDIUM SERIES</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr"/>
-      <c r="D23" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>368</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>9,200.00</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24" ht="23.6" customHeight="1">
+      <c r="G23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="39.2" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>NATION PVA ECONOMY 20L - 015-001</t>
+          <t>ENDURRECEDOR PARA POLIURETANO PREMIUM 1L - 015-001</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1056</v>
+        <v>854.41</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>105,600.00</t>
+          <t>1,708.82</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="8" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
+    <row r="25" ht="39.2" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>DILUENTE PARA POLIURETANO PREMIUM 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>486.09</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>972.18</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
     </row>
     <row r="26" ht="39.2" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>PRÓSPERO COMERCIAL SOC.UNIP LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 11 Mins</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27" ht="23.6" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>TINTA POLIURETANO 2K PREMIUM 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1222.73</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3,668.19</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="6" t="n"/>
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
       <c r="F27" s="6" t="n"/>
-      <c r="G27" s="7" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
+      <c r="G27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="23.6" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>FERRAGEM HAPPY TOGETHER (called)</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
     </row>
     <row r="29" ht="23.6" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>PAK-MOZ FERRAGEM (visited)</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 15 Mins</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr"/>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr"/>
     </row>
     <row r="30" ht="23.6" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr"/>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>Sold Qty</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>Order Value</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr"/>
-    </row>
-    <row r="31" ht="23.6" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>DILUENTE LAQUER THINNER 750ml</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>3,450.00</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="39.2" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CHARME ECONOMY 1L - 015-001</t>
+          <t>TINTA DE ALUMINIO PREMIUM 1L - 015-001</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="n">
-        <v>216</v>
+        <v>18</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>356</v>
+        <v>341.6</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>76,896.00</t>
+          <t>6,148.80</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1965,162 +2421,194 @@
     <row r="32" ht="39.2" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ZARCAO SECAGEM NORMAL TRADE 5L - 015-001</t>
+          <t>10276 - DILUENTE SINTETICO ECONOMY 5L</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1428</v>
+        <v>636</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>71,400.00</t>
+          <t>3,816.00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
-    <row r="33" ht="39.2" customHeight="1">
+    <row r="33" ht="23.6" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
+          <t>DILUENTE LAQUER THINNER 750ml</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="n">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>386</v>
+        <v>138</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>69,480.00</t>
+          <t>3,450.00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
     </row>
-    <row r="34" ht="39.2" customHeight="1">
+    <row r="34" ht="23.6" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>DILUENTE SINTETICO ECONOMY 0.75L - 015-001</t>
+          <t>CHARME ECONOMY 1L - 015-001</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>350</v>
+        <v>36</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>124</v>
+        <v>360</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>43,400.00</t>
+          <t>12,960.00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
-    <row r="35" ht="23.6" customHeight="1">
+    <row r="35" ht="39.2" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>DILUENTE LAQUER THINNER 750ml</t>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>135</v>
+        <v>386</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>47,250.00</t>
+          <t>34,740.00</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="8" t="n"/>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
+    <row r="36" ht="39.2" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>28,560.00</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
     </row>
     <row r="37" ht="23.6" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>STEEL TRADE, LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 00 Mins</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr"/>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-    </row>
-    <row r="38" ht="23.6" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
-      <c r="G38" s="7" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>3,730.00</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="39.2" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>206-0001-020 - Nation PVA Branco 20L</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>1056</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>105,600.00</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="8" t="n"/>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="n"/>
-      <c r="G39" s="8" t="n"/>
+      <c r="A39" s="6" t="n"/>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n"/>
     </row>
     <row r="40" ht="23.6" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>FERRAGEM SERGIO E.I (visited)</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 00 Mins</t>
-        </is>
-      </c>
+          <t>AF FERRAGEM E.I (called)</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr"/>
       <c r="C40" s="4" t="inlineStr"/>
       <c r="D40" s="4" t="inlineStr"/>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2130,113 +2618,153 @@
     <row r="41" ht="23.6" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="6" t="n"/>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="8" t="n"/>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="8" t="n"/>
-      <c r="G42" s="8" t="n"/>
-    </row>
-    <row r="43" ht="39.2" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>FERRAGEM ABASEEN - SOC. UNIP. LDA (called)</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr"/>
-      <c r="C43" s="4" t="inlineStr"/>
-      <c r="D43" s="4" t="inlineStr"/>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr"/>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr"/>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42" ht="39.2" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>6,500.00</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="23.6" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1347</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>8,082.00</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
     </row>
     <row r="44" ht="23.6" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr"/>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>Sold Qty</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>Order Value</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 5L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1347</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>5,388.00</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
     </row>
     <row r="45" ht="23.6" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CHARME ECONOMY 5L - MEDIUM SERIES</t>
+          <t>CHARME ECONOMY 1L - 015-001</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1633.65</v>
+        <v>364</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>19,603.80</t>
+          <t>6,552.00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
     </row>
-    <row r="46" ht="23.6" customHeight="1">
+    <row r="46" ht="39.2" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>CHARME ECONOMY 5L - DARK SERIES</t>
+          <t>ZARCAO SECAGEM NORMAL TRADE 5L - 015-001</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1633.65</v>
+        <v>1458</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>45,742.20</t>
+          <t>8,748.00</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -2244,137 +2772,113 @@
     <row r="47" ht="39.2" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>MASSA ROBBIFILLA ECONOMY FILLER/ PUTTY 1KG - 015-001</t>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>128.62</v>
+        <v>394</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3,215.50</t>
+          <t>7,092.00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
     </row>
-    <row r="48" ht="23.6" customHeight="1">
+    <row r="48" ht="39.2" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>CHARME ECONOMY 1L - LIGHT SERIES</t>
+          <t>BERGER EXPERT ECONOMY 20L - 015-001</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>440.99</v>
+        <v>1115</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>71,440.38</t>
+          <t>24,530.00</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
     </row>
-    <row r="49" ht="23.6" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>CHARME ECONOMY 20L - LIGHT SERIES</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr"/>
-      <c r="D49" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>1633.65</v>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>8,168.25</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n"/>
     </row>
     <row r="50" ht="23.6" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>CHARME ECONOMY 1L - MEDIUM SERIES</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>1633.65</v>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>16,336.50</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>STEEL TRADE, LDA (called)</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr"/>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
     </row>
     <row r="51" ht="23.6" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>SUBCAPA PREMIUM 1L  - 015-001</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr"/>
-      <c r="D51" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>307.35</v>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>16,596.90</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52" ht="23.6" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr"/>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="39.2" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>769</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CHARME ECONOMY 1L - DARK SERIES</t>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 0.5L - DARK SERIES</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
@@ -2382,87 +2886,111 @@
         <v>36</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>440.99</v>
+        <v>178</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>15,875.64</t>
+          <t>6,408.00</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
     </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="8" t="n"/>
-      <c r="B53" s="8" t="n"/>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
-    </row>
-    <row r="54" ht="23.6" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>FERRAGEM BORJAN, LDA (called)</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr"/>
-      <c r="C54" s="4" t="inlineStr"/>
-      <c r="D54" s="4" t="inlineStr"/>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="4" t="inlineStr"/>
+    <row r="53" ht="39.2" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>12,880.00</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="39.2" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>12,880.00</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
     </row>
     <row r="55" ht="23.6" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr"/>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>Sold Qty</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>Order Value</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="inlineStr"/>
-    </row>
-    <row r="56" ht="23.6" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>DILUENTE LAQUER THINNER 750ml</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>17,125.00</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="39.2" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>191</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CHARME ECONOMY 1L - LIGHT SERIES</t>
+          <t>DILUENTE SINTETICO ECONOMY 0.75L - 015-001</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>440.99</v>
+        <v>124</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>7,937.82</t>
+          <t>31,000.00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2480,14 +3008,14 @@
       </c>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>440.99</v>
+        <v>397.56</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>7,937.82</t>
+          <t>21,468.24</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2495,24 +3023,24 @@
     <row r="58" ht="23.6" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>666</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CHARME ECONOMY 1L - MEDIUM SERIES</t>
+          <t>CHARME ECONOMY 1L - DARK SERIES</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>612.48</v>
+        <v>397.56</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>11,024.64</t>
+          <t>21,468.24</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2530,14 +3058,14 @@
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>440.99</v>
+        <v>552.16</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>63,502.56</t>
+          <t>49,694.40</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2545,24 +3073,24 @@
     <row r="60" ht="23.6" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>NATION PVA ECONOMY 5L - 015-001</t>
+          <t>CHARME ECONOMY 1L - 015-001</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>11,040.00</t>
+          <t>32,040.00</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -2570,24 +3098,24 @@
     <row r="61" ht="39.2" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>254</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - DARK SERIES</t>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - MEDIUM SERIES</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>318</v>
+        <v>397.56</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>38,160.00</t>
+          <t>21,468.24</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2595,24 +3123,24 @@
     <row r="62" ht="39.2" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>684</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - 015-001</t>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - DARK SERIES</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="n">
-        <v>160</v>
+        <v>54</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>318</v>
+        <v>397.56</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>50,880.00</t>
+          <t>21,468.24</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2620,221 +3148,44 @@
     <row r="63" ht="39.2" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>DILUENTE LAQUER THINNER PREMIUM 5L - 015-001</t>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="n">
-        <v>35</v>
+        <v>180</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>858</v>
+        <v>386</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>30,030.00</t>
+          <t>69,480.00</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
     </row>
-    <row r="64" ht="39.2" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>1025</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>10276 - DILUENTE SINTETICO ECONOMY 5L</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr"/>
-      <c r="D64" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>623</v>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>18,690.00</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65" ht="23.6" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>CHARME ECONOMY 5L - DARK SERIES</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr"/>
-      <c r="D65" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>52,800.00</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66" ht="23.6" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>CHARME ECONOMY 5L - 015-001</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="E66" s="2" t="n">
-        <v>1320</v>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>72,600.00</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67" ht="23.6" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>CHARME ECONOMY 1L - DARK SERIES</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr"/>
-      <c r="D67" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="E67" s="2" t="n">
-        <v>612.48</v>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>88,197.12</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="8" t="n"/>
-      <c r="B68" s="8" t="n"/>
-      <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
-      <c r="E68" s="8" t="n"/>
-      <c r="F68" s="8" t="n"/>
-      <c r="G68" s="8" t="n"/>
-    </row>
-    <row r="69" ht="23.6" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>ATLANTICA STEEL LDA (called)</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr"/>
-      <c r="C69" s="4" t="inlineStr"/>
-      <c r="D69" s="4" t="inlineStr"/>
-      <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr"/>
-      <c r="G69" s="4" t="inlineStr"/>
-    </row>
-    <row r="70" ht="23.6" customHeight="1">
-      <c r="A70" s="9" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr"/>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>Sold Qty</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>Order Value</t>
-        </is>
-      </c>
-      <c r="G70" s="9" t="inlineStr"/>
-    </row>
-    <row r="71" ht="23.6" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>PENDLEO TRADE 5L  - DARK SERIES</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr"/>
-      <c r="D71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="2" t="n">
-        <v>1832.43</v>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>1,832.43</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="8" t="n"/>
-      <c r="B72" s="8" t="n"/>
-      <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="n"/>
-      <c r="E72" s="8" t="n"/>
-      <c r="F72" s="8" t="n"/>
-      <c r="G72" s="8" t="n"/>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="6" t="n"/>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="6" t="n"/>
+      <c r="G64" s="6" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A41:G41"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -701,10 +701,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>5</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -1406,17 +1406,17 @@
       </c>
       <c r="P6" s="5" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="S6" s="5" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="V6" s="5" t="inlineStr">
         <is>
-          <t>16/20</t>
+          <t>13/20</t>
         </is>
       </c>
     </row>
@@ -1630,17 +1630,17 @@
       </c>
       <c r="P8" s="5" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="S8" s="5" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="V8" s="5" t="inlineStr">
         <is>
-          <t>9/20</t>
+          <t>6/20</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Q10" s="5" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R10" s="5" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>15/20</t>
+          <t>14/20</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="25" customHeight="1">
+    <row r="6" ht="39.2" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>INÁCIO RODRIGUES</t>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 16, 17, 18, 19 (4 days)</t>
+          <t>No attendance on dates: 16, 17, 18, 19, 20, 23, 24 (7 days)</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 2, 4, 6, 9, 10, 12, 13, 16, 17, 18, 19 (11 days)</t>
+          <t>No attendance on dates: 2, 4, 6, 9, 10, 12, 13, 16, 17, 18, 19, 20, 23, 24 (14 days)</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="25" customHeight="1">
+    <row r="10" ht="39.2" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>RICARDO MACUACUA</t>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 10, 12, 13, 16, 17 (5 days)</t>
+          <t>No attendance on dates: 10, 12, 13, 16, 17, 23 (6 days)</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2176,12 +2176,12 @@
     <row r="1" ht="23.6" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>FERRAGEM NHAMPIMBE, EI (visited)</t>
+          <t>FERRAGEM ACACIA (visited)</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 17 Mins</t>
+          <t>Time Spent: 00 Hrs 16 Mins</t>
         </is>
       </c>
       <c r="C1" s="6" t="inlineStr"/>
@@ -2222,102 +2222,66 @@
     <row r="3" ht="39.2" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>10276 - DILUENTE SINTETICO ECONOMY 5L</t>
+          <t>206-0001-020 - Nation PVA Branco 20L</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>5</v>
+        <v>501</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>636</v>
+        <v>1040</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>3,180.00</t>
+          <t>521,040.00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
     </row>
-    <row r="4" ht="39.2" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 5L - DARK SERIES</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1289</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,445.00</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
     </row>
     <row r="5" ht="23.6" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>PENDLEO TRADE 5L  - DARK SERIES</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>1526.75</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4,580.25</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM 1º DE MAIO (visited)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 40 Mins</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="23.6" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>PENDLEO TRADE 5L  - 015-001</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>1526.75</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,687.25</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="11" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="8" t="n"/>
@@ -2331,12 +2295,12 @@
     <row r="8" ht="23.6" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>SAAK INTERNACIONAL, LDA (visited)</t>
+          <t>CONSTRUA BUILD IT (visited)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 19 Mins</t>
+          <t>Time Spent: 00 Hrs 27 Mins</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr"/>
@@ -2370,12 +2334,12 @@
     <row r="11" ht="23.6" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>FERRAGEM VAVA, EI (visited)</t>
+          <t>SOLECTRIC, LDA (visited)</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 25 Mins</t>
+          <t>Time Spent: 00 Hrs 19 Mins</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr"/>
@@ -2406,15 +2370,15 @@
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
     </row>
-    <row r="14" ht="39.2" customHeight="1">
+    <row r="14" ht="23.6" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>OUSAF INTERNATIONAL TRADING LDA (visited)</t>
+          <t>FAZAL COMERCIAL, EI (visited)</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 17 Mins</t>
+          <t>Time Spent: 00 Hrs 31 Mins</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr"/>
@@ -2445,15 +2409,15 @@
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
     </row>
-    <row r="17" ht="39.2" customHeight="1">
+    <row r="17" ht="23.6" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>ELECTRO FERRAGEM MASTER SOLUTIONS (visited)</t>
+          <t>FERRAGEM COQUEIRO, LDA (visited)</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Time Spent: 00 Hrs 29 Mins</t>
+          <t>Time Spent: 00 Hrs 23 Mins</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr"/>
@@ -2463,315 +2427,215 @@
       <c r="G17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="23.6" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+    </row>
+    <row r="20" ht="39.2" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO DO RIO VERDE, SOC. UNIP. LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 14 Mins</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="23.6" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="11" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="39.2" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>FRANCIS FERRAGEM SOC. UNIP. LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 22 Mins</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr"/>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="23.6" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="8" t="n"/>
+    </row>
+    <row r="26" ht="23.6" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM CHOUPAL (called)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="23.6" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Product ID</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Product Description</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr"/>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr"/>
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>Sold Qty</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>Order Value</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="39.2" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>1025</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>10276 - DILUENTE SINTETICO ECONOMY 5L</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="n">
+      <c r="G27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28" ht="23.6" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>GAMMA COR PREMIUM 25KG - 015-001</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>636</v>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3,180.00</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20" ht="39.2" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>10275 - DILUENTE SINTETICO ECONOMY 1L</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,720.00</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-    </row>
-    <row r="22" ht="23.6" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>FAZAL COMERCIAL, EI (visited)</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 20 Mins</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr"/>
-      <c r="D22" s="6" t="inlineStr"/>
-      <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr"/>
-      <c r="G22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23" ht="23.6" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="11" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-    </row>
-    <row r="25" ht="23.6" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>FERRAGEM MUNHISSE MNISI, E.I (called)</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr"/>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="23.6" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr"/>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Sold Qty</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Order Value</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27" ht="23.6" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>PENDAGUA TRADE 20L - DARK SERIES</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr"/>
-      <c r="D27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>2999.2</v>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>5,998.40</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
+      <c r="E28" s="2" t="n">
+        <v>1952.8</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>9,764.00</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
     </row>
     <row r="29" ht="23.6" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>FERRAGEM ZAM ZAM (called)</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr"/>
-      <c r="C29" s="6" t="inlineStr"/>
-      <c r="D29" s="6" t="inlineStr"/>
-      <c r="E29" s="6" t="inlineStr"/>
-      <c r="F29" s="6" t="inlineStr"/>
-      <c r="G29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30" ht="23.6" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr"/>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Sold Qty</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>Order Value</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31" ht="23.6" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>1023</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10274 - wallplast  25kgs</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr"/>
-      <c r="D31" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>958</v>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>105,380.00</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32" ht="23.6" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>NATION PVA ECONOMY 20L - 015-001</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="n">
-        <v>501</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>1040</v>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>521,040.00</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="8" t="n"/>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>GAMMA COR PREMIUM 25KG - 015-001</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>2244.6</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>6,733.80</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A23:G23"/>
+  <mergeCells count="7">
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2783,7 +2647,1094 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="23.6" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>CONSTRU YAKA (visited)</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 13 Mins</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr"/>
+      <c r="D1" s="6" t="inlineStr"/>
+      <c r="E1" s="6" t="inlineStr"/>
+      <c r="F1" s="6" t="inlineStr"/>
+      <c r="G1" s="6" t="inlineStr"/>
+    </row>
+    <row r="2" ht="23.6" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="11" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="23.6" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM ABAB LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 01 Hrs 09 Mins</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="23.6" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="23.6" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>AKBAR FERRAGEM (visited)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 13 Mins</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="23.6" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="23.6" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>AUTO FERRAGEM LAZARO COME (visited)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 10 Mins</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="23.6" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="11" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A11:G11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="23.6" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>TINTAS BERGER MAPUTO OFFICE (visited)</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 18 Mins</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr"/>
+      <c r="D1" s="6" t="inlineStr"/>
+      <c r="E1" s="6" t="inlineStr"/>
+      <c r="F1" s="6" t="inlineStr"/>
+      <c r="G1" s="6" t="inlineStr"/>
+    </row>
+    <row r="2" ht="23.6" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="11" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="23.6" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>GIRASSOL TRADING LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 01 Hrs 03 Mins</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="23.6" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="23.6" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 5L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15,840.00</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="23.6" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15,840.00</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="23.6" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 1L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25,632.00</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="23.6" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>25,632.00</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="39.2" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>27,792.00</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+    </row>
+    <row r="12" ht="23.6" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEIRA SÃO JOSÉ (visited)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 15 Mins</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13" ht="23.6" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="11" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+    </row>
+    <row r="15" ht="23.6" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM INDICO (visited)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 01 Mins</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16" ht="23.6" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+    </row>
+    <row r="18" ht="39.2" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM LABAIK SOC.UNIP, LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 06 Mins</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="23.6" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+    </row>
+    <row r="21" ht="39.2" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM MACICAME, SOCIEDADE UNIPESSOAL, LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 00 Hrs 53 Mins</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22" ht="23.6" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="23.6" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4,476.00</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="23.6" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 1L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>6,552.00</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="23.6" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6,552.00</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="39.2" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>7,092.00</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+    </row>
+    <row r="28" ht="23.6" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM MUHENGO, LDA (visited)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 01 Hrs 17 Mins</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="23.6" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+    </row>
+    <row r="31" ht="23.6" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM SERGIO E.I (visited)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Time Spent: 01 Hrs 32 Mins</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr"/>
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="23.6" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>No orders</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="8" t="n"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="8" t="n"/>
+    </row>
+    <row r="34" ht="39.2" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>MAKARAN COMERCIAL-SOCIEDADE UNIPESSOAL, LIMITADA (called)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr"/>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="23.6" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36" ht="23.6" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SUBCAPA PREMIUM 1L  - 015-001</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>307.35</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>3,073.50</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="39.2" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>10276 - DILUENTE SINTETICO ECONOMY 5L</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>636</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>3,180.00</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="39.2" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>7,092.00</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="39.2" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>DILUENTE SINTETICO ECONOMY 0.75L - 015-001</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>3,175.00</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="23.6" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>DILUENTE LAQUER THINNER 750ml</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>3,450.00</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="23.6" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>8,096.00</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="39.2" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>206-0001-020 - Nation PVA Branco 20L</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1056</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>105,600.00</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="8" t="n"/>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+    </row>
+    <row r="44" ht="23.6" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>FERRAGEM RHULANE EI (called)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr"/>
+      <c r="C44" s="6" t="inlineStr"/>
+      <c r="D44" s="6" t="inlineStr"/>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="23.6" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46" ht="23.6" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>3,730.00</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="8" t="n"/>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A19:G19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2798,14 +3749,10 @@
     <row r="1" ht="39.2" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>OUSAF INTERNATIONAL TRADING LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 15 Mins</t>
-        </is>
-      </c>
+          <t>PAIZINHO COMERCIAL SOC. UNIP. LDA (called)</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr"/>
       <c r="C1" s="6" t="inlineStr"/>
       <c r="D1" s="6" t="inlineStr"/>
       <c r="E1" s="6" t="inlineStr"/>
@@ -2813,56 +3760,108 @@
       <c r="G1" s="6" t="inlineStr"/>
     </row>
     <row r="2" ht="23.6" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="11" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="n"/>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr"/>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="39.2" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DILUENTE LAQUER THINNER PREMIUM 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>858</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>17,160.00</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4" ht="39.2" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>INDO AFRICA COMERCIAL - ARMAZENS VITORIA (visited)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 15 Mins</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr"/>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>DILUENTE LAQUER THINNER PREMIUM 1L -015-001</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20,500.00</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="23.6" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="n"/>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="11" t="n"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 20L - 015-001</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>104,000.00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="8" t="n"/>
@@ -2876,14 +3875,10 @@
     <row r="7" ht="23.6" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>FARZANA SERVICES (visited)</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 15 Mins</t>
-        </is>
-      </c>
+          <t>TINTAS E FERRAGENS, LDA (called)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr"/>
@@ -2891,94 +3886,130 @@
       <c r="G7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="23.6" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="11" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="39.2" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>10272 - CORANTE CROWN DU T MEDIUM 1L</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1671.24</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>40,109.76</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
     </row>
     <row r="10" ht="39.2" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>FERRAGEM - E- HUSSAIN SOC. UNIP LDA - AV. JOSINA MACHEL. BAIXA (visited)</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 35 Mins</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr"/>
-      <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr"/>
-      <c r="G10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11" ht="23.6" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Sold Qty</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Order Value</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>10263 - CORANTE CROWN DU AXX ORGANIC 1L</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1364.72</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16,376.64</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="39.2" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>10269 - CORANTE CROWN DU QS HS YELLOW 1L</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>2201.59</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26,419.08</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12" ht="39.2" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - 015-001</t>
+          <t>10259 - CORANTE CROWN DU C YELLOW 1L</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>325</v>
+        <v>902.85</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,250.00</t>
+          <t>21,668.40</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -2986,278 +4017,374 @@
     <row r="13" ht="39.2" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - DARK SERIES</t>
+          <t>10268 - CORANTE CROWN DU V MAGENTA 1L</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>325</v>
+        <v>1483.32</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,250.00</t>
+          <t>26,699.76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
     </row>
-    <row r="14" ht="23.6" customHeight="1">
+    <row r="14" ht="39.2" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHARME ECONOMY 5L - 015-001</t>
+          <t>10258 - CORANTE CROWN DU B  BLACK 1L</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1333</v>
+        <v>663.15</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,330.00</t>
+          <t>15,915.60</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
-    <row r="15" ht="23.6" customHeight="1">
+    <row r="15" ht="39.2" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>NATION PVA ECONOMY 5L - 015-001</t>
+          <t>10260 - CORANTE CROWN DU F RED OXIDE 1L</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>373</v>
+        <v>1008</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,730.00</t>
+          <t>18,144.00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
     </row>
-    <row r="16" ht="23.6" customHeight="1">
+    <row r="16" ht="39.2" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>PREMIER PREMIUM 20L -015-001</t>
+          <t>10261 - CORANTE CROWN DU XX WHITE 1L</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1122.51</v>
+        <v>983.87</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,225.10</t>
+          <t>17,709.66</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
-    <row r="17" ht="23.6" customHeight="1">
+    <row r="17" ht="39.2" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>NATION PVA ECONOMY 20L - 015-001</t>
+          <t>10265 - CORANTE CROWN DU E PHTHALO 1L</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>748.34</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>13,470.12</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="39.2" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>081-1001 - PENDAGUA PASTEL BASE 20L</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2105.54</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>21,055.40</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="23.6" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>081-1002 - PENDAGUA DEEP BASE 20L</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1993.62</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>29,904.30</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="39.2" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>10211 - SILKY SMOOTH PASTEL BASE 5L</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>925.4</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>18,508.00</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="39.2" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>119-1001 - SILKY SMOOTH PASTEL BASE 20L</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>1088</v>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>27,200.00</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-    </row>
-    <row r="19" ht="23.6" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>ARIMEK COMERCIAL EI (visited)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 20 Mins</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20" ht="23.6" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="11" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
+      <c r="E21" s="2" t="n">
+        <v>3279.48</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>81,987.00</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
     </row>
     <row r="22" ht="39.2" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>MBFL FERRAGENS - SOC. UNIP. LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 15 Mins</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr"/>
-      <c r="D22" s="6" t="inlineStr"/>
-      <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr"/>
-      <c r="G22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23" ht="23.6" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="11" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>10215 - SILKY SMOOTH ACCENT BASE 5L</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1060.24</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>26,506.00</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="39.2" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>119-1003 - SILKY SMOOTH ACCENT BASE 20L</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>3866.28</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>96,657.00</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="23.6" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>10213 - SILKY SMOOTH DEEP BASE 5L</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>876.12</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>13,141.80</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="39.2" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>FERRAGEM HUSSAIN E.I AV ANGOLA 2216 (called)</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr"/>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>119-1002 - SILKY SMOOTH DEEP BASE 20L</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>3142.86</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>157,143.00</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
     </row>
     <row r="26" ht="23.6" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr"/>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Sold Qty</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Order Value</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27" ht="39.2" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SILKY SMOOTH PREMIUM 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1098</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>16,470.00</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="23.6" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - 015-001</t>
+          <t>SILKY SMOOTH PREMIUM 20L - 015-001</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>325</v>
+        <v>3256</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3,250.00</t>
+          <t>48,840.00</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -3265,24 +4392,24 @@
     <row r="28" ht="39.2" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - DARK SERIES</t>
+          <t>CROWN ECO VESTA ECONOMY 20L - 015-001</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>325</v>
+        <v>1333</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3,250.00</t>
+          <t>33,325.00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -3290,933 +4417,591 @@
     <row r="29" ht="23.6" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>667</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CHARME ECONOMY 5L - 015-001</t>
+          <t>CHARME ECONOMY 5L - DARK SERIES</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1333</v>
+        <v>1320</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13,330.00</t>
+          <t>19,800.00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
     </row>
-    <row r="30" ht="39.2" customHeight="1">
+    <row r="30" ht="23.6" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>NATION ESMALTE ECONOMY 5L - 015-001</t>
+          <t>CHARME ECONOMY 1L - 015-001</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3,730.00</t>
+          <t>5,460.00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
-    <row r="31" ht="39.2" customHeight="1">
+    <row r="31" ht="23.6" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>666</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>NATION ESMALTE ECONOMY 20L - 015-001</t>
+          <t>CHARME ECONOMY 1L - DARK SERIES</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1088</v>
+        <v>364</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27,200.00</t>
+          <t>5,460.00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="8" t="n"/>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A23:G23"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="23.6" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>TINTAS BERGER MAPUTO OFFICE (visited)</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 48 Mins</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr"/>
-      <c r="D1" s="6" t="inlineStr"/>
-      <c r="E1" s="6" t="inlineStr"/>
-      <c r="F1" s="6" t="inlineStr"/>
-      <c r="G1" s="6" t="inlineStr"/>
-    </row>
-    <row r="2" ht="23.6" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="11" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="n"/>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
-    </row>
-    <row r="4" ht="23.6" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>ELECTRO FERRAGEM BIÉ,E.I (visited)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 17 Mins</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr"/>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="23.6" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="n"/>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="11" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="39.2" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>MAKARAN COMERCIAL-SOCIEDADE UNIPESSOAL, LIMITADA (visited)</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 17 Mins</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="23.6" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="11" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-    </row>
-    <row r="10" ht="23.6" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>SOHA TRADING. SOC. UNIP (visited)</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 03 Mins</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr"/>
-      <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr"/>
-      <c r="G10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11" ht="23.6" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Sold Qty</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Order Value</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12" ht="23.6" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="32" ht="23.6" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NATION PVA ECONOMY 5L - 015-001</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>368</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,040.00</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
-    </row>
-    <row r="14" ht="23.6" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>SUGIRA FERRAGEM, SU,LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 37 Mins</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15" ht="23.6" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="11" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-    </row>
-    <row r="17" ht="39.2" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>FERRAGEM MACICAME, SOCIEDADE UNIPESSOAL, LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 42 Mins</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18" ht="23.6" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="11" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-    </row>
-    <row r="20" ht="39.2" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>NAWAZ TRADER, COMERCIAL. SOC. UNIP.LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 16 Mins</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-    </row>
-    <row r="21" ht="23.6" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="11" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-    </row>
-    <row r="23" ht="23.6" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>CUAMBA&amp;#039;S FERRAGEM, EI (visited)</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 56 Mins</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr"/>
-      <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
-      <c r="G23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="23.6" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="11" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="8" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-    </row>
-    <row r="26" ht="23.6" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>FERRAGEM YANG, SU,LDA (called)</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr"/>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27" ht="23.6" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Sold Qty</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Order Value</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28" ht="39.2" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>386</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>41,688.00</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="8" t="n"/>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
-    </row>
-    <row r="30" ht="23.6" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>FERRAGEM RHULANE EI (called)</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr"/>
-      <c r="C30" s="6" t="inlineStr"/>
-      <c r="D30" s="6" t="inlineStr"/>
-      <c r="E30" s="6" t="inlineStr"/>
-      <c r="F30" s="6" t="inlineStr"/>
-      <c r="G30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31" ht="23.6" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr"/>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>Sold Qty</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Order Value</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32" ht="39.2" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>206-0001-020 - Nation PVA Branco 20L</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1088</v>
+        <v>368</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>23,936.00</t>
+          <t>18,400.00</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="8" t="n"/>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
+    <row r="33" ht="23.6" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 20L - 015-001</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>104,000.00</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="39.2" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>ZARCAO SECAGEM NORMAL TRADE 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>5,910.00</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="8" t="n"/>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="n"/>
+      <c r="G35" s="8" t="n"/>
+    </row>
+    <row r="36" ht="39.2" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>COMPANHIA DONA CECILIA FERRAGEM (called)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr"/>
+      <c r="C36" s="6" t="inlineStr"/>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr"/>
+      <c r="F36" s="6" t="inlineStr"/>
+      <c r="G36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="23.6" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38" ht="23.6" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 20L - 015-001</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>520,000.00</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="8" t="n"/>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="8" t="n"/>
+    </row>
+    <row r="40" ht="23.6" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>ELECTRO FERRAGEM NDZIMANE LDA (called)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr"/>
+      <c r="C40" s="6" t="inlineStr"/>
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="23.6" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42" ht="23.6" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 20L - 015-001</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>156,000.00</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="39.2" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>DILUENTE SINTETICO ECONOMY 0.75L - 015-001</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>9,300.00</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="23.6" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>3,730.00</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="8" t="n"/>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="8" t="n"/>
+    </row>
+    <row r="46" ht="23.6" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>P.P. IMPORTACAO E EXPORTACAO (called)</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr"/>
+      <c r="C46" s="6" t="inlineStr"/>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="23.6" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Sold Qty</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>Order Value</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48" ht="39.2" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 0.5L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>188.55</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>13,575.60</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="23.6" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>CHARME ECONOMY 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>1428.57</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>7,142.85</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="39.2" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - DARK SERIES</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>478.67</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>19,146.80</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="39.2" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - 015-001</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>344.64</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>20,678.40</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="39.2" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 0.5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>188.55</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>20,363.40</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="23.6" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 5L - 015-001</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>377.97</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>9,449.25</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="23.6" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>NATION PVA ECONOMY 20L - 015-001</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>1039.5</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>155,925.00</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="8" t="n"/>
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="8" t="n"/>
+      <c r="F55" s="8" t="n"/>
+      <c r="G55" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A5:G5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="23.6" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>TINTAS E FERRAGENS, LDA (visited)</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 53 Mins</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr"/>
-      <c r="D1" s="6" t="inlineStr"/>
-      <c r="E1" s="6" t="inlineStr"/>
-      <c r="F1" s="6" t="inlineStr"/>
-      <c r="G1" s="6" t="inlineStr"/>
-    </row>
-    <row r="2" ht="23.6" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="11" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="n"/>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
-    </row>
-    <row r="4" ht="23.6" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>P.P. IMPORTACAO E EXPORTACAO (visited)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 15 Mins</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr"/>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="23.6" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="n"/>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="11" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="23.6" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>NATVARLAL COMERCIAL EI (visited)</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 41 Mins</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="23.6" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="11" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-    </row>
-    <row r="10" ht="23.6" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>ABDUL SULTANE (visited)</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 11 Mins</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr"/>
-      <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr"/>
-      <c r="G10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11" ht="23.6" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="10" t="n"/>
-      <c r="G11" s="11" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-    </row>
-    <row r="13" ht="23.6" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>FERRAGEM GUAMBE (visited)</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Time Spent: 00 Hrs 23 Mins</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14" ht="23.6" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>No orders</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="11" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-    </row>
-    <row r="16" ht="23.6" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>DAFITI COMERCIO E SERVICO LDA (called)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr"/>
-      <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="6" t="inlineStr"/>
-      <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17" ht="23.6" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Sold Qty</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Order Value</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18" ht="39.2" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>VERNIZ PARA MADEIRA INCOLOR+ CORES PREMIUM 1L - 015-001</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>328.23</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,564.60</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A5:G5"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -72,16 +75,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -481,7 +484,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -496,7 +499,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -556,7 +559,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -586,7 +589,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -1091,7 +1094,7 @@
       </c>
       <c r="S4" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="T4" s="4" t="inlineStr">
@@ -1106,7 +1109,7 @@
       </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t>18/20</t>
+          <t>17/20</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1318,7 @@
       </c>
       <c r="S6" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="T6" s="4" t="inlineStr">
@@ -1330,7 +1333,7 @@
       </c>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t>13/20</t>
+          <t>12/20</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1542,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="T8" s="4" t="inlineStr">
@@ -1554,7 +1557,7 @@
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>6/20</t>
+          <t>5/20</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1766,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="T10" s="4" t="inlineStr">
@@ -1778,7 +1781,7 @@
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>13/20</t>
+          <t>12/20</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1878,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="T11" s="4" t="inlineStr">
@@ -1890,7 +1893,7 @@
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>18/20</t>
+          <t>17/20</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1959,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 23, 24 (2 days)</t>
+          <t>No attendance on dates: 23, 24, 25 (3 days)</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1983,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 16, 17, 18, 19, 20, 23, 24 (7 days)</t>
+          <t>No attendance on dates: 16, 17, 18, 19, 20, 23, 24, 25 (8 days)</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2007,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 2, 4, 6, 9, 10, 12, 13, 16, 17, 18, 19, 20, 23, 24 (14 days)</t>
+          <t>No attendance on dates: 2, 4, 6, 9, 10, 12, 13, 16, 17, 18, 19, 20, 23, 24, 25 (15 days)</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2031,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 10, 12, 13, 16, 17, 23, 24 (7 days)</t>
+          <t>No attendance on dates: 10, 12, 13, 16, 17, 23, 24, 25 (8 days)</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2043,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 23, 24 (2 days)</t>
+          <t>No attendance on dates: 23, 24, 25 (3 days)</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="S4" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="T4" s="4" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t>18/20</t>
+          <t>17/20</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="S6" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="T6" s="4" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t>13/20</t>
+          <t>12/20</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="T8" s="4" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>6/20</t>
+          <t>5/20</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="T10" s="4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>13/20</t>
+          <t>12/20</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>X</t>
         </is>
       </c>
       <c r="T11" s="4" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>18/20</t>
+          <t>17/20</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 23, 24 (2 days)</t>
+          <t>No attendance on dates: 23, 24, 25 (3 days)</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 16, 17, 18, 19, 20, 23, 24 (7 days)</t>
+          <t>No attendance on dates: 16, 17, 18, 19, 20, 23, 24, 25 (8 days)</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 2, 4, 6, 9, 10, 12, 13, 16, 17, 18, 19, 20, 23, 24 (14 days)</t>
+          <t>No attendance on dates: 2, 4, 6, 9, 10, 12, 13, 16, 17, 18, 19, 20, 23, 24, 25 (15 days)</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 10, 12, 13, 16, 17, 23, 24 (7 days)</t>
+          <t>No attendance on dates: 10, 12, 13, 16, 17, 23, 24, 25 (8 days)</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 23, 24 (2 days)</t>
+          <t>No attendance on dates: 23, 24, 25 (3 days)</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Day Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Attendance Grid - February" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Monthly Attendance - February" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Day Visits" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,19 +871,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T2" s="4" t="inlineStr"/>
+      <c r="U2" s="4" t="inlineStr"/>
       <c r="V2" s="4" t="inlineStr">
         <is>
-          <t>20/20 - Perfect attendance</t>
+          <t>18/18 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -982,19 +975,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T3" s="4" t="inlineStr"/>
+      <c r="U3" s="4" t="inlineStr"/>
       <c r="V3" s="4" t="inlineStr">
         <is>
-          <t>19/20</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1094,19 +1079,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t>17/20</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1206,19 +1183,11 @@
           <t>L</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
       <c r="V5" s="4" t="inlineStr">
         <is>
-          <t>0/20</t>
+          <t>0/18</t>
         </is>
       </c>
     </row>
@@ -1318,19 +1287,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t>12/20</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1430,19 +1391,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T7" s="4" t="inlineStr"/>
+      <c r="U7" s="4" t="inlineStr"/>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t>20/20 - Perfect attendance</t>
+          <t>18/18 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1542,19 +1495,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T8" s="4" t="inlineStr"/>
+      <c r="U8" s="4" t="inlineStr"/>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>5/20</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1654,19 +1599,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T9" s="4" t="inlineStr"/>
+      <c r="U9" s="4" t="inlineStr"/>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>20/20 - Perfect attendance</t>
+          <t>18/18 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1766,19 +1703,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T10" s="4" t="inlineStr"/>
+      <c r="U10" s="4" t="inlineStr"/>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>12/20</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1878,19 +1807,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T11" s="4" t="inlineStr"/>
+      <c r="U11" s="4" t="inlineStr"/>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>17/20</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2047,4 +1968,465 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Salesperson</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Customer Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Time Spent</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ANDRE MARQUEZA</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM NHAMPIMBE, EI</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 56 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ANDRE MARQUEZA</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>TELLES COMERCIO &amp;amp; SERVICOS, LDA.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 21 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ANDRE MARQUEZA</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>FUXIN MATERIAL DE CONSTRUCAO TRADING, LDA</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 33 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ANDRE MARQUEZA</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ELECTRO FERRAGEM AFRICA, LDA</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 43 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ANDRE MARQUEZA</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>FIVE STAR COMERCIAL, EI</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 31 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ANDRE MARQUEZA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM MAHNOOR</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 21 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ANDRE MARQUEZA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM PONTE, LDA</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 41 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM TREVO FAMILIA</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 16 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM ALEX UCUCHO87</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 17 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>ELETRICA VOLTZ</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 17 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>HOME STORE</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 17 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>AQUAPESCA</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 17 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>KINTECH INTERNATIONAL CO SOCIEDADE UNIPESSOAL,LDA</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 19 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ITO BENEDITO</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM LIU</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 06 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ITO BENEDITO</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM ZAINAB, LDA</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 15 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ITO BENEDITO</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM DA PRACA</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 19 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ITO BENEDITO</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>MACOMAT MAT. CONSTRUCAO DE MOC.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 03 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ITO BENEDITO</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>GOD WIN FERRAGEM</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 20 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ITO BENEDITO</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM PURE ON HEART</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 12 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ITO BENEDITO</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>BLESSED MIKO IMPORT AND EXPORT, EI</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>TINTAS BERGER MAPUTO OFFICE</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>TINTAS BERGER MAPUTO OFFICE</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 45 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>AF FERRAGEM E.I</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 27 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEIRA SÃO JOSÉ</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 38 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM YANG, SU,LDA</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 31 Mins</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -497,11 +497,11 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Used App</t>
+          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
@@ -512,11 +512,11 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Did Not Use App</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -871,11 +871,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr"/>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U2" s="4" t="inlineStr"/>
       <c r="V2" s="4" t="inlineStr">
         <is>
-          <t>18/18 - Perfect attendance</t>
+          <t>19/19 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -975,11 +979,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="U3" s="4" t="inlineStr"/>
       <c r="V3" s="4" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -1079,11 +1087,15 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U4" s="4" t="inlineStr"/>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -1183,11 +1195,15 @@
           <t>L</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="U5" s="4" t="inlineStr"/>
       <c r="V5" s="4" t="inlineStr">
         <is>
-          <t>0/18</t>
+          <t>0/19</t>
         </is>
       </c>
     </row>
@@ -1287,11 +1303,15 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="U6" s="4" t="inlineStr"/>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -1391,11 +1411,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U7" s="4" t="inlineStr"/>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t>18/18 - Perfect attendance</t>
+          <t>19/19 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1495,11 +1519,15 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="U8" s="4" t="inlineStr"/>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -1599,11 +1627,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U9" s="4" t="inlineStr"/>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>18/18 - Perfect attendance</t>
+          <t>19/19 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1703,11 +1735,15 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T10" s="4" t="inlineStr"/>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="U10" s="4" t="inlineStr"/>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -1807,11 +1843,15 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="U11" s="4" t="inlineStr"/>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1905,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>No attendance on date: 23</t>
+          <t>No attendance on dates: 23, 26 (2 days)</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1941,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 16, 17, 18, 19, 20, 23, 24, 25 (8 days)</t>
+          <t>No attendance on dates: 16, 17, 18, 19, 20, 23, 24, 25, 26 (9 days)</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1965,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 2, 4, 6, 9, 10, 12, 13, 16, 17, 18, 19, 20, 23, 24, 25 (15 days)</t>
+          <t>No attendance on dates: 2, 4, 6, 9, 10, 12, 13, 16, 17, 18, 19, 20, 23, 24, 25, 26 (16 days)</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1989,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 10, 12, 13, 16, 17, 23, 24, 25 (8 days)</t>
+          <t>No attendance on dates: 10, 12, 13, 16, 17, 23, 24, 25, 26 (9 days)</t>
         </is>
       </c>
     </row>
@@ -1961,7 +2001,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 23, 24, 25 (3 days)</t>
+          <t>No attendance on dates: 23, 24, 25, 26 (4 days)</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2049,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM NHAMPIMBE, EI</t>
+          <t>KADI COMERCIAL</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 56 Mins</t>
+          <t>01 Hrs 54 Mins</t>
         </is>
       </c>
     </row>
@@ -2026,12 +2066,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TELLES COMERCIO &amp;amp; SERVICOS, LDA.</t>
+          <t>SAAK INTERNACIONAL, LDA</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 21 Mins</t>
+          <t>00 Hrs 30 Mins</t>
         </is>
       </c>
     </row>
@@ -2043,12 +2083,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FUXIN MATERIAL DE CONSTRUCAO TRADING, LDA</t>
+          <t>MALABAR MATERIAL DE CONSTRUCAO SOCIEDADE UNIPESSOAL, LD</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 33 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
@@ -2060,12 +2100,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ELECTRO FERRAGEM AFRICA, LDA</t>
+          <t>FERRAGEM DAS MAHOTAS,LDA</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 43 Mins</t>
+          <t>00 Hrs 45 Mins</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2117,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FIVE STAR COMERCIAL, EI</t>
+          <t>R.V ELECTRO FERRAGEM LDA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 31 Mins</t>
+          <t>00 Hrs 34 Mins</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2134,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM MAHNOOR</t>
+          <t>FERRAGEM MAFOCOSHO</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 21 Mins</t>
+          <t>00 Hrs 29 Mins</t>
         </is>
       </c>
     </row>
@@ -2111,58 +2151,58 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM PONTE, LDA</t>
+          <t>FERRAGEM BOM TEMPO</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 41 Mins</t>
+          <t>01 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM TREVO FAMILIA</t>
+          <t>MAKUZA COMERCIAL</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 16 Mins</t>
+          <t>00 Hrs 29 Mins</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ALEX UCUCHO87</t>
+          <t>FERNEX FERRAGEM</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 17 Mins</t>
+          <t>00 Hrs 24 Mins</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ELETRICA VOLTZ</t>
+          <t>FERRAGEM EXCLUSIVO</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2174,51 +2214,51 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>HOME STORE</t>
+          <t>FERRAGEM DA PRACA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 17 Mins</t>
+          <t>00 Hrs 04 Mins</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>AQUAPESCA</t>
+          <t>ROMSHA TRADING, LDA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 17 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>KINTECH INTERNATIONAL CO SOCIEDADE UNIPESSOAL,LDA</t>
+          <t>ELECTRO FERRAGEM REAL</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 19 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
@@ -2230,12 +2270,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM LIU</t>
+          <t>FERRAGEM MUIZ, EI</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 36 Mins</t>
         </is>
       </c>
     </row>
@@ -2247,12 +2287,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ZAINAB, LDA</t>
+          <t>AUTO FERRAGEM NELCIA, EI</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 14 Mins</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2304,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM DA PRACA</t>
+          <t>MBFL FERRAGENS - SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 19 Mins</t>
+          <t>00 Hrs 23 Mins</t>
         </is>
       </c>
     </row>
@@ -2281,12 +2321,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>MACOMAT MAT. CONSTRUCAO DE MOC.</t>
+          <t>ESTEVÃO BAPTISTA MUGUAMBE AUTO FERRAGEM</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 03 Mins</t>
+          <t>00 Hrs 02 Mins</t>
         </is>
       </c>
     </row>
@@ -2298,46 +2338,46 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>GOD WIN FERRAGEM</t>
+          <t>MT COMERCIAL, E.I</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 20 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM PURE ON HEART</t>
+          <t>TINTAS BERGER MAPUTO OFFICE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 12 Mins</t>
+          <t>01 Hrs 17 Mins</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>BLESSED MIKO IMPORT AND EXPORT, EI</t>
+          <t>CASA AMIZADE, LDA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>01 Hrs 52 Mins</t>
         </is>
       </c>
     </row>
@@ -2349,12 +2389,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>TINTAS BERGER MAPUTO OFFICE</t>
+          <t>MOZ INVESTIMENT &amp;amp; SERVICES, LDA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 26 Mins</t>
         </is>
       </c>
     </row>
@@ -2366,12 +2406,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>TINTAS BERGER MAPUTO OFFICE</t>
+          <t>INTERMETAL, SA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 45 Mins</t>
+          <t>00 Hrs 30 Mins</t>
         </is>
       </c>
     </row>
@@ -2383,12 +2423,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>AF FERRAGEM E.I</t>
+          <t>FERRAGEM ALI, SOCIEDADE UNIPESSOAL, LIMITADA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 27 Mins</t>
+          <t>01 Hrs 17 Mins</t>
         </is>
       </c>
     </row>
@@ -2400,12 +2440,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEIRA SÃO JOSÉ</t>
+          <t>TONY TINTAS</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 38 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2457,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM YANG, SU,LDA</t>
+          <t>CUAMBA&amp;#039;S FERRAGEM, EI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 31 Mins</t>
+          <t>00 Hrs 45 Mins</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>On Leave</t>
+          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Did Not Use App</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Did Not Use App</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
@@ -783,8 +783,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr"/>
-      <c r="D2" s="4" t="inlineStr"/>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E2" s="4" t="inlineStr"/>
       <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" s="4" t="inlineStr"/>
@@ -806,7 +814,7 @@
       <c r="W2" s="4" t="inlineStr"/>
       <c r="X2" s="4" t="inlineStr">
         <is>
-          <t>1/1 - Perfect attendance</t>
+          <t>3/3 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -821,8 +829,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr"/>
@@ -844,7 +860,7 @@
       <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr">
         <is>
-          <t>1/1 - Perfect attendance</t>
+          <t>3/3 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -859,8 +875,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr"/>
@@ -882,7 +906,7 @@
       <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/3</t>
         </is>
       </c>
     </row>
@@ -897,8 +921,16 @@
           <t>L</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr"/>
@@ -920,7 +952,7 @@
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/3</t>
         </is>
       </c>
     </row>
@@ -935,8 +967,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr"/>
@@ -958,7 +998,7 @@
       <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>1/1 - Perfect attendance</t>
+          <t>3/3 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -973,8 +1013,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr"/>
@@ -996,7 +1044,7 @@
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>2/3</t>
         </is>
       </c>
     </row>
@@ -1011,8 +1059,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr"/>
@@ -1034,7 +1090,7 @@
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>1/1 - Perfect attendance</t>
+          <t>3/3 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1049,8 +1105,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr"/>
@@ -1072,7 +1136,7 @@
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/3</t>
         </is>
       </c>
     </row>
@@ -1087,8 +1151,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr"/>
@@ -1110,7 +1182,7 @@
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/3</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1248,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>No attendance on date: 2</t>
+          <t>No attendance on dates: 2, 4 (2 days)</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1260,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Not active - On leave</t>
+          <t>No attendance on date: 4</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1308,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>No attendance on date: 2</t>
+          <t>No attendance on dates: 2, 3 (2 days)</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1320,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>No attendance on date: 2</t>
+          <t>No attendance on dates: 2, 3, 4 (3 days)</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1296,12 +1368,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM CHOUPAL</t>
+          <t>SOLECTRIC, LDA</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 31 Mins</t>
+          <t>00 Hrs 14 Mins</t>
         </is>
       </c>
     </row>
@@ -1313,63 +1385,590 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KHENSANY FERRAGEM, LDA</t>
+          <t>CHINA MALL, LDA</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 38 Mins</t>
+          <t>00 Hrs 21 Mins</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>PRIME MAPUTO</t>
+          <t>FRANCIS FERRAGEM SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 19 Mins</t>
+          <t>02 Hrs 21 Mins</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM AFRIPAK TRADING EI</t>
+          <t>NOVO MOZ TRADING</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 14 Mins</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>ANDRE MARQUEZA</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM EBENEZER</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 14 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ANDRE MARQUEZA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>KADI COMERCIAL</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 27 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ANDRE MARQUEZA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM COQUEIRO, LDA</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 55 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>PANLEEN OFFICE</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 18 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>MARABIL IMOBILIARIA</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 03 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>TEIXEIRA DUARTE</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 02 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>CONSTRUCAO DE HOTEL</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 04 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>EDIFICIO MULTIFAMILIAR</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 04 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>PANORAMA TOWER</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 04 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>GAME STORE</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 08 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>JULEN CONSTRUÇÕES</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 14 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ITO BENEDITO</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>J. ELECTRO FERRAGEM SOC. UNIP. LDA</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 13 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ITO BENEDITO</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>BLESSED MIKO IMPORT AND EXPORT, EI</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ITO BENEDITO</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>XIANG FENG MERCADO</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 16 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ITO BENEDITO</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM BLESSED DESIGN</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 16 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ITO BENEDITO</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM PURE ON HEART</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 06 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ITO BENEDITO</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM AUTO GEMO</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 47 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>KUMAR CHAMPAKLAL</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>HOTEL SENA</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 08 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>KUMAR CHAMPAKLAL</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM NOVA PODEROSA SOC. UNIP. LDA</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>TINTAS BERGER MAPUTO OFFICE</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>06 Hrs 09 Mins</t>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>02 Hrs 06 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>ELECTRO FERRAGEM BIÉ,E.I</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 20 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>INTERMETAL, SA</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM DULA EI</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 03 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>PAK-MOZ FERRAGEM</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 15 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>STEEL TRADE, LDA</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 20 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>GAYE GROUP FERRAGEM,  LDA</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 07 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>ATLANTICA STEEL LDA</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 27 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>UZAMBIANE FERRAGENS LDA</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>P.P. IMPORTACAO E EXPORTACAO</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 18 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>LANGA COMERCIAL SOC UNP LDA</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 49 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>TINTAS E FERRAGENS, LDA</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 05 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGENS JALASAI</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -512,11 +512,11 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Did Not Use App</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -602,11 +602,11 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Did Not Use App</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr"/>
@@ -814,7 +818,7 @@
       <c r="W2" s="4" t="inlineStr"/>
       <c r="X2" s="4" t="inlineStr">
         <is>
-          <t>3/3 - Perfect attendance</t>
+          <t>4/4 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -839,7 +843,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr"/>
@@ -860,7 +868,7 @@
       <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr">
         <is>
-          <t>3/3 - Perfect attendance</t>
+          <t>4/4 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -885,7 +893,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr"/>
@@ -906,7 +918,7 @@
       <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/4</t>
         </is>
       </c>
     </row>
@@ -931,7 +943,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
@@ -952,7 +968,7 @@
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -977,7 +993,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr"/>
@@ -998,7 +1018,7 @@
       <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>3/3 - Perfect attendance</t>
+          <t>4/4 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1043,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr"/>
@@ -1044,7 +1068,7 @@
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/4</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1093,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr"/>
@@ -1090,7 +1118,7 @@
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>3/3 - Perfect attendance</t>
+          <t>4/4 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1143,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr"/>
@@ -1136,7 +1168,7 @@
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/4</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1193,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr"/>
@@ -1182,7 +1218,7 @@
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/4</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1296,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>No attendance on date: 4</t>
+          <t>No attendance on dates: 4, 5 (2 days)</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1368,12 +1404,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SOLECTRIC, LDA</t>
+          <t>FERRAGEM DAS MAHOTAS,LDA</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>00 Hrs 29 Mins</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1421,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CHINA MALL, LDA</t>
+          <t>FIVE STAR COMERCIAL, EI</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 21 Mins</t>
+          <t>01 Hrs 16 Mins</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1438,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FRANCIS FERRAGEM SOC. UNIP. LDA</t>
+          <t>SUPERMERCADO DO RIO VERDE, SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>02 Hrs 21 Mins</t>
+          <t>00 Hrs 57 Mins</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1455,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>NOVO MOZ TRADING</t>
+          <t>LIMPOPO TRADING, LDA</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>00 Hrs 30 Mins</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1472,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM EBENEZER</t>
+          <t>FERRAGEM 1º DE MAIO</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>00 Hrs 43 Mins</t>
         </is>
       </c>
     </row>
@@ -1453,29 +1489,29 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>KADI COMERCIAL</t>
+          <t>FERRAGEM NHAMPIMBE, EI</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 27 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM COQUEIRO, LDA</t>
+          <t>SUPERMERCADO NUMBER ONE</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 55 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1523,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>PANLEEN OFFICE</t>
+          <t>FEI TENG TONG</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 18 Mins</t>
+          <t>00 Hrs 38 Mins</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1540,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>MARABIL IMOBILIARIA</t>
+          <t>XIANG FENG MERCADO</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 03 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1557,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TEIXEIRA DUARTE</t>
+          <t>MAZZA FERRAGEM</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 02 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1574,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CONSTRUCAO DE HOTEL</t>
+          <t>FERRAGEM SIMBINE</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 04 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1591,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>EDIFICIO MULTIFAMILIAR</t>
+          <t>M.O FERRAFEM VENTURES</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 04 Mins</t>
+          <t>00 Hrs 14 Mins</t>
         </is>
       </c>
     </row>
@@ -1572,63 +1608,63 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PANORAMA TOWER</t>
+          <t>FERRAGEM MARCELINO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 04 Mins</t>
+          <t>00 Hrs 14 Mins</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>GAME STORE</t>
+          <t>CRESCENTE COMERCIAL TETE</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 11 Mins</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>JULEN CONSTRUÇÕES</t>
+          <t>ELECTRO LIDER</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>04 Hrs 43 Mins</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>J. ELECTRO FERRAGEM SOC. UNIP. LDA</t>
+          <t>FORMEX</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 13 Mins</t>
+          <t>00 Hrs 21 Mins</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1676,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>BLESSED MIKO IMPORT AND EXPORT, EI</t>
+          <t>GHORI COMERCIAL, EI</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 11 Mins</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1693,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>XIANG FENG MERCADO</t>
+          <t>FERRAGEM ZAINAB, LDA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 16 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1710,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM BLESSED DESIGN</t>
+          <t>FERRAGEM FATIMA, LDA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 16 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1727,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM PURE ON HEART</t>
+          <t>Z.K FERRAGEM, E.I</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 28 Mins</t>
         </is>
       </c>
     </row>
@@ -1708,148 +1744,148 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM AUTO GEMO</t>
+          <t>FERRAGEM CAMINHO DA OBRA, LDA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 47 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>HOTEL SENA</t>
+          <t>MODALAND INTERPRICES</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 27 Mins</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM NOVA PODEROSA SOC. UNIP. LDA</t>
+          <t>OBINNY FERRAGEM IITEGRATED</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 25 Mins</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TINTAS BERGER MAPUTO OFFICE</t>
+          <t>FERRAGEM PURE ON HEART</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>02 Hrs 06 Mins</t>
+          <t>00 Hrs 01 Mins</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ELECTRO FERRAGEM BIÉ,E.I</t>
+          <t>MOBILITY INVESTIMENTO, EI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 20 Mins</t>
+          <t>00 Hrs 01 Mins</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>INTERMETAL, SA</t>
+          <t>FERROX</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 09 Mins</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM DULA EI</t>
+          <t>CHEER BEST DEVELOPMENT LDA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 03 Mins</t>
+          <t>00 Hrs 04 Mins</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>PAK-MOZ FERRAGEM</t>
+          <t>FERSOL</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>STEEL TRADE, LDA</t>
+          <t>FERRAGEM AISHA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 20 Mins</t>
+          <t>00 Hrs 11 Mins</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1897,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GAYE GROUP FERRAGEM,  LDA</t>
+          <t>TINTAS BERGER MAPUTO OFFICE</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>02 Hrs 30 Mins</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1914,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ATLANTICA STEEL LDA</t>
+          <t>MOZ INVESTIMENT &amp;amp; SERVICES, LDA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 27 Mins</t>
+          <t>00 Hrs 13 Mins</t>
         </is>
       </c>
     </row>
@@ -1895,80 +1931,233 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>UZAMBIANE FERRAGENS LDA</t>
+          <t>IFRESH, LDA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 22 Mins</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>P.P. IMPORTACAO E EXPORTACAO</t>
+          <t>HANANA STEELS, LDA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 18 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>LANGA COMERCIAL SOC UNP LDA</t>
+          <t>FERRAGEM AUTO J.J, LDA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 49 Mins</t>
+          <t>00 Hrs 18 Mins</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>TINTAS E FERRAGENS, LDA</t>
+          <t>FERRAGEM ABASEEN - SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>CHIBUKEN LIMITADA</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 12 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM POSTOS SOC.UNIP. LDA</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 12 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>ELECTRO FERRAGEM UNIVERSO,  E.I</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 42 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>ARMANDO FERRAGEM, E.I</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 31 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
           <t>RICARDO MACUACUA</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>FERRAGENS JALASAI</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 00 Mins</t>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 45 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>TINTAS E FERRAGENS, LDA</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>01 Hrs 07 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM GLORIOSO</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 18 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>UAMUSSE FERRANGEM</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 15 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>ALIN COMERCIAL</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>01 Hrs 17 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>AMAL COMERCIAL</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -73,16 +76,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -482,7 +485,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -497,7 +500,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -512,7 +515,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -542,7 +545,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -557,7 +560,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -572,7 +575,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -587,7 +590,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -798,7 +801,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr"/>
       <c r="I2" s="4" t="inlineStr"/>
@@ -818,7 +825,7 @@
       <c r="W2" s="4" t="inlineStr"/>
       <c r="X2" s="4" t="inlineStr">
         <is>
-          <t>4/4 - Perfect attendance</t>
+          <t>5/5 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -848,7 +855,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr"/>
@@ -868,7 +879,7 @@
       <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr">
         <is>
-          <t>4/4 - Perfect attendance</t>
+          <t>5/5 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -898,7 +909,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr"/>
       <c r="I4" s="4" t="inlineStr"/>
@@ -918,7 +933,7 @@
       <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>3/5</t>
         </is>
       </c>
     </row>
@@ -948,7 +963,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr"/>
@@ -968,7 +987,7 @@
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>0/5</t>
         </is>
       </c>
     </row>
@@ -998,7 +1017,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr"/>
@@ -1018,7 +1041,7 @@
       <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>4/4 - Perfect attendance</t>
+          <t>5/5 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1071,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr"/>
@@ -1068,7 +1095,7 @@
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/5</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1125,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="4" t="inlineStr"/>
@@ -1118,7 +1149,7 @@
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>4/4 - Perfect attendance</t>
+          <t>5/5 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1179,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr"/>
@@ -1168,7 +1203,7 @@
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>3/5</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1233,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr"/>
       <c r="I10" s="4" t="inlineStr"/>
@@ -1218,7 +1257,7 @@
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>2/5</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1335,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 4, 5 (2 days)</t>
+          <t>No attendance on dates: 4, 5, 6 (3 days)</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1404,12 +1443,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM DAS MAHOTAS,LDA</t>
+          <t>ELECTRO FERRAGEM MASTER SOLUTIONS</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 29 Mins</t>
+          <t>00 Hrs 14 Mins</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1460,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>FIVE STAR COMERCIAL, EI</t>
+          <t>FERRAGEM PONTE, LDA</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 16 Mins</t>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1477,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO DO RIO VERDE, SOC. UNIP. LDA</t>
+          <t>JOHNSON FERRAGENS. SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 57 Mins</t>
+          <t>00 Hrs 26 Mins</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1494,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>LIMPOPO TRADING, LDA</t>
+          <t>CONSTRUA BUILD IT</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 30 Mins</t>
+          <t>00 Hrs 26 Mins</t>
         </is>
       </c>
     </row>
@@ -1472,29 +1511,29 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM 1º DE MAIO</t>
+          <t>FERRAGEM SABHA, LDA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 43 Mins</t>
+          <t>00 Hrs 50 Mins</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM NHAMPIMBE, EI</t>
+          <t>FERRAGEM AUTOCARIZ</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 19 Mins</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1545,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO NUMBER ONE</t>
+          <t>J COMO FERRAGEM</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 17 Mins</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1562,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FEI TENG TONG</t>
+          <t>FERRAGEM MONDWA</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 38 Mins</t>
+          <t>00 Hrs 11 Mins</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1579,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>XIANG FENG MERCADO</t>
+          <t>FERRAGEM KHURULA</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 18 Mins</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1596,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MAZZA FERRAGEM</t>
+          <t>FERRAGEM ARTESÃO</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1569,595 +1608,476 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM SIMBINE</t>
+          <t>RASHID COMERCIAL</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>M.O FERRAFEM VENTURES</t>
+          <t>AKBAR FERRAGEM</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM MARCELINO</t>
+          <t>AUTO FERRAGEM LAZARO COME</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>00 Hrs 01 Mins</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE BERTUR</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CRESCENTE COMERCIAL TETE</t>
+          <t>FERRAGEM LIU</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 11 Mins</t>
+          <t>00 Hrs 03 Mins</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE BERTUR</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ELECTRO LIDER</t>
+          <t>FERRAGEM CHAMISSAVA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>04 Hrs 43 Mins</t>
+          <t>00 Hrs 03 Mins</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE BERTUR</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FORMEX</t>
+          <t>FERRAGEM CAMINHO DA OBRA, LDA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 21 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>GHORI COMERCIAL, EI</t>
+          <t>CHEER BEST DEVELOPMENT LDA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 11 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ZAINAB, LDA</t>
+          <t>FERSOL</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>00 Hrs 26 Mins</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM FATIMA, LDA</t>
+          <t>G.F COMERCIAL</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 19 Mins</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Z.K FERRAGEM, E.I</t>
+          <t>TINTAS BERGER MAPUTO OFFICE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 28 Mins</t>
+          <t>01 Hrs 23 Mins</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM CAMINHO DA OBRA, LDA</t>
+          <t>FERRAGEM ALI, SOCIEDADE UNIPESSOAL, LIMITADA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 24 Mins</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MODALAND INTERPRICES</t>
+          <t>SUPERMERCADO AAA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 27 Mins</t>
+          <t>00 Hrs 20 Mins</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>OBINNY FERRAGEM IITEGRATED</t>
+          <t>FEY YU IMPORT.EXPORT. LDA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 25 Mins</t>
+          <t>00 Hrs 19 Mins</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM PURE ON HEART</t>
+          <t>JUSTIN COMERCIAL, EI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 01 Mins</t>
+          <t>00 Hrs 22 Mins</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MOBILITY INVESTIMENTO, EI</t>
+          <t>FERRAGEM MACICAME</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 01 Mins</t>
+          <t>00 Hrs 35 Mins</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FERROX</t>
+          <t>FERRAGEM TANDAVATO EI</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 09 Mins</t>
+          <t>00 Hrs 13 Mins</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CHEER BEST DEVELOPMENT LDA</t>
+          <t>ATLANTICA STEEL LDA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 04 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>FERSOL</t>
+          <t>CUAMBA&amp;#039;S FERRAGEM, EI</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM AISHA</t>
+          <t>FERRAGEM GLORIOSO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 11 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>TINTAS BERGER MAPUTO OFFICE</t>
+          <t>P.T. COMERCIAL, EI</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>02 Hrs 30 Mins</t>
+          <t>00 Hrs 16 Mins</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MOZ INVESTIMENT &amp;amp; SERVICES, LDA</t>
+          <t>PAIZINHO COMERCIAL SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 13 Mins</t>
+          <t>00 Hrs 29 Mins</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>IFRESH, LDA</t>
+          <t>FERRAGEM DIMAS</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 22 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>HANANA STEELS, LDA</t>
+          <t>ABDUL SULTANE</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 04 Mins</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM AUTO J.J, LDA</t>
+          <t>NATVARLAL COMERCIAL EI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 18 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ABASEEN - SOC. UNIP. LDA</t>
+          <t>P.P. IMPORTACAO E EXPORTACAO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 10 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>SAIDATA ZALIA</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CHIBUKEN LIMITADA</t>
+          <t>RAGE COMERCIAL</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 12 Mins</t>
+          <t>00 Hrs 19 Mins</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>SAIDATA ZALIA</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM POSTOS SOC.UNIP. LDA</t>
+          <t>KHALID SU LDA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 12 Mins</t>
+          <t>00 Hrs 20 Mins</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>SAIDATA ZALIA</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ELECTRO FERRAGEM UNIVERSO,  E.I</t>
+          <t>KHALID SU LDA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 42 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>ARMANDO FERRAGEM, E.I</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 31 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGENS JALASAI</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 45 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>TINTAS E FERRAGENS, LDA</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>01 Hrs 07 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM GLORIOSO</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 18 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>UAMUSSE FERRANGEM</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 15 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>SAIDATA ZALIA</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>ALIN COMERCIAL</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>01 Hrs 17 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>SAIDATA ZALIA</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>AMAL COMERCIAL</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -76,16 +73,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -485,11 +482,11 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Used App</t>
+          <t>On Leave</t>
         </is>
       </c>
     </row>
@@ -500,7 +497,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -545,7 +542,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -560,7 +557,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -575,7 +572,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -806,7 +803,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="H2" s="4" t="inlineStr"/>
       <c r="I2" s="4" t="inlineStr"/>
       <c r="J2" s="4" t="inlineStr"/>
@@ -825,7 +826,7 @@
       <c r="W2" s="4" t="inlineStr"/>
       <c r="X2" s="4" t="inlineStr">
         <is>
-          <t>5/5 - Perfect attendance</t>
+          <t>5/6</t>
         </is>
       </c>
     </row>
@@ -860,7 +861,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr"/>
@@ -879,7 +884,7 @@
       <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr">
         <is>
-          <t>5/5 - Perfect attendance</t>
+          <t>6/6 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -914,7 +919,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H4" s="4" t="inlineStr"/>
       <c r="I4" s="4" t="inlineStr"/>
       <c r="J4" s="4" t="inlineStr"/>
@@ -933,7 +942,7 @@
       <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/6</t>
         </is>
       </c>
     </row>
@@ -968,7 +977,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr"/>
@@ -987,7 +1000,7 @@
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/6</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1035,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr"/>
       <c r="J6" s="4" t="inlineStr"/>
@@ -1041,7 +1058,7 @@
       <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>5/5 - Perfect attendance</t>
+          <t>6/6 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1093,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr"/>
@@ -1095,7 +1116,7 @@
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/6</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1151,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="4" t="inlineStr"/>
       <c r="J8" s="4" t="inlineStr"/>
@@ -1149,7 +1174,7 @@
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>5/5 - Perfect attendance</t>
+          <t>6/6 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1209,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr"/>
@@ -1203,7 +1232,7 @@
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/6</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1267,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H10" s="4" t="inlineStr"/>
       <c r="I10" s="4" t="inlineStr"/>
       <c r="J10" s="4" t="inlineStr"/>
@@ -1257,7 +1290,7 @@
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/6</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1368,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 4, 5, 6 (3 days)</t>
+          <t>No attendance on dates: 4, 5, 6, 9 (4 days)</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1438,29 +1471,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ELECTRO FERRAGEM MASTER SOLUTIONS</t>
+          <t>BEACH FRONT</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM PONTE, LDA</t>
+          <t>COWORK LAB</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1472,51 +1505,51 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>JOHNSON FERRAGENS. SOC. UNIP. LDA</t>
+          <t>CONDOMINIO</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 26 Mins</t>
+          <t>00 Hrs 13 Mins</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CONSTRUA BUILD IT</t>
+          <t>EDIFICIO GOLDEN SUN</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 26 Mins</t>
+          <t>00 Hrs 13 Mins</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM SABHA, LDA</t>
+          <t>FERRAGEM DIAMANTE</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 50 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
@@ -1528,97 +1561,97 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM AUTOCARIZ</t>
+          <t>FERRAGEM MAZIVE</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 19 Mins</t>
+          <t>00 Hrs 13 Mins</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>J COMO FERRAGEM</t>
+          <t>KULUN MATERIAL DE CONSTRUCAO, LIMITADA</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 17 Mins</t>
+          <t>03 Hrs 46 Mins</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM MONDWA</t>
+          <t>KAAFERR FERRAGEM</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 11 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM KHURULA</t>
+          <t>FERRAGEM CAMINHO DA OBRA, LDA</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 18 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ARTESÃO</t>
+          <t>ROMSHA TRADING, LDA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE BERTUR</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>RASHID COMERCIAL</t>
+          <t>JKAS COMERCIAL, LDA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 11 Mins</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1663,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>AKBAR FERRAGEM</t>
+          <t>FERRAGEM MUIZ, EI</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 11 Mins</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1680,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>AUTO FERRAGEM LAZARO COME</t>
+          <t>FARZANA SERVICES</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 01 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
@@ -1664,46 +1697,46 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM LIU</t>
+          <t>FERRAGEM AFRIPAK TRADING EI</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 03 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM CHAMISSAVA</t>
+          <t>FERRAGEM L.H.A</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 03 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM CAMINHO DA OBRA, LDA</t>
+          <t>FERROX</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1748,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CHEER BEST DEVELOPMENT LDA</t>
+          <t>FERRAGEM ASIA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
@@ -1732,29 +1765,29 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FERSOL</t>
+          <t>CASA CONSTRUCOES SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 26 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>G.F COMERCIAL</t>
+          <t>TINTAS BERGER MAPUTO OFFICE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 19 Mins</t>
+          <t>00 Hrs 55 Mins</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1799,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>TINTAS BERGER MAPUTO OFFICE</t>
+          <t>HANANA STEELS, LDA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 23 Mins</t>
+          <t>00 Hrs 16 Mins</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1816,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ALI, SOCIEDADE UNIPESSOAL, LIMITADA</t>
+          <t>CHIBUKEN LIMITADA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1800,12 +1833,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO AAA</t>
+          <t>FERRAGEM AUTO J.J, LDA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 20 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1850,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FEY YU IMPORT.EXPORT. LDA</t>
+          <t>IFRESH, LDA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 19 Mins</t>
+          <t>00 Hrs 20 Mins</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1867,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>JUSTIN COMERCIAL, EI</t>
+          <t>FERRAGEIRA SÃO JOSÉ</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 22 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1884,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM MACICAME</t>
+          <t>FERRAGEIRA SÃO JOSÉ</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 35 Mins</t>
+          <t>00 Hrs 26 Mins</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1901,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM TANDAVATO EI</t>
+          <t>NAWAZ TRADER, COMERCIAL. SOC. UNIP.LDA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 13 Mins</t>
+          <t>00 Hrs 03 Mins</t>
         </is>
       </c>
     </row>
@@ -1885,29 +1918,29 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ATLANTICA STEEL LDA</t>
+          <t>NELITO SIMANGO INVESTIMENTO, SU,LDA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CUAMBA&amp;#039;S FERRAGEM, EI</t>
+          <t>P.P. IMPORTACAO E EXPORTACAO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 18 Mins</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1952,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM GLORIOSO</t>
+          <t>LANGA COMERCIAL SOC UNP LDA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>01 Hrs 25 Mins</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1969,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>P.T. COMERCIAL, EI</t>
+          <t>TINTAS E FERRAGENS, LDA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 16 Mins</t>
+          <t>00 Hrs 18 Mins</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1986,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>PAIZINHO COMERCIAL SOC. UNIP. LDA</t>
+          <t>FERRAGENS JALASAI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 29 Mins</t>
+          <t>02 Hrs 19 Mins</t>
         </is>
       </c>
     </row>
@@ -1970,12 +2003,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM DIMAS</t>
+          <t>FERRAGEM UNIVERSAL</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
@@ -1987,12 +2020,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ABDUL SULTANE</t>
+          <t>ROYAL FERRAGEM SUCURSAL LDA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 04 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
@@ -2004,29 +2037,29 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>NATVARLAL COMERCIAL EI</t>
+          <t>FERRAGEM GUAMBE</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 18 Mins</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>SAIDATA ZALIA</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>P.P. IMPORTACAO E EXPORTACAO</t>
+          <t>KHALID SU LDA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
@@ -2038,46 +2071,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>RAGE COMERCIAL</t>
+          <t>EMCO LDA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 19 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>SAIDATA ZALIA</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>KHALID SU LDA</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 20 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>SAIDATA ZALIA</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>KHALID SU LDA</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 24 Mins</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>On Leave</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
@@ -512,11 +512,11 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Used App</t>
+          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Did Not Use App</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -808,7 +808,11 @@
           <t>L</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I2" s="4" t="inlineStr"/>
       <c r="J2" s="4" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr"/>
@@ -826,7 +830,7 @@
       <c r="W2" s="4" t="inlineStr"/>
       <c r="X2" s="4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
     </row>
@@ -866,7 +870,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr"/>
@@ -884,7 +892,7 @@
       <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr">
         <is>
-          <t>6/6 - Perfect attendance</t>
+          <t>7/7 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -924,7 +932,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I4" s="4" t="inlineStr"/>
       <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr"/>
@@ -942,7 +954,7 @@
       <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -982,7 +994,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr"/>
@@ -1000,7 +1016,7 @@
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/7</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1056,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I6" s="4" t="inlineStr"/>
       <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
@@ -1058,7 +1078,7 @@
       <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>6/6 - Perfect attendance</t>
+          <t>7/7 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1118,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr"/>
@@ -1116,7 +1140,7 @@
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1180,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I8" s="4" t="inlineStr"/>
       <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
@@ -1174,7 +1202,7 @@
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>6/6 - Perfect attendance</t>
+          <t>7/7 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1242,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr"/>
@@ -1232,7 +1264,7 @@
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1304,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I10" s="4" t="inlineStr"/>
       <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr"/>
@@ -1290,7 +1326,7 @@
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1392,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 2, 4 (2 days)</t>
+          <t>No attendance on dates: 2, 4, 10 (3 days)</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1471,182 +1507,182 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BEACH FRONT</t>
+          <t>FERRAGEM MUNHISSE MNISI, E.I</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 20 Mins</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>COWORK LAB</t>
+          <t>KUSHI MAPUTO LDA</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 10 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CONDOMINIO</t>
+          <t>MALABAR MATERIAL DE CONSTRUCAO SOCIEDADE UNIPESSOAL, LD</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 13 Mins</t>
+          <t>00 Hrs 25 Mins</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>EDIFICIO GOLDEN SUN</t>
+          <t>FERRAGEM KAMAL</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 13 Mins</t>
+          <t>00 Hrs 37 Mins</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM DIAMANTE</t>
+          <t>FERRAGEM COQUEIRO, LDA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 53 Mins</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM MAZIVE</t>
+          <t>KADI COMERCIAL</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 13 Mins</t>
+          <t>00 Hrs 36 Mins</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE BERTUR</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>KULUN MATERIAL DE CONSTRUCAO, LIMITADA</t>
+          <t>FERRAGEM ZINTAVA SOC UNP LDA</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>03 Hrs 46 Mins</t>
+          <t>01 Hrs 55 Mins</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>KAAFERR FERRAGEM</t>
+          <t>FERRAGEM ALEX UCUCHO87</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>00 Hrs 09 Mins</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM CAMINHO DA OBRA, LDA</t>
+          <t>FERRAGEM TREVO FAMILIA</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ROMSHA TRADING, LDA</t>
+          <t>MINI FERRAGEM NHANGUMBE</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>00 Hrs 13 Mins</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>JKAS COMERCIAL, LDA</t>
+          <t>AGOGO SUPERMEECADO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1658,80 +1694,80 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM MUIZ, EI</t>
+          <t>ZHI JUN</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 11 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>FARZANA SERVICES</t>
+          <t>FERRAGEM MICHAFUTENE</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 17 Mins</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM AFRIPAK TRADING EI</t>
+          <t>FORMEX MOZAMBIQUE, LIMITADA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 32 Mins</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM L.H.A</t>
+          <t>NEW HOTEL, LDA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FERROX</t>
+          <t>NOSSA FERRAGEM SOCIEDADE UNIPESSOAL LIMITADA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1743,340 +1779,646 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ASIA</t>
+          <t>BLUE OCEAN, LIMITADA ( SUCURSAL) NAMPULA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CASA CONSTRUCOES SOC. UNIP. LDA</t>
+          <t>ALI SHOP ,SOCIEDADE UNIPESSOAL, LIMITADA ( SUCURSAL)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>TINTAS BERGER MAPUTO OFFICE</t>
+          <t>ELECTRO FERRAGEIRA,LDA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 55 Mins</t>
+          <t>00 Hrs 14 Mins</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>HANANA STEELS, LDA</t>
+          <t>FERRAGEM LIU</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 16 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CHIBUKEN LIMITADA</t>
+          <t>ROMSHA TRADING, LDA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 24 Mins</t>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM AUTO J.J, LDA</t>
+          <t>FERRAGEM FATIMA, LDA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 12 Mins</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>IFRESH, LDA</t>
+          <t>FARZANA SERVICES</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 20 Mins</t>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEIRA SÃO JOSÉ</t>
+          <t>OUSAF INTERNATIONAL TRADING LDA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEIRA SÃO JOSÉ</t>
+          <t>INDO AFRICA COMERCIAL - ARMAZENS VITORIA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 26 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>NAWAZ TRADER, COMERCIAL. SOC. UNIP.LDA</t>
+          <t>FERRAGEM KULSOOM LDA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 03 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>NELITO SIMANGO INVESTIMENTO, SU,LDA</t>
+          <t>FERRAGEM AFRIPAK TRADING EI</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>P.P. IMPORTACAO E EXPORTACAO</t>
+          <t>GOD WIN FERRAGEM</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 18 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>LANGA COMERCIAL SOC UNP LDA</t>
+          <t>ARIMEK COMERCIAL EI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 25 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>TINTAS E FERRAGENS, LDA</t>
+          <t>HOTEL SENA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 18 Mins</t>
+          <t>00 Hrs 09 Mins</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>FERRAGENS JALASAI</t>
+          <t>ALEF ELETRO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>02 Hrs 19 Mins</t>
+          <t>00 Hrs 12 Mins</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM UNIVERSAL</t>
+          <t>FERRAGEM NOVA PODEROSA SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ROYAL FERRAGEM SUCURSAL LDA</t>
+          <t>BRIGHT</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>00 Hrs 03 Mins</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM GUAMBE</t>
+          <t>TINTAS BERGER MAPUTO OFFICE</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 18 Mins</t>
+          <t>01 Hrs 37 Mins</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SAIDATA ZALIA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>KHALID SU LDA</t>
+          <t>VIDRIOFER, LDA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 16 Mins</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>AF FERRAGEM E.I</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>TONY TINTAS</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>ELECTRO FERRAGEM UNIVERSO,  E.I</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 15 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>IR SERVIÇOS LIMITADA</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM AIYAKENE, SOCIEDADE UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 35 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM SERGIO E.I</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 20 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM MUHENGO, LDA</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 16 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>UAMUSSE FERRANGEM</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 05 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>KHAN FERRAGEM EI</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 16 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>FERRANGEM MAHUMANE</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>ECLIPSE COMERCIAL LDA</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 11 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>ELECTRO FERRAGEM DE CHOKWE LDA</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 28 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>COMPANHIA DONA CECILIA FERRAGEM</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 12 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>ELECTRO FERRAGEM NDZIMANE LDA</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 22 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>P.P. IMPORTACAO E EXPORTACAO</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 07 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>TINTAS E FERRAGENS, LDA</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 02 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
           <t>SAIDATA ZALIA</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>EMCO LDA</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 24 Mins</t>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>RAGE COMERCIAL</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 16 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM MAHAMUDO</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 28 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>ALIN COMERCIAL</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 18 Mins</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Used App</t>
+          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -813,7 +813,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J2" s="4" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr"/>
       <c r="L2" s="4" t="inlineStr"/>
@@ -830,7 +834,7 @@
       <c r="W2" s="4" t="inlineStr"/>
       <c r="X2" s="4" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/8</t>
         </is>
       </c>
     </row>
@@ -875,7 +879,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr"/>
       <c r="L3" s="4" t="inlineStr"/>
@@ -892,7 +900,7 @@
       <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr">
         <is>
-          <t>7/7 - Perfect attendance</t>
+          <t>8/8 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -937,7 +945,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="4" t="inlineStr"/>
@@ -954,7 +966,7 @@
       <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr">
         <is>
-          <t>4/7</t>
+          <t>4/8</t>
         </is>
       </c>
     </row>
@@ -999,7 +1011,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="4" t="inlineStr"/>
@@ -1016,7 +1032,7 @@
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>1/7</t>
+          <t>1/8</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1077,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr"/>
@@ -1078,7 +1098,7 @@
       <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>7/7 - Perfect attendance</t>
+          <t>8/8 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1143,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="4" t="inlineStr"/>
@@ -1140,7 +1164,7 @@
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/8</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1209,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="4" t="inlineStr"/>
@@ -1202,7 +1230,7 @@
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>7/7 - Perfect attendance</t>
+          <t>8/8 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1275,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="4" t="inlineStr"/>
@@ -1264,7 +1296,7 @@
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>6/8</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1341,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="4" t="inlineStr"/>
@@ -1326,7 +1362,7 @@
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>4/7</t>
+          <t>5/8</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1428,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 2, 4, 10 (3 days)</t>
+          <t>No attendance on dates: 2, 4, 10, 11 (4 days)</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1440,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 4, 5, 6, 9 (4 days)</t>
+          <t>No attendance on dates: 4, 5, 6, 9, 11 (5 days)</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1512,12 +1548,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM MUNHISSE MNISI, E.I</t>
+          <t>FERRAGEM PONTE, LDA</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 20 Mins</t>
+          <t>00 Hrs 48 Mins</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1565,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KUSHI MAPUTO LDA</t>
+          <t>MASSANGO PAINTS, EI</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 35 Mins</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1582,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>MALABAR MATERIAL DE CONSTRUCAO SOCIEDADE UNIPESSOAL, LD</t>
+          <t>FERRAGEM ACACIA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 25 Mins</t>
+          <t>00 Hrs 29 Mins</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1599,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM KAMAL</t>
+          <t>QUATRO ESTRELAS FERRAGENS</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 37 Mins</t>
+          <t>00 Hrs 21 Mins</t>
         </is>
       </c>
     </row>
@@ -1580,46 +1616,46 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM COQUEIRO, LDA</t>
+          <t>FERRAGEM DAS MAHOTAS,LDA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 53 Mins</t>
+          <t>01 Hrs 26 Mins</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>KADI COMERCIAL</t>
+          <t>FERRAGEM CAPANE</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 36 Mins</t>
+          <t>00 Hrs 14 Mins</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ZINTAVA SOC UNP LDA</t>
+          <t>FERRAGEM XINGOMANE</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 55 Mins</t>
+          <t>00 Hrs 12 Mins</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1667,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ALEX UCUCHO87</t>
+          <t>FERRAGEM TUZINE E FILHOS SERVICOS, LDA</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1643,782 +1679,442 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM TREVO FAMILIA</t>
+          <t>J. ELECTRO FERRAGEM SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 04 Mins</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MINI FERRAGEM NHANGUMBE</t>
+          <t>BLESSED MIKO IMPORT AND EXPORT, EI</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 13 Mins</t>
+          <t>00 Hrs 20 Mins</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>AGOGO SUPERMEECADO</t>
+          <t>MT COMERCIAL, E.I</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 11 Mins</t>
+          <t>00 Hrs 13 Mins</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ZHI JUN</t>
+          <t>FERRAGEM PURE ON HEART</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 19 Mins</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM MICHAFUTENE</t>
+          <t>FERRAGEM AFRIPAK TRADING EI</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 17 Mins</t>
+          <t>03 Hrs 25 Mins</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>FORMEX MOZAMBIQUE, LIMITADA</t>
+          <t>MODALAND INTERPRICES</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 32 Mins</t>
+          <t>00 Hrs 03 Mins</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>NEW HOTEL, LDA</t>
+          <t>FERROX</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>NOSSA FERRAGEM SOCIEDADE UNIPESSOAL LIMITADA</t>
+          <t>SOCOL S9FALA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>BLUE OCEAN, LIMITADA ( SUCURSAL) NAMPULA</t>
+          <t>FERSOL</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 25 Mins</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ALI SHOP ,SOCIEDADE UNIPESSOAL, LIMITADA ( SUCURSAL)</t>
+          <t>FERRAGEM SOFALA, LDA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 51 Mins</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ELECTRO FERRAGEIRA,LDA</t>
+          <t>FERRAGEM SOFALA, LDA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>00 Hrs 13 Mins</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM LIU</t>
+          <t>TINTAS BERGER MAPUTO OFFICE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 30 Mins</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ROMSHA TRADING, LDA</t>
+          <t>FERRAGEM MUHENGO, LDA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 10 Mins</t>
+          <t>00 Hrs 22 Mins</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM FATIMA, LDA</t>
+          <t>FERRAGEM SERGIO E.I</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 12 Mins</t>
+          <t>01 Hrs 25 Mins</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FARZANA SERVICES</t>
+          <t>VIDRIOFER, LDA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 10 Mins</t>
+          <t>00 Hrs 11 Mins</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>OUSAF INTERNATIONAL TRADING LDA</t>
+          <t>SOHA TRADING. SOC. UNIP</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>INDO AFRICA COMERCIAL - ARMAZENS VITORIA</t>
+          <t>TUBOS DE ÁGUA &amp;amp; SERVIÇO,  LIMITADA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>01 Hrs 09 Mins</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM KULSOOM LDA</t>
+          <t>UAMUSSE FERRANGEM</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>01 Hrs 18 Mins</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM AFRIPAK TRADING EI</t>
+          <t>ROYAL FERRAGEM SUCURSAL LDA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 02 Mins</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GOD WIN FERRAGEM</t>
+          <t>TINTAS E FERRAGENS, LDA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 42 Mins</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ARIMEK COMERCIAL EI</t>
+          <t>LANGA COMERCIAL SOC UNP LDA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>00 Hrs 21 Mins</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>HOTEL SENA</t>
+          <t>P.P. IMPORTACAO E EXPORTACAO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 09 Mins</t>
+          <t>03 Hrs 03 Mins</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ALEF ELETRO</t>
+          <t>FERRAGENS JALASAI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 12 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM NOVA PODEROSA SOC. UNIP. LDA</t>
+          <t>FERRAGEM UNIVERSAL</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 02 Mins</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>BRIGHT</t>
+          <t>FERRAGEM GLORIOSO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 03 Mins</t>
+          <t>00 Hrs 19 Mins</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>SAIDATA ZALIA</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>TINTAS BERGER MAPUTO OFFICE</t>
+          <t>CENTRO DE FERRAGEM</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 37 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>VIDRIOFER, LDA</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 16 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>AF FERRAGEM E.I</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 00 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>TONY TINTAS</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 00 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>ELECTRO FERRAGEM UNIVERSO,  E.I</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 15 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>IR SERVIÇOS LIMITADA</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 00 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM AIYAKENE, SOCIEDADE UNIPESSOAL, LDA</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 35 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM SERGIO E.I</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 20 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM MUHENGO, LDA</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 16 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>UAMUSSE FERRANGEM</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 05 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>KHAN FERRAGEM EI</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 16 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>FERRANGEM MAHUMANE</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 00 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>ECLIPSE COMERCIAL LDA</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 11 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>ELECTRO FERRAGEM DE CHOKWE LDA</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 28 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>COMPANHIA DONA CECILIA FERRAGEM</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 12 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>ELECTRO FERRAGEM NDZIMANE LDA</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 22 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>P.P. IMPORTACAO E EXPORTACAO</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 07 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>TINTAS E FERRAGENS, LDA</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 02 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>SAIDATA ZALIA</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>RAGE COMERCIAL</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 16 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>SAIDATA ZALIA</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM MAHAMUDO</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 28 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>SAIDATA ZALIA</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>ALIN COMERCIAL</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 18 Mins</t>
+          <t>00 Hrs 23 Mins</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Day Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Attendance Grid - March" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Monthly Attendance - March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Day Visits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attendance Grid - March" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Attendance - March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day Visits" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -73,16 +76,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -482,7 +485,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -497,7 +500,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -512,11 +515,11 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Did Not Use App</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
@@ -527,11 +530,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Did Not Use App</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
@@ -557,7 +560,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -572,7 +575,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -587,7 +590,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -602,7 +605,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -818,7 +821,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K2" s="4" t="inlineStr"/>
       <c r="L2" s="4" t="inlineStr"/>
       <c r="M2" s="4" t="inlineStr"/>
@@ -834,7 +841,7 @@
       <c r="W2" s="4" t="inlineStr"/>
       <c r="X2" s="4" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>8/9</t>
         </is>
       </c>
     </row>
@@ -884,7 +891,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K3" s="4" t="inlineStr"/>
       <c r="L3" s="4" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr"/>
@@ -900,7 +911,7 @@
       <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr">
         <is>
-          <t>8/8 - Perfect attendance</t>
+          <t>9/9 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -950,7 +961,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="4" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr"/>
@@ -966,7 +981,7 @@
       <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>5/9</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1031,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="4" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr"/>
@@ -1032,7 +1051,7 @@
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>2/9</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1101,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr"/>
@@ -1098,7 +1121,7 @@
       <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>8/8 - Perfect attendance</t>
+          <t>9/9 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1171,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="4" t="inlineStr"/>
       <c r="M7" s="4" t="inlineStr"/>
@@ -1164,7 +1191,7 @@
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>8/9</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1241,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="4" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr"/>
@@ -1230,7 +1261,7 @@
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>8/8 - Perfect attendance</t>
+          <t>9/9 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1311,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="4" t="inlineStr"/>
       <c r="M9" s="4" t="inlineStr"/>
@@ -1296,7 +1331,7 @@
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>7/9</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1381,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="4" t="inlineStr"/>
       <c r="M10" s="4" t="inlineStr"/>
@@ -1362,7 +1401,7 @@
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>6/9</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1548,12 +1587,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM PONTE, LDA</t>
+          <t>SUPERMERCADO DO RIO VERDE, SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 48 Mins</t>
+          <t>01 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1604,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MASSANGO PAINTS, EI</t>
+          <t>KHENSANY FERRAGEM, LDA</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 35 Mins</t>
+          <t>01 Hrs 02 Mins</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1621,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ACACIA</t>
+          <t>KHENSANY FERRAGEM, LDA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 29 Mins</t>
+          <t>01 Hrs 02 Mins</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1638,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>QUATRO ESTRELAS FERRAGENS</t>
+          <t>R.V ELECTRO FERRAGEM LDA</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 21 Mins</t>
+          <t>00 Hrs 18 Mins</t>
         </is>
       </c>
     </row>
@@ -1616,194 +1655,194 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM DAS MAHOTAS,LDA</t>
+          <t>FERRAGEM NHAMPIMBE, EI</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 26 Mins</t>
+          <t>00 Hrs 16 Mins</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM CAPANE</t>
+          <t>TELLES COMERCIO &amp;amp; SERVICOS, LDA.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>00 Hrs 27 Mins</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM XINGOMANE</t>
+          <t>UNIAO COMERCIAL ZANDA</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 12 Mins</t>
+          <t>00 Hrs 24 Mins</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM TUZINE E FILHOS SERVICOS, LDA</t>
+          <t>CONSTRUA BUILD IT</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 09 Mins</t>
+          <t>00 Hrs 57 Mins</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>J. ELECTRO FERRAGEM SOC. UNIP. LDA</t>
+          <t>FERRAGEM KA MUCHINA</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 04 Mins</t>
+          <t>00 Hrs 13 Mins</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>BLESSED MIKO IMPORT AND EXPORT, EI</t>
+          <t>ELETRO FERRAGEM DIAMOND</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 20 Mins</t>
+          <t>00 Hrs 02 Mins</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MT COMERCIAL, E.I</t>
+          <t>ELETRO FERRAGEM DIAMOND</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 13 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM PURE ON HEART</t>
+          <t>FERRAGEM DOMINGOS MOMBE</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 19 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM AFRIPAK TRADING EI</t>
+          <t>FERRAGEM NGONHAMA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>03 Hrs 25 Mins</t>
+          <t>00 Hrs 13 Mins</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>MODALAND INTERPRICES</t>
+          <t>FERRAGEM NAIMITO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 03 Mins</t>
+          <t>00 Hrs 13 Mins</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FERROX</t>
+          <t>FERRAGEM MUTCHATAZINA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 04 Mins</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SOCOL S9FALA</t>
+          <t>ELECTRO FERRAGEIRA,LDA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1815,306 +1854,527 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FERSOL</t>
+          <t>NEW HOTEL, LDA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 25 Mins</t>
+          <t>00 Hrs 11 Mins</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM SOFALA, LDA</t>
+          <t>NOSSA FERRAGEM SOCIEDADE UNIPESSOAL LIMITADA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 51 Mins</t>
+          <t>00 Hrs 09 Mins</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM SOFALA, LDA</t>
+          <t>HANANA STEELS, LDA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 13 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>TINTAS BERGER MAPUTO OFFICE</t>
+          <t>SIAL KINGDOM SUCURAL</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 30 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM MUHENGO, LDA</t>
+          <t>BLUE OCEAN, LIMITADA ( SUCURSAL) NAMPULA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 22 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM SERGIO E.I</t>
+          <t>FERRAGEM MUIZ, EI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 25 Mins</t>
+          <t>00 Hrs 11 Mins</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>VIDRIOFER, LDA</t>
+          <t>ELECTRO FERRAGEM REAL</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 11 Mins</t>
+          <t>00 Hrs 04 Mins</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SOHA TRADING. SOC. UNIP</t>
+          <t>MACOMAT MAT. CONSTRUCAO DE MOC.</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 03 Mins</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TUBOS DE ÁGUA &amp;amp; SERVIÇO,  LIMITADA</t>
+          <t>M.S.S FERRAGEM</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 09 Mins</t>
+          <t>00 Hrs 18 Mins</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>UAMUSSE FERRANGEM</t>
+          <t>FERRAGEM PURE ON HEART</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 18 Mins</t>
+          <t>00 Hrs 02 Mins</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ROYAL FERRAGEM SUCURSAL LDA</t>
+          <t>ESTEVÃO BAPTISTA MUGUAMBE AUTO FERRAGEM</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 02 Mins</t>
+          <t>01 Hrs 37 Mins</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>TINTAS E FERRAGENS, LDA</t>
+          <t>G.F COMERCIAL</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 42 Mins</t>
+          <t>00 Hrs 54 Mins</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>LANGA COMERCIAL SOC UNP LDA</t>
+          <t>FERRAGEM L.H.A</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 21 Mins</t>
+          <t>00 Hrs 28 Mins</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>P.P. IMPORTACAO E EXPORTACAO</t>
+          <t>SOCOL S9FALA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>03 Hrs 03 Mins</t>
+          <t>00 Hrs 20 Mins</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>FERRAGENS JALASAI</t>
+          <t>TINTAS BERGER MAPUTO OFFICE</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>01 Hrs 27 Mins</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM UNIVERSAL</t>
+          <t>NAWAZ TRADER, COMERCIAL. SOC. UNIP.LDA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 02 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM GLORIOSO</t>
+          <t>FERRAGEM ARIF</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 19 Mins</t>
+          <t>00 Hrs 01 Mins</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>KHAN FERRAGEM ELECTRICO, LDA</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>CHIBUKEN LIMITADA</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 18 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM ABASEEN - SOC. UNIP. LDA</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 22 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM AUTO J.J, LDA</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 29 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>STEEL TRADE, LDA</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>CUAMBA&amp;#039;S FERRAGEM, EI</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>UAMUSSE FERRANGEM</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 56 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>ROYAL FERRAGEM SUCURSAL LDA</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>02 Hrs 07 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>ABDUL SULTANE</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 16 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>NATVARLAL COMERCIAL EI</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 12 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM GUAMBE</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 09 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>P.P. IMPORTACAO E EXPORTACAO</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
           <t>SAIDATA ZALIA</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>AMAL COMERCIAL</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 23 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>CENTRO DE FERRAGEM</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 23 Mins</t>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -512,11 +512,11 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Did Not Use App</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Did Not Use App</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -602,11 +602,11 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Used App</t>
+          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
@@ -818,8 +818,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L2" s="4" t="inlineStr"/>
       <c r="M2" s="4" t="inlineStr"/>
       <c r="N2" s="4" t="inlineStr"/>
@@ -834,7 +842,7 @@
       <c r="W2" s="4" t="inlineStr"/>
       <c r="X2" s="4" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -884,8 +892,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L3" s="4" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr"/>
       <c r="N3" s="4" t="inlineStr"/>
@@ -900,7 +916,7 @@
       <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr">
         <is>
-          <t>8/8 - Perfect attendance</t>
+          <t>10/10 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -950,8 +966,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L4" s="4" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr"/>
       <c r="N4" s="4" t="inlineStr"/>
@@ -966,7 +990,7 @@
       <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1016,8 +1040,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L5" s="4" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr"/>
       <c r="N5" s="4" t="inlineStr"/>
@@ -1032,7 +1064,7 @@
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -1082,8 +1114,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L6" s="4" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr"/>
       <c r="N6" s="4" t="inlineStr"/>
@@ -1098,7 +1138,7 @@
       <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>8/8 - Perfect attendance</t>
+          <t>10/10 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1148,8 +1188,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L7" s="4" t="inlineStr"/>
       <c r="M7" s="4" t="inlineStr"/>
       <c r="N7" s="4" t="inlineStr"/>
@@ -1164,7 +1212,7 @@
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -1214,8 +1262,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L8" s="4" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr"/>
       <c r="N8" s="4" t="inlineStr"/>
@@ -1230,7 +1286,7 @@
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>8/8 - Perfect attendance</t>
+          <t>10/10 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1280,8 +1336,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L9" s="4" t="inlineStr"/>
       <c r="M9" s="4" t="inlineStr"/>
       <c r="N9" s="4" t="inlineStr"/>
@@ -1296,7 +1360,7 @@
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -1346,8 +1410,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="L10" s="4" t="inlineStr"/>
       <c r="M10" s="4" t="inlineStr"/>
       <c r="N10" s="4" t="inlineStr"/>
@@ -1362,7 +1434,7 @@
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1572,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 2, 3, 4 (3 days)</t>
+          <t>No attendance on dates: 2, 3, 4, 13 (4 days)</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1548,12 +1620,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM PONTE, LDA</t>
+          <t>CHINA MALL, LDA</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 48 Mins</t>
+          <t>00 Hrs 34 Mins</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1637,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MASSANGO PAINTS, EI</t>
+          <t>NOVO MOZ TRADING</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 35 Mins</t>
+          <t>00 Hrs 31 Mins</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1654,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ACACIA</t>
+          <t>FERRAGEM EBENEZER</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 29 Mins</t>
+          <t>00 Hrs 30 Mins</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1671,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>QUATRO ESTRELAS FERRAGENS</t>
+          <t>FERRAGEM CHOUPAL</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 21 Mins</t>
+          <t>00 Hrs 23 Mins</t>
         </is>
       </c>
     </row>
@@ -1616,29 +1688,29 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM DAS MAHOTAS,LDA</t>
+          <t>FRANCIS FERRAGEM SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 26 Mins</t>
+          <t>00 Hrs 26 Mins</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM CAPANE</t>
+          <t>FERRAGEM SABHA, LDA</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>00 Hrs 18 Mins</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1722,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM XINGOMANE</t>
+          <t>LASO MOCAMBIQUE</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 12 Mins</t>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>
@@ -1667,454 +1739,624 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM TUZINE E FILHOS SERVICOS, LDA</t>
+          <t>FERRAGEM FORTALEZA</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 09 Mins</t>
+          <t>00 Hrs 16 Mins</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>J. ELECTRO FERRAGEM SOC. UNIP. LDA</t>
+          <t>SSR TRADING</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 04 Mins</t>
+          <t>00 Hrs 14 Mins</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>BLESSED MIKO IMPORT AND EXPORT, EI</t>
+          <t>GODS PLAN</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 20 Mins</t>
+          <t>00 Hrs 16 Mins</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MT COMERCIAL, E.I</t>
+          <t>FERRAGEM WATE</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 13 Mins</t>
+          <t>00 Hrs 09 Mins</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM PURE ON HEART</t>
+          <t>CHOSENS ELETRO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 19 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM AFRIPAK TRADING EI</t>
+          <t>EC FERRAGEM E.I</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>03 Hrs 25 Mins</t>
+          <t>01 Hrs 25 Mins</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>MODALAND INTERPRICES</t>
+          <t>KULUN MATERIAL DE CONSTRUCAO, LIMITADA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 03 Mins</t>
+          <t>00 Hrs 20 Mins</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FERROX</t>
+          <t>BLUE OCEAN, LIMITADA ( SUCURSAL) NAMPULA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>01 Hrs 01 Mins</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SOCOL S9FALA</t>
+          <t>FORMEX MOZAMBIQUE, LIMITADA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FERSOL</t>
+          <t>ELECTRO FERRAGEIRA,LDA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 25 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM SOFALA, LDA</t>
+          <t>NOSSA FERRAGEM SOCIEDADE UNIPESSOAL LIMITADA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 51 Mins</t>
+          <t>01 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM SOFALA, LDA</t>
+          <t>ESTEVÃO BAPTISTA MUGUAMBE AUTO FERRAGEM</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 13 Mins</t>
+          <t>00 Hrs 19 Mins</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>TINTAS BERGER MAPUTO OFFICE</t>
+          <t>FERRAGEM PURE ON HEART</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 30 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM MUHENGO, LDA</t>
+          <t>FARZANA SERVICES</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 22 Mins</t>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM SERGIO E.I</t>
+          <t>GHORI COMERCIAL, EI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 25 Mins</t>
+          <t>00 Hrs 01 Mins</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>VIDRIOFER, LDA</t>
+          <t>GHORI COMERCIAL, EI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 11 Mins</t>
+          <t>00 Hrs 04 Mins</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SOHA TRADING. SOC. UNIP</t>
+          <t>FERRAGEM NOVA PODEROSA SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 14 Mins</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TUBOS DE ÁGUA &amp;amp; SERVIÇO,  LIMITADA</t>
+          <t>MAHAM COMERCIAL</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 09 Mins</t>
+          <t>00 Hrs 37 Mins</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>UAMUSSE FERRANGEM</t>
+          <t>SOCOL S9FALA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 18 Mins</t>
+          <t>00 Hrs 21 Mins</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ROYAL FERRAGEM SUCURSAL LDA</t>
+          <t>TINTAS BERGER MAPUTO OFFICE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 02 Mins</t>
+          <t>01 Hrs 13 Mins</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>TINTAS E FERRAGENS, LDA</t>
+          <t>MOZAMBIQUE OASIS, LDA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 42 Mins</t>
+          <t>00 Hrs 22 Mins</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>LANGA COMERCIAL SOC UNP LDA</t>
+          <t>FERRAGEM CASA DA AMIZADE, EI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 21 Mins</t>
+          <t>00 Hrs 20 Mins</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>P.P. IMPORTACAO E EXPORTACAO</t>
+          <t>NELITO SIMANGO INVESTIMENTO, SU,LDA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>03 Hrs 03 Mins</t>
+          <t>00 Hrs 14 Mins</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>FERRAGENS JALASAI</t>
+          <t>SUPERMERCADO AAA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM UNIVERSAL</t>
+          <t>IFRESH, LDA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 02 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM GLORIOSO</t>
+          <t>FERRAGEM MUHENGO, LDA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 19 Mins</t>
+          <t>00 Hrs 52 Mins</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>SAIDATA ZALIA</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CENTRO DE FERRAGEM</t>
+          <t>FERRAGEM SERGIO E.I</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 23 Mins</t>
+          <t>00 Hrs 32 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>PAK-MOZ FERRAGEM</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>PATEL FERRAGEM, EI</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>MAGUENGUE AUTO-PAINTS</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 39 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>ROYAL FERRAGEM SUCURSAL LDA</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 09 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM UNIVERSAL</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 11 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>P.P. IMPORTACAO E EXPORTACAO</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 10 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>LANGA COMERCIAL SOC UNP LDA</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 04 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM SAMANTHA</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 04 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>LANGA COMERCIAL SOC UNP LDA</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 07 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO MACUACUA</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>TINTAS E FERRAGENS, LDA</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 01 Mins</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -497,11 +497,11 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Used App</t>
+          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -602,11 +602,11 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Did Not Use App</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr"/>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M2" s="4" t="inlineStr"/>
       <c r="N2" s="4" t="inlineStr"/>
       <c r="O2" s="4" t="inlineStr"/>
@@ -842,7 +846,7 @@
       <c r="W2" s="4" t="inlineStr"/>
       <c r="X2" s="4" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -902,7 +906,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M3" s="4" t="inlineStr"/>
       <c r="N3" s="4" t="inlineStr"/>
       <c r="O3" s="4" t="inlineStr"/>
@@ -916,7 +924,7 @@
       <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr">
         <is>
-          <t>10/10 - Perfect attendance</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -976,7 +984,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M4" s="4" t="inlineStr"/>
       <c r="N4" s="4" t="inlineStr"/>
       <c r="O4" s="4" t="inlineStr"/>
@@ -990,7 +1002,7 @@
       <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1062,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M5" s="4" t="inlineStr"/>
       <c r="N5" s="4" t="inlineStr"/>
       <c r="O5" s="4" t="inlineStr"/>
@@ -1064,7 +1080,7 @@
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1140,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M6" s="4" t="inlineStr"/>
       <c r="N6" s="4" t="inlineStr"/>
       <c r="O6" s="4" t="inlineStr"/>
@@ -1138,7 +1158,7 @@
       <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>10/10 - Perfect attendance</t>
+          <t>11/11 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1218,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M7" s="4" t="inlineStr"/>
       <c r="N7" s="4" t="inlineStr"/>
       <c r="O7" s="4" t="inlineStr"/>
@@ -1212,7 +1236,7 @@
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1296,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M8" s="4" t="inlineStr"/>
       <c r="N8" s="4" t="inlineStr"/>
       <c r="O8" s="4" t="inlineStr"/>
@@ -1286,7 +1314,7 @@
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>10/10 - Perfect attendance</t>
+          <t>11/11 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1374,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M9" s="4" t="inlineStr"/>
       <c r="N9" s="4" t="inlineStr"/>
       <c r="O9" s="4" t="inlineStr"/>
@@ -1360,7 +1392,7 @@
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1452,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M10" s="4" t="inlineStr"/>
       <c r="N10" s="4" t="inlineStr"/>
       <c r="O10" s="4" t="inlineStr"/>
@@ -1434,7 +1470,7 @@
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1524,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Perfect attendance</t>
+          <t>No attendance on date: 16</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1620,12 +1656,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CHINA MALL, LDA</t>
+          <t>ZANG FERRAGEM</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 34 Mins</t>
+          <t>00 Hrs 23 Mins</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1673,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>NOVO MOZ TRADING</t>
+          <t>ELECTRO FERRAGEM AFRICA, LDA</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 31 Mins</t>
+          <t>00 Hrs 33 Mins</t>
         </is>
       </c>
     </row>
@@ -1654,12 +1690,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM EBENEZER</t>
+          <t>FERRAGEM VAVA, EI</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 30 Mins</t>
+          <t>00 Hrs 32 Mins</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1707,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM CHOUPAL</t>
+          <t>JOHNSON FERRAGENS. SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 23 Mins</t>
+          <t>00 Hrs 42 Mins</t>
         </is>
       </c>
     </row>
@@ -1688,12 +1724,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FRANCIS FERRAGEM SOC. UNIP. LDA</t>
+          <t>ELECTRO FERRAGEM MASTER SOLUTIONS</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 26 Mins</t>
+          <t>00 Hrs 22 Mins</t>
         </is>
       </c>
     </row>
@@ -1705,352 +1741,352 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM SABHA, LDA</t>
+          <t>FERRAGEM KAMAL</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 18 Mins</t>
+          <t>00 Hrs 28 Mins</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>LASO MOCAMBIQUE</t>
+          <t>FERCON</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 10 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM FORTALEZA</t>
+          <t>FORMEX MOZAMBIQUE, LIMITADA</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 16 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SSR TRADING</t>
+          <t>BLUE OCEAN, LIMITADA ( SUCURSAL) NAMPULA</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>00 Hrs 09 Mins</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>GODS PLAN</t>
+          <t>FERRAGEM ALAR,LDA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 16 Mins</t>
+          <t>00 Hrs 14 Mins</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM WATE</t>
+          <t>ELECTRO FERRAGEIRA,LDA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 09 Mins</t>
+          <t>00 Hrs 16 Mins</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CHOSENS ELETRO</t>
+          <t>NEW HOTEL, LDA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 04 Mins</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>EC FERRAGEM E.I</t>
+          <t>ALI SHOP ,SOCIEDADE UNIPESSOAL, LIMITADA ( SUCURSAL)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 25 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE BERTUR</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>KULUN MATERIAL DE CONSTRUCAO, LIMITADA</t>
+          <t>FERRAGEM JAIME ELIAS MABOXE</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 20 Mins</t>
+          <t>00 Hrs 11 Mins</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BLUE OCEAN, LIMITADA ( SUCURSAL) NAMPULA</t>
+          <t>FERRAGEM MUIZ, EI</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 01 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FORMEX MOZAMBIQUE, LIMITADA</t>
+          <t>FERRAGEM CAMINHO DA OBRA, LDA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ELECTRO FERRAGEIRA,LDA</t>
+          <t>FERRAGEM AFRIPAK TRADING EI</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>NOSSA FERRAGEM SOCIEDADE UNIPESSOAL LIMITADA</t>
+          <t>FERRAGEM AUTO GEMO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 15 Mins</t>
+          <t>00 Hrs 02 Mins</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ESTEVÃO BAPTISTA MUGUAMBE AUTO FERRAGEM</t>
+          <t>FERROX</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 19 Mins</t>
+          <t>00 Hrs 04 Mins</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM PURE ON HEART</t>
+          <t>MUTARARA FERRAGEM</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 16 Mins</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FARZANA SERVICES</t>
+          <t>FERRAGEM ASIA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 10 Mins</t>
+          <t>00 Hrs 11 Mins</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GHORI COMERCIAL, EI</t>
+          <t>UZAMBIANE FERRAGENS LDA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 01 Mins</t>
+          <t>00 Hrs 20 Mins</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GHORI COMERCIAL, EI</t>
+          <t>CENTRAL GRAFICA, LDA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 04 Mins</t>
+          <t>00 Hrs 20 Mins</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM NOVA PODEROSA SOC. UNIP. LDA</t>
+          <t>PATEL FERRAGEM, EI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>00 Hrs 02 Mins</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MAHAM COMERCIAL</t>
+          <t>CUAMBA&amp;#039;S FERRAGEM, EI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 37 Mins</t>
+          <t>00 Hrs 00 Mins</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SOCOL S9FALA</t>
+          <t>ELECTRO FERRAGEM MATOLA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 21 Mins</t>
+          <t>00 Hrs 34 Mins</t>
         </is>
       </c>
     </row>
@@ -2062,301 +2098,80 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>TINTAS BERGER MAPUTO OFFICE</t>
+          <t>ARMANDO FERRAGEM, E.I</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 13 Mins</t>
+          <t>01 Hrs 32 Mins</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MOZAMBIQUE OASIS, LDA</t>
+          <t>UAMUSSE FERRANGEM</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 22 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>RICARDO MACUACUA</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM CASA DA AMIZADE, EI</t>
+          <t>MAGUENGUE AUTO-PAINTS</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 20 Mins</t>
+          <t>01 Hrs 43 Mins</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>SAIDATA ZALIA</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>NELITO SIMANGO INVESTIMENTO, SU,LDA</t>
+          <t>EMCO LDA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>00 Hrs 09 Mins</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>SAIDATA ZALIA</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO AAA</t>
+          <t>AMAL COMERCIAL</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>IFRESH, LDA</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 00 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM MUHENGO, LDA</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 52 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM SERGIO E.I</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 32 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>PAK-MOZ FERRAGEM</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 00 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>PATEL FERRAGEM, EI</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 00 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>MAGUENGUE AUTO-PAINTS</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 39 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>ROYAL FERRAGEM SUCURSAL LDA</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
           <t>00 Hrs 09 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM UNIVERSAL</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 11 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>P.P. IMPORTACAO E EXPORTACAO</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 10 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>LANGA COMERCIAL SOC UNP LDA</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 04 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM SAMANTHA</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 04 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>LANGA COMERCIAL SOC UNP LDA</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 07 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>TINTAS E FERRAGENS, LDA</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 01 Mins</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Day Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Attendance Grid - March" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Monthly Attendance - March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Day Visits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attendance Grid - March" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Attendance - March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day Visits" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -73,16 +76,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -482,7 +485,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -497,11 +500,11 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Did Not Use App</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
@@ -512,11 +515,11 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Used App</t>
+          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
@@ -527,7 +530,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -542,7 +545,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -557,7 +560,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -572,7 +575,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -587,11 +590,11 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Used App</t>
+          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
@@ -602,7 +605,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -833,8 +836,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O2" s="4" t="inlineStr"/>
       <c r="P2" s="4" t="inlineStr"/>
       <c r="Q2" s="4" t="inlineStr"/>
@@ -846,7 +857,7 @@
       <c r="W2" s="4" t="inlineStr"/>
       <c r="X2" s="4" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -911,8 +922,16 @@
           <t>X</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O3" s="4" t="inlineStr"/>
       <c r="P3" s="4" t="inlineStr"/>
       <c r="Q3" s="4" t="inlineStr"/>
@@ -924,7 +943,7 @@
       <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -989,8 +1008,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="O4" s="4" t="inlineStr"/>
       <c r="P4" s="4" t="inlineStr"/>
       <c r="Q4" s="4" t="inlineStr"/>
@@ -1002,7 +1029,7 @@
       <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1067,8 +1094,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O5" s="4" t="inlineStr"/>
       <c r="P5" s="4" t="inlineStr"/>
       <c r="Q5" s="4" t="inlineStr"/>
@@ -1080,7 +1115,7 @@
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1145,8 +1180,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O6" s="4" t="inlineStr"/>
       <c r="P6" s="4" t="inlineStr"/>
       <c r="Q6" s="4" t="inlineStr"/>
@@ -1158,7 +1201,7 @@
       <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>11/11 - Perfect attendance</t>
+          <t>13/13 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1223,8 +1266,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O7" s="4" t="inlineStr"/>
       <c r="P7" s="4" t="inlineStr"/>
       <c r="Q7" s="4" t="inlineStr"/>
@@ -1236,7 +1287,7 @@
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -1301,8 +1352,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O8" s="4" t="inlineStr"/>
       <c r="P8" s="4" t="inlineStr"/>
       <c r="Q8" s="4" t="inlineStr"/>
@@ -1314,7 +1373,7 @@
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>11/11 - Perfect attendance</t>
+          <t>13/13 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1379,8 +1438,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="O9" s="4" t="inlineStr"/>
       <c r="P9" s="4" t="inlineStr"/>
       <c r="Q9" s="4" t="inlineStr"/>
@@ -1392,7 +1459,7 @@
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1457,8 +1524,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O10" s="4" t="inlineStr"/>
       <c r="P10" s="4" t="inlineStr"/>
       <c r="Q10" s="4" t="inlineStr"/>
@@ -1470,7 +1545,7 @@
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1611,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 2, 4, 10, 11 (4 days)</t>
+          <t>No attendance on dates: 2, 4, 10, 11, 18 (5 days)</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1671,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 2, 3 (2 days)</t>
+          <t>No attendance on dates: 2, 3, 18 (3 days)</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1656,12 +1731,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ZANG FERRAGEM</t>
+          <t>MALABAR MATERIAL DE CONSTRUCAO SOCIEDADE UNIPESSOAL, LD</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 23 Mins</t>
+          <t>00 Hrs 28 Mins</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1748,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ELECTRO FERRAGEM AFRICA, LDA</t>
+          <t>FERRAGEM SABHA, LDA</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 33 Mins</t>
+          <t>00 Hrs 35 Mins</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1765,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM VAVA, EI</t>
+          <t>FERRAGEM MAHNOOR</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 32 Mins</t>
+          <t>00 Hrs 46 Mins</t>
         </is>
       </c>
     </row>
@@ -1707,12 +1782,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>JOHNSON FERRAGENS. SOC. UNIP. LDA</t>
+          <t>FUXIN MATERIAL DE CONSTRUCAO TRADING, LDA</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 42 Mins</t>
+          <t>00 Hrs 30 Mins</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1799,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ELECTRO FERRAGEM MASTER SOLUTIONS</t>
+          <t>FERRAGEM ACACIA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 22 Mins</t>
+          <t>01 Hrs 02 Mins</t>
         </is>
       </c>
     </row>
@@ -1741,24 +1816,24 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM KAMAL</t>
+          <t>FERRAGEM ZINTAVA SOC UNP LDA</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 28 Mins</t>
+          <t>00 Hrs 45 Mins</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE BERTUR</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>FERCON</t>
+          <t>R.V ELECTRO FERRAGEM LDA</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1770,408 +1845,595 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FORMEX MOZAMBIQUE, LIMITADA</t>
+          <t>FERRAGEM TREVO FAMILIA</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>BLUE OCEAN, LIMITADA ( SUCURSAL) NAMPULA</t>
+          <t>FERRAGEM ALEX UCUCHO87</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 09 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ALAR,LDA</t>
+          <t>FERRAGEM FORTALEZA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ELECTRO FERRAGEIRA,LDA</t>
+          <t>SSR TRADING</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 16 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>NEW HOTEL, LDA</t>
+          <t>GODS PLAN</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 04 Mins</t>
+          <t>01 Hrs 03 Mins</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ALI SHOP ,SOCIEDADE UNIPESSOAL, LIMITADA ( SUCURSAL)</t>
+          <t>FERRAGEM LANGA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 19 Mins</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM JAIME ELIAS MABOXE</t>
+          <t>NOSSA FERRAGEM SOCIEDADE UNIPESSOAL LIMITADA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 11 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM MUIZ, EI</t>
+          <t>LBN COMERCIAL,LDA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>00 Hrs 27 Mins</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM CAMINHO DA OBRA, LDA</t>
+          <t>FERRAGEM ALAR,LDA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 12 Mins</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM AFRIPAK TRADING EI</t>
+          <t>FERRAGEM ERA , NAMPULA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 19 Mins</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM AUTO GEMO</t>
+          <t>BLUE OCEAN, LIMITADA ( SUCURSAL) NAMPULA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 02 Mins</t>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FERROX</t>
+          <t>FERRAGEM JAIME ELIAS MABOXE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 04 Mins</t>
+          <t>00 Hrs 33 Mins</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MUTARARA FERRAGEM</t>
+          <t>J. ELECTRO FERRAGEM SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 16 Mins</t>
+          <t>00 Hrs 11 Mins</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ASIA</t>
+          <t>BLESSED MIKO IMPORT AND EXPORT, EI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 11 Mins</t>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>UZAMBIANE FERRAGENS LDA</t>
+          <t>FERRAGEM SORTHIA, LDA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 20 Mins</t>
+          <t>00 Hrs 09 Mins</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CENTRAL GRAFICA, LDA</t>
+          <t>MFD FERRAGEM</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 20 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PATEL FERRAGEM, EI</t>
+          <t>FERRAGEM KULSOOM LDA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 02 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CUAMBA&amp;#039;S FERRAGEM, EI</t>
+          <t>FERRAGEM DA PRACA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 04 Mins</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ELECTRO FERRAGEM MATOLA</t>
+          <t>FERRAGEM MUIZ, EI</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 34 Mins</t>
+          <t>00 Hrs 14 Mins</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ARMANDO FERRAGEM, E.I</t>
+          <t>HOTEL RANIS</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 32 Mins</t>
+          <t>00 Hrs 18 Mins</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>UAMUSSE FERRANGEM</t>
+          <t>CONSTRUA MEHEK</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 04 Mins</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MACUACUA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MAGUENGUE AUTO-PAINTS</t>
+          <t>KULUN MATERIAL DE CONSTRUCAO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 43 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>SAIDATA ZALIA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>EMCO LDA</t>
+          <t>FERCON</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 09 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>KUMAR CHAMPAKLAL</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>KEYU COMERCIAL</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 07 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>KUMAR CHAMPAKLAL</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>FORMEX MOCAMBIQUE BAIXA</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 07 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>TINTAS BERGER MAPUTO OFFICE</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 18 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SIMBA HOME CARE, SU,LDA</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 21 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEIRA SÃO JOSÉ</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 23 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>NELITO SIMANGO INVESTIMENTO, SU,LDA</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 28 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>AC CHARLES - SOCIEDADE UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>A.B.STEEL,LIMITADA</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>KHAN FERRAGEM ELECTRICO, LDA</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
           <t>SAIDATA ZALIA</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>RAGE COMERCIAL</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 16 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>AMAL COMERCIAL</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 09 Mins</t>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 12 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE FERRAGEM</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 29 Mins</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -42,7 +42,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004F81BD"/>
         <bgColor rgb="004F81BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -82,10 +88,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -453,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -481,11 +493,11 @@
     <row r="2" ht="23.6" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>ADERITO MACHOVO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -496,11 +508,11 @@
     <row r="3" ht="23.6" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -511,56 +523,56 @@
     <row r="4" ht="23.6" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Used App</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="23.6" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>HENRIQUE BERTUR</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Did Not Use App</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="23.6" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>IMRAN AHMED</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Used App</t>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Suspended</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23.6" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Used App</t>
+          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
     <row r="7" ht="23.6" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -571,11 +583,11 @@
     <row r="8" ht="23.6" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -586,28 +598,43 @@
     <row r="9" ht="23.6" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Used App</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="23.6" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
           <t>RICARDO MACUACUA</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Did Not Use App</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="23.6" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Suspended</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="23.6" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>SAIDATA ZALIA</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Used App</t>
         </is>
@@ -624,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -650,7 +677,7 @@
     <col width="4" customWidth="1" min="21" max="21"/>
     <col width="4" customWidth="1" min="22" max="22"/>
     <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="35" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -776,776 +803,850 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ADERITO MACHOVO</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr"/>
+      <c r="C2" s="5" t="inlineStr"/>
+      <c r="D2" s="5" t="inlineStr"/>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr"/>
+      <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr"/>
+      <c r="U2" s="5" t="inlineStr"/>
+      <c r="V2" s="5" t="inlineStr"/>
+      <c r="W2" s="5" t="inlineStr"/>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>1/1 - Perfect attendance</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ANDRE MARQUEZA</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr">
-        <is>
-          <t>12/13</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr"/>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>FRANCISCO TOMAS</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="inlineStr"/>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>12/13</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr"/>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>HENRIQUE BERTUR</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>8/13</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>SUS</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="5" t="inlineStr"/>
+      <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="5" t="inlineStr">
+        <is>
+          <t>8/13 | Suspended from 2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>IMRAN AHMED</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>6/13</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>ITO BENEDITO</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>13/13 - Perfect attendance</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr"/>
+      <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="5" t="inlineStr"/>
+      <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="5" t="inlineStr">
+        <is>
+          <t>14/14 - Perfect attendance</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr">
-        <is>
-          <t>12/13</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr"/>
+      <c r="S8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr"/>
+      <c r="U8" s="5" t="inlineStr"/>
+      <c r="V8" s="5" t="inlineStr"/>
+      <c r="W8" s="5" t="inlineStr"/>
+      <c r="X8" s="5" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr"/>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="inlineStr"/>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>13/13 - Perfect attendance</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr"/>
+      <c r="U9" s="5" t="inlineStr"/>
+      <c r="V9" s="5" t="inlineStr"/>
+      <c r="W9" s="5" t="inlineStr"/>
+      <c r="X9" s="5" t="inlineStr">
+        <is>
+          <t>14/14 - Perfect attendance</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>RICARDO MACUACUA</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>SUS</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>SUS</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr"/>
+      <c r="U10" s="5" t="inlineStr"/>
+      <c r="V10" s="5" t="inlineStr"/>
+      <c r="W10" s="5" t="inlineStr"/>
+      <c r="X10" s="5" t="inlineStr">
+        <is>
+          <t>10/12 | Suspended from 2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t>10/13</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>SAIDATA ZALIA</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr"/>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>9/13</t>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr"/>
+      <c r="U11" s="5" t="inlineStr"/>
+      <c r="V11" s="5" t="inlineStr"/>
+      <c r="W11" s="5" t="inlineStr"/>
+      <c r="X11" s="5" t="inlineStr">
+        <is>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1582,106 +1683,118 @@
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>ADERITO MACHOVO</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Perfect attendance</t>
+          <t>New starter from 2026-03-19</t>
         </is>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>No attendance on date: 16</t>
+          <t>Perfect attendance</t>
         </is>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>FRANCISCO TOMAS</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>No attendance on date: 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="39.2" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>HENRIQUE BERTUR</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>No attendance on dates: 2, 4, 10, 11, 18 (5 days)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>IMRAN AHMED</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>No attendance on dates: 4, 5, 6, 9, 11 (5 days)</t>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>No attendance on dates: 2, 4, 10, 11, 18 (5 days) | Suspended from 2026-03-19</t>
         </is>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Perfect attendance</t>
+          <t>No attendance on dates: 4, 5, 6, 9, 11, 19 (6 days)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>No attendance on date: 2</t>
+          <t>Perfect attendance</t>
         </is>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Perfect attendance</t>
+          <t>No attendance on date: 2</t>
         </is>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Perfect attendance</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="39.2" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
           <t>RICARDO MACUACUA</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>No attendance on dates: 2, 3, 18 (3 days)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>No attendance on dates: 2, 3, 18 (3 days) | Suspended from 2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>SAIDATA ZALIA</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>No attendance on dates: 2, 3, 4, 13 (4 days)</t>
         </is>
@@ -1698,7 +1811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1726,352 +1839,352 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>ADERITO MACHOVO</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MALABAR MATERIAL DE CONSTRUCAO SOCIEDADE UNIPESSOAL, LD</t>
+          <t>MAGUENGUE AUTO-PAINTS</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 28 Mins</t>
+          <t>00 Hrs 16 Mins</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>ADERITO MACHOVO</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM SABHA, LDA</t>
+          <t>UAMUSSE FERRANGEM</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 35 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>ADERITO MACHOVO</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM MAHNOOR</t>
+          <t>FERRAGEM GLORIOSO</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 46 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>ADERITO MACHOVO</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>FUXIN MATERIAL DE CONSTRUCAO TRADING, LDA</t>
+          <t>ROYAL FERRAGEM SUCURSAL LDA</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 30 Mins</t>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>ADERITO MACHOVO</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ACACIA</t>
+          <t>FERRAGEM UNIVERSAL</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 02 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>ADERITO MACHOVO</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ZINTAVA SOC UNP LDA</t>
+          <t>P.P. IMPORTACAO E EXPORTACAO</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 45 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>ADERITO MACHOVO</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>R.V ELECTRO FERRAGEM LDA</t>
+          <t>LANGA COMERCIAL SOC UNP LDA</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ADERITO MACHOVO</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM TREVO FAMILIA</t>
+          <t>FERRAGEM TENHA FÉ</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ADERITO MACHOVO</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ALEX UCUCHO87</t>
+          <t>TINTAS E FERRAGENS, LDA</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM FORTALEZA</t>
+          <t>MASSANGO PAINTS, EI</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 10 Mins</t>
+          <t>00 Hrs 17 Mins</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SSR TRADING</t>
+          <t>FERRAGEM DAS MAHOTAS,LDA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 21 Mins</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>GODS PLAN</t>
+          <t>QUATRO ESTRELAS FERRAGENS</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 03 Mins</t>
+          <t>00 Hrs 43 Mins</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM LANGA</t>
+          <t>CHINA MALL, LDA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 19 Mins</t>
+          <t>00 Hrs 30 Mins</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>NOSSA FERRAGEM SOCIEDADE UNIPESSOAL LIMITADA</t>
+          <t>KUSHI MAPUTO LDA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 16 Mins</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LBN COMERCIAL,LDA</t>
+          <t>FERRAGEM PONTE, LDA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 27 Mins</t>
+          <t>00 Hrs 16 Mins</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ALAR,LDA</t>
+          <t>LIMPOPO TRADING, LDA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 12 Mins</t>
+          <t>00 Hrs 29 Mins</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM ERA , NAMPULA</t>
+          <t>FERRAGEM CH CONSTRUCOES</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 19 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>BLUE OCEAN, LIMITADA ( SUCURSAL) NAMPULA</t>
+          <t>FERRAGEM SOBRINHO DE DEUS</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 10 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM JAIME ELIAS MABOXE</t>
+          <t>PATEL HARDWARE MOCAMBIQUE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 33 Mins</t>
+          <t>00 Hrs 09 Mins</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>J. ELECTRO FERRAGEM SOC. UNIP. LDA</t>
+          <t>FERRAGEM RHUMBANE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 11 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>BLESSED MIKO IMPORT AND EXPORT, EI</t>
+          <t>JIANGHAI CONSTRUCOES E SOCIEDADE UNIPESSOAL, LDA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2083,357 +2196,459 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM SORTHIA, LDA</t>
+          <t>KULUN MATERIAL DE CONSTRUCAO, LIMITADA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 09 Mins</t>
+          <t>00 Hrs 25 Mins</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MFD FERRAGEM</t>
+          <t>FERCON</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 24 Mins</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM KULSOOM LDA</t>
+          <t>FERRAGEM MAHAMCOMERCIAL</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>00 Hrs 02 Mins</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM DA PRACA</t>
+          <t>ROSE GONSALVES</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 04 Mins</t>
+          <t>00 Hrs 25 Mins</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM MUIZ, EI</t>
+          <t>HAO FA COMERCIAL</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>01 Hrs 18 Mins</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>HOTEL RANIS</t>
+          <t>FERNEX FERRAGEM</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 18 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>HENRIQUE BERTUR</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CONSTRUA MEHEK</t>
+          <t>IMRAN FERRAGEM</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 04 Mins</t>
+          <t>00 Hrs 16 Mins</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>KULUN MATERIAL DE CONSTRUCAO</t>
+          <t>FERRAGEM AFRIPAK TRADING EI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 09 Mins</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>FERCON</t>
+          <t>ARIMEK COMERCIAL EI</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 18 Mins</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>KEYU COMERCIAL</t>
+          <t>MODALAND INTERPRICES</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 09 Mins</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>FORMEX MOCAMBIQUE BAIXA</t>
+          <t>GOD WIN FERRAGEM</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>TINTAS BERGER MAPUTO OFFICE</t>
+          <t>FERRAGEM AUTO GEMO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 18 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SIMBA HOME CARE, SU,LDA</t>
+          <t>MOBILITY INVESTIMENTO, EI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 21 Mins</t>
+          <t>00 Hrs 14 Mins</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEIRA SÃO JOSÉ</t>
+          <t>FERRAGEM PURE ON HEART</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 23 Mins</t>
+          <t>00 Hrs 03 Mins</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>NELITO SIMANGO INVESTIMENTO, SU,LDA</t>
+          <t>LUA E MAR</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 28 Mins</t>
+          <t>00 Hrs 47 Mins</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>AC CHARLES - SOCIEDADE UNIPESSOAL, LDA</t>
+          <t>ROSSY GONSALVES</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 29 Mins</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>A.B.STEEL,LIMITADA</t>
+          <t>HAO FA COMERCIALL</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>KHAN FERRAGEM ELECTRICO, LDA</t>
+          <t>AGOSTINHO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 00 Mins</t>
+          <t>00 Hrs 11 Mins</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>SAIDATA ZALIA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>RAGE COMERCIAL</t>
+          <t>FERNEX</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 16 Mins</t>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SAIDATA ZALIA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>AMAL COMERCIAL</t>
+          <t>IMRANYAKUB</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 12 Mins</t>
+          <t>00 Hrs 16 Mins</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>AF FERRAGEM E.I</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 08 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>AUTO FERRAGEM PEQUENINO</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 39 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM MUHENGO, LDA</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>01 Hrs 01 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM SERGIO E.I</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 45 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>FANTASTIC INDUSTRIES, LDA</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
           <t>SAIDATA ZALIA</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>CENTRO DE FERRAGEM</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 29 Mins</t>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>EMCO LDA</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 12 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>KHALID SU LDA</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attendance Grid - March" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Attendance - March" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day Visits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Day Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Attendance Grid - March" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Monthly Attendance - March" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Day Visits" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -82,22 +79,22 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -497,7 +494,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -512,7 +509,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -527,7 +524,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -572,7 +569,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -587,7 +584,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -602,7 +599,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -632,11 +629,11 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Used App</t>
+          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
@@ -826,7 +823,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q2" s="5" t="inlineStr"/>
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr"/>
@@ -836,7 +837,7 @@
       <c r="W2" s="5" t="inlineStr"/>
       <c r="X2" s="5" t="inlineStr">
         <is>
-          <t>1/1 - Perfect attendance</t>
+          <t>2/2 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -916,7 +917,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q3" s="5" t="inlineStr"/>
       <c r="R3" s="5" t="inlineStr"/>
       <c r="S3" s="5" t="inlineStr"/>
@@ -926,7 +931,7 @@
       <c r="W3" s="5" t="inlineStr"/>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1011,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr"/>
@@ -1016,7 +1025,7 @@
       <c r="W4" s="5" t="inlineStr"/>
       <c r="X4" s="5" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1105,11 @@
           <t>SUS</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr"/>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>SUS</t>
+        </is>
+      </c>
       <c r="Q5" s="5" t="inlineStr"/>
       <c r="R5" s="5" t="inlineStr"/>
       <c r="S5" s="5" t="inlineStr"/>
@@ -1186,7 +1199,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
@@ -1196,7 +1213,7 @@
       <c r="W6" s="5" t="inlineStr"/>
       <c r="X6" s="5" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1293,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q7" s="5" t="inlineStr"/>
       <c r="R7" s="5" t="inlineStr"/>
       <c r="S7" s="5" t="inlineStr"/>
@@ -1286,7 +1307,7 @@
       <c r="W7" s="5" t="inlineStr"/>
       <c r="X7" s="5" t="inlineStr">
         <is>
-          <t>14/14 - Perfect attendance</t>
+          <t>15/15 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1387,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q8" s="5" t="inlineStr"/>
       <c r="R8" s="5" t="inlineStr"/>
       <c r="S8" s="5" t="inlineStr"/>
@@ -1376,7 +1401,7 @@
       <c r="W8" s="5" t="inlineStr"/>
       <c r="X8" s="5" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1481,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q9" s="5" t="inlineStr"/>
       <c r="R9" s="5" t="inlineStr"/>
       <c r="S9" s="5" t="inlineStr"/>
@@ -1466,7 +1495,7 @@
       <c r="W9" s="5" t="inlineStr"/>
       <c r="X9" s="5" t="inlineStr">
         <is>
-          <t>14/14 - Perfect attendance</t>
+          <t>15/15 - Perfect attendance</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1575,11 @@
           <t>SUS</t>
         </is>
       </c>
-      <c r="P10" s="5" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>SUS</t>
+        </is>
+      </c>
       <c r="Q10" s="5" t="inlineStr"/>
       <c r="R10" s="5" t="inlineStr"/>
       <c r="S10" s="5" t="inlineStr"/>
@@ -1636,7 +1669,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="Q11" s="5" t="inlineStr"/>
       <c r="R11" s="5" t="inlineStr"/>
       <c r="S11" s="5" t="inlineStr"/>
@@ -1646,7 +1683,7 @@
       <c r="W11" s="5" t="inlineStr"/>
       <c r="X11" s="5" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1765,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="25" customHeight="1">
+    <row r="6" ht="39.2" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>IMRAN AHMED</t>
@@ -1736,7 +1773,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 4, 5, 6, 9, 11, 19 (6 days)</t>
+          <t>No attendance on dates: 4, 5, 6, 9, 11, 19, 20 (7 days)</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1833,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 2, 3, 4, 13 (4 days)</t>
+          <t>No attendance on dates: 2, 3, 4, 13, 20 (5 days)</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1849,7 +1886,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 16 Mins</t>
+          <t>01 Hrs 02 Mins</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1898,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>UAMUSSE FERRANGEM</t>
+          <t>FERRAGEM TAWAKULL</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 24 Mins</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1915,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM GLORIOSO</t>
+          <t>O.S HOLDING, LDA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 18 Mins</t>
         </is>
       </c>
     </row>
@@ -1895,12 +1932,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ROYAL FERRAGEM SUCURSAL LDA</t>
+          <t>FERRAGENS JALASAI</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 10 Mins</t>
+          <t>00 Hrs 19 Mins</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1949,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM UNIVERSAL</t>
+          <t>TINTAS E FERRAGENS, LDA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>
@@ -1929,63 +1966,63 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>P.P. IMPORTACAO E EXPORTACAO</t>
+          <t>FERRAGEM SAMANTHA</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 16 Mins</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ADERITO MACHOVO</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>LANGA COMERCIAL SOC UNP LDA</t>
+          <t>FERRAGEM EBENEZER</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 18 Mins</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ADERITO MACHOVO</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM TENHA FÉ</t>
+          <t>FERRAGEM 1º DE MAIO</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 28 Mins</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ADERITO MACHOVO</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>TINTAS E FERRAGENS, LDA</t>
+          <t>FRANCIS FERRAGEM SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 30 Mins</t>
         </is>
       </c>
     </row>
@@ -1997,12 +2034,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MASSANGO PAINTS, EI</t>
+          <t>FERRAGEM BOM TEMPO</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 17 Mins</t>
+          <t>00 Hrs 34 Mins</t>
         </is>
       </c>
     </row>
@@ -2014,641 +2051,318 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM DAS MAHOTAS,LDA</t>
+          <t>KADI COMERCIAL</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 21 Mins</t>
+          <t>00 Hrs 32 Mins</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>QUATRO ESTRELAS FERRAGENS</t>
+          <t>FERRAGEM AFRIPAK TRADING EI</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 43 Mins</t>
+          <t>00 Hrs 14 Mins</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CHINA MALL, LDA</t>
+          <t>ARIMEK COMERCIAL EI</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 30 Mins</t>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>KUSHI MAPUTO LDA</t>
+          <t>FERRAGEM AUTO GEMO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 16 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM PONTE, LDA</t>
+          <t>JKAS COMERCIAL, LDA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 16 Mins</t>
+          <t>00 Hrs 02 Mins</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LIMPOPO TRADING, LDA</t>
+          <t>ROMSHA TRADING, LDA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 29 Mins</t>
+          <t>00 Hrs 03 Mins</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM CH CONSTRUCOES</t>
+          <t>INDO AFRICA COMERCIAL - ARMAZENS VITORIA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM SOBRINHO DE DEUS</t>
+          <t>KAAFERR FERRAGEM</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 08 Mins</t>
+          <t>00 Hrs 03 Mins</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PATEL HARDWARE MOCAMBIQUE</t>
+          <t>CONSTRUCTION SITE - AVENIDA MILAGRE MAPOTE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 09 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM RHUMBANE</t>
+          <t>FERRAGEM BAIANA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 15 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO TOMAS</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>JIANGHAI CONSTRUCOES E SOCIEDADE UNIPESSOAL, LDA</t>
+          <t>G.F COMERCIAL</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 10 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE BERTUR</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>KULUN MATERIAL DE CONSTRUCAO, LIMITADA</t>
+          <t>FERRAGEM L.H.A</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 25 Mins</t>
+          <t>00 Hrs 13 Mins</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE BERTUR</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FERCON</t>
+          <t>LUA E MAR</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 24 Mins</t>
+          <t>00 Hrs 07 Mins</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE BERTUR</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM MAHAMCOMERCIAL</t>
+          <t>TINTAS BERGER MAPUTO OFFICE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 02 Mins</t>
+          <t>00 Hrs 40 Mins</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE BERTUR</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ROSE GONSALVES</t>
+          <t>BEST CHAPA SOCIEDADE-UNIPESSOAL LDA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 25 Mins</t>
+          <t>00 Hrs 40 Mins</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE BERTUR</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>HAO FA COMERCIAL</t>
+          <t>FERRAGEM MACICAME, SOCIEDADE UNIPESSOAL, LDA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 18 Mins</t>
+          <t>00 Hrs 25 Mins</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE BERTUR</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>FERNEX FERRAGEM</t>
+          <t>IFRESH, LDA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 05 Mins</t>
+          <t>00 Hrs 22 Mins</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE BERTUR</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>IMRAN FERRAGEM</t>
+          <t>FERRAGEM NATAL</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 16 Mins</t>
+          <t>00 Hrs 12 Mins</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM AFRIPAK TRADING EI</t>
+          <t>FERRAGEM ALMADINA SOC.UNIP,LDA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 09 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>ITO BENEDITO</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>ARIMEK COMERCIAL EI</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 18 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>ITO BENEDITO</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>MODALAND INTERPRICES</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 09 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>ITO BENEDITO</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>GOD WIN FERRAGEM</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 06 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>ITO BENEDITO</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM AUTO GEMO</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 05 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>ITO BENEDITO</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>MOBILITY INVESTIMENTO, EI</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 14 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>ITO BENEDITO</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM PURE ON HEART</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 03 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>KUMAR CHAMPAKLAL</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>LUA E MAR</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 47 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>KUMAR CHAMPAKLAL</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>ROSSY GONSALVES</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 29 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>KUMAR CHAMPAKLAL</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>HAO FA COMERCIALL</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 10 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>KUMAR CHAMPAKLAL</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>AGOSTINHO</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 11 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>KUMAR CHAMPAKLAL</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>FERNEX</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 10 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>KUMAR CHAMPAKLAL</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>IMRANYAKUB</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 16 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>AF FERRAGEM E.I</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 08 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>AUTO FERRAGEM PEQUENINO</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 39 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM MUHENGO, LDA</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>01 Hrs 01 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM SERGIO E.I</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 45 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>FANTASTIC INDUSTRIES, LDA</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 00 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>SAIDATA ZALIA</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>EMCO LDA</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 12 Mins</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>SAIDATA ZALIA</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>KHALID SU LDA</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 10 Mins</t>
+          <t>00 Hrs 27 Mins</t>
         </is>
       </c>
     </row>

--- a/Daily_CSFA_Report.xlsx
+++ b/Daily_CSFA_Report.xlsx
@@ -39,7 +39,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="004F81BD"/>
         <bgColor rgb="004F81BD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,16 +79,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -462,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -494,7 +482,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -509,7 +497,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -524,7 +512,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -533,43 +521,43 @@
       </c>
     </row>
     <row r="5" ht="23.6" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>HENRIQUE BERTUR</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Suspended</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>IMRAN AHMED</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Used App</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23.6" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Did Not Use App</t>
+          <t>Used App</t>
         </is>
       </c>
     </row>
     <row r="7" ht="23.6" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -580,11 +568,11 @@
     <row r="8" ht="23.6" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -595,45 +583,15 @@
     <row r="9" ht="23.6" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>SAIDATA ZALIA</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Used App</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="23.6" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Suspended</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="23.6" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>SAIDATA ZALIA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Did Not Use App</t>
         </is>
       </c>
     </row>
@@ -648,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X11"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -800,890 +758,734 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>ADERITO MACHOVO</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr"/>
-      <c r="C2" s="5" t="inlineStr"/>
-      <c r="D2" s="5" t="inlineStr"/>
-      <c r="E2" s="5" t="inlineStr"/>
-      <c r="F2" s="5" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr"/>
-      <c r="M2" s="5" t="inlineStr"/>
-      <c r="N2" s="5" t="inlineStr"/>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P2" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="5" t="inlineStr"/>
-      <c r="R2" s="5" t="inlineStr"/>
-      <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr"/>
-      <c r="W2" s="5" t="inlineStr"/>
-      <c r="X2" s="5" t="inlineStr">
-        <is>
-          <t>2/2 - Perfect attendance</t>
+      <c r="B2" s="4" t="inlineStr"/>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr"/>
+      <c r="L2" s="4" t="inlineStr"/>
+      <c r="M2" s="4" t="inlineStr"/>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="4" t="inlineStr"/>
+      <c r="U2" s="4" t="inlineStr"/>
+      <c r="V2" s="4" t="inlineStr"/>
+      <c r="W2" s="4" t="inlineStr"/>
+      <c r="X2" s="4" t="inlineStr">
+        <is>
+          <t>3/3 - Perfect attendance</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ANDRE MARQUEZA</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr"/>
-      <c r="S3" s="5" t="inlineStr"/>
-      <c r="T3" s="5" t="inlineStr"/>
-      <c r="U3" s="5" t="inlineStr"/>
-      <c r="V3" s="5" t="inlineStr"/>
-      <c r="W3" s="5" t="inlineStr"/>
-      <c r="X3" s="5" t="inlineStr">
-        <is>
-          <t>14/15</t>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr"/>
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="inlineStr"/>
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>15/16</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>FRANCISCO TOMAS</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr"/>
-      <c r="V4" s="5" t="inlineStr"/>
-      <c r="W4" s="5" t="inlineStr"/>
-      <c r="X4" s="5" t="inlineStr">
-        <is>
-          <t>14/15</t>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="inlineStr"/>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>15/16</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>HENRIQUE BERTUR</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>IMRAN AHMED</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>SUS</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>SUS</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="inlineStr"/>
-      <c r="R5" s="5" t="inlineStr"/>
-      <c r="S5" s="5" t="inlineStr"/>
-      <c r="T5" s="5" t="inlineStr"/>
-      <c r="U5" s="5" t="inlineStr"/>
-      <c r="V5" s="5" t="inlineStr"/>
-      <c r="W5" s="5" t="inlineStr"/>
-      <c r="X5" s="5" t="inlineStr">
-        <is>
-          <t>8/13 | Suspended from 2026-03-19</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>7/16</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>IMRAN AHMED</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>ITO BENEDITO</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="inlineStr"/>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>16/16 - Perfect attendance</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>KUMAR CHAMPAKLAL</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr"/>
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="inlineStr"/>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>15/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr"/>
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="inlineStr"/>
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>16/16 - Perfect attendance</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
-      <c r="V6" s="5" t="inlineStr"/>
-      <c r="W6" s="5" t="inlineStr"/>
-      <c r="X6" s="5" t="inlineStr">
-        <is>
-          <t>6/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>ITO BENEDITO</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="5" t="inlineStr"/>
-      <c r="S7" s="5" t="inlineStr"/>
-      <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="5" t="inlineStr"/>
-      <c r="V7" s="5" t="inlineStr"/>
-      <c r="W7" s="5" t="inlineStr"/>
-      <c r="X7" s="5" t="inlineStr">
-        <is>
-          <t>15/15 - Perfect attendance</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>KUMAR CHAMPAKLAL</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="inlineStr"/>
-      <c r="R8" s="5" t="inlineStr"/>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr"/>
-      <c r="U8" s="5" t="inlineStr"/>
-      <c r="V8" s="5" t="inlineStr"/>
-      <c r="W8" s="5" t="inlineStr"/>
-      <c r="X8" s="5" t="inlineStr">
-        <is>
-          <t>14/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>RICARDO DINIS LANGA</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="5" t="inlineStr"/>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="5" t="inlineStr"/>
-      <c r="V9" s="5" t="inlineStr"/>
-      <c r="W9" s="5" t="inlineStr"/>
-      <c r="X9" s="5" t="inlineStr">
-        <is>
-          <t>15/15 - Perfect attendance</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr">
-        <is>
-          <t>SUS</t>
-        </is>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>SUS</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>SUS</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="inlineStr"/>
-      <c r="R10" s="5" t="inlineStr"/>
-      <c r="S10" s="5" t="inlineStr"/>
-      <c r="T10" s="5" t="inlineStr"/>
-      <c r="U10" s="5" t="inlineStr"/>
-      <c r="V10" s="5" t="inlineStr"/>
-      <c r="W10" s="5" t="inlineStr"/>
-      <c r="X10" s="5" t="inlineStr">
-        <is>
-          <t>10/12 | Suspended from 2026-03-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SAIDATA ZALIA</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q11" s="5" t="inlineStr"/>
-      <c r="R11" s="5" t="inlineStr"/>
-      <c r="S11" s="5" t="inlineStr"/>
-      <c r="T11" s="5" t="inlineStr"/>
-      <c r="U11" s="5" t="inlineStr"/>
-      <c r="V11" s="5" t="inlineStr"/>
-      <c r="W11" s="5" t="inlineStr"/>
-      <c r="X11" s="5" t="inlineStr">
-        <is>
-          <t>10/15</t>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr"/>
+      <c r="U9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="inlineStr"/>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1754,84 +1556,60 @@
       </c>
     </row>
     <row r="5" ht="39.2" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>HENRIQUE BERTUR</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>No attendance on dates: 2, 4, 10, 11, 18 (5 days) | Suspended from 2026-03-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="39.2" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>IMRAN AHMED</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>No attendance on dates: 4, 5, 6, 9, 11, 19, 20 (7 days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IMRAN AHMED</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>No attendance on dates: 4, 5, 6, 9, 11, 19, 20 (7 days)</t>
+          <t>Perfect attendance</t>
         </is>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Perfect attendance</t>
+          <t>No attendance on date: 2</t>
         </is>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>No attendance on date: 2</t>
+          <t>Perfect attendance</t>
         </is>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>SAIDATA ZALIA</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Perfect attendance</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="39.2" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>RICARDO MACUACUA</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>No attendance on dates: 2, 3, 18 (3 days) | Suspended from 2026-03-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>SAIDATA ZALIA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>No attendance on dates: 2, 3, 4, 13, 20 (5 days)</t>
         </is>
@@ -1848,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1886,92 +1664,92 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>01 Hrs 02 Mins</t>
+          <t>00 Hrs 32 Mins</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ADERITO MACHOVO</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM TAWAKULL</t>
+          <t>SOLECTRIC, LDA</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 24 Mins</t>
+          <t>01 Hrs 33 Mins</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ADERITO MACHOVO</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>O.S HOLDING, LDA</t>
+          <t>FERRAGEM CHOUPAL</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 18 Mins</t>
+          <t>00 Hrs 43 Mins</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ADERITO MACHOVO</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>FERRAGENS JALASAI</t>
+          <t>NOVO MOZ TRADING</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 19 Mins</t>
+          <t>01 Hrs 01 Mins</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ADERITO MACHOVO</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TINTAS E FERRAGENS, LDA</t>
+          <t>CHINA MALL, LDA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 10 Mins</t>
+          <t>00 Hrs 19 Mins</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ADERITO MACHOVO</t>
+          <t>ANDRE MARQUEZA</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM SAMANTHA</t>
+          <t>JOHNSON FERRAGENS. SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 16 Mins</t>
+          <t>00 Hrs 32 Mins</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1761,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM EBENEZER</t>
+          <t>SUPERMERCADO DO RIO VERDE, SOC. UNIP. LDA</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2000,12 +1778,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM 1º DE MAIO</t>
+          <t>FIVE STAR COMERCIAL, EI</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 28 Mins</t>
+          <t>00 Hrs 34 Mins</t>
         </is>
       </c>
     </row>
@@ -2017,46 +1795,46 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>FRANCIS FERRAGEM SOC. UNIP. LDA</t>
+          <t>UNIAO COMERCIAL ZANDA</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 30 Mins</t>
+          <t>00 Hrs 39 Mins</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM BOM TEMPO</t>
+          <t>FERRAGEM FATIMA, LDA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 34 Mins</t>
+          <t>00 Hrs 03 Mins</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ANDRE MARQUEZA</t>
+          <t>FRANCISCO TOMAS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>KADI COMERCIAL</t>
+          <t>FARZANA SERVICES</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 32 Mins</t>
+          <t>00 Hrs 01 Mins</t>
         </is>
       </c>
     </row>
@@ -2068,12 +1846,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM AFRIPAK TRADING EI</t>
+          <t>FERRAGEM CAMINHO DA OBRA, LDA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 14 Mins</t>
+          <t>00 Hrs 02 Mins</t>
         </is>
       </c>
     </row>
@@ -2085,12 +1863,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ARIMEK COMERCIAL EI</t>
+          <t>M.S.S FERRAGEM</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 10 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
@@ -2102,75 +1880,75 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM AUTO GEMO</t>
+          <t>FERRAGEM - E- HUSSAIN SOC. UNIP LDA - AV. JOSINA MACHEL. BAIXA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 15 Mins</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>JKAS COMERCIAL, LDA</t>
+          <t>FERRAGEM ERA , NAMPULA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 02 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ROMSHA TRADING, LDA</t>
+          <t>ALI SHOP ,SOCIEDADE UNIPESSOAL, LIMITADA ( SUCURSAL)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 03 Mins</t>
+          <t>00 Hrs 10 Mins</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>INDO AFRICA COMERCIAL - ARMAZENS VITORIA</t>
+          <t>FERRAGEM ALAR,LDA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 04 Mins</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>KAAFERR FERRAGEM</t>
+          <t>ELECTRO FERRAGEIRA,LDA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2182,187 +1960,476 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CONSTRUCTION SITE - AVENIDA MILAGRE MAPOTE</t>
+          <t>NEW HOTEL, LDA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 09 Mins</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ITO BENEDITO</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM BAIANA</t>
+          <t>ALI SHOP ,SOCIEDADE UNIPESSOAL, LIMITADA ( SUCURSAL)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>00 Hrs 13 Mins</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>IMRAN AHMED</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>G.F COMERCIAL</t>
+          <t>FORMEX MOZAMBIQUE, LIMITADA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 06 Mins</t>
+          <t>00 Hrs 08 Mins</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM L.H.A</t>
+          <t>FERRAGEM SORTHIA, LDA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 13 Mins</t>
+          <t>00 Hrs 22 Mins</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>KUMAR CHAMPAKLAL</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>LUA E MAR</t>
+          <t>ELECTRO FERRAGEM EURO, LDA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 07 Mins</t>
+          <t>02 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TINTAS BERGER MAPUTO OFFICE</t>
+          <t>MODALAND INTERPRICES</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 40 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>BEST CHAPA SOCIEDADE-UNIPESSOAL LDA</t>
+          <t>FERRAGEM PURE ON HEART</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 40 Mins</t>
+          <t>00 Hrs 05 Mins</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM MACICAME, SOCIEDADE UNIPESSOAL, LDA</t>
+          <t>DHP LDA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 25 Mins</t>
+          <t>00 Hrs 06 Mins</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>ITO BENEDITO</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>IFRESH, LDA</t>
+          <t>BALDRAN FERRAGENS</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 22 Mins</t>
+          <t>00 Hrs 11 Mins</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DINIS LANGA</t>
+          <t>KUMAR CHAMPAKLAL</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>FERRAGEM NATAL</t>
+          <t>MOHAMD SHAH ZADAH</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>00 Hrs 12 Mins</t>
+          <t>00 Hrs 29 Mins</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>KUMAR CHAMPAKLAL</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>HABIBULA MESBAH</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 08 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>KUMAR CHAMPAKLAL</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>LEADER FERRAGEM 2</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 26 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>KUMAR CHAMPAKLAL</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>RACHID</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 26 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>KUMAR CHAMPAKLAL</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>METRO FERRAGEM</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 12 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>KUMAR CHAMPAKLAL</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>ROSSY GONSALVES</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 10 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>KUMAR CHAMPAKLAL</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>HOTEL RANIS</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 43 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
           <t>RICARDO DINIS LANGA</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>FERRAGEM ALMADINA SOC.UNIP,LDA</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>00 Hrs 27 Mins</t>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>TINTAS BERGER MAPUTO OFFICE</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>01 Hrs 27 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM MUHENGO, LDA</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 23 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM SERGIO E.I</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 37 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>PAK-MOZ FERRAGEM</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM ABASEEN - SOC. UNIP. LDA</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>KHAN FERRAGEM ELECTRICO, LDA</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM AIYAKENE, SOCIEDADE UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 00 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>RICARDO DINIS LANGA</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>NAWAZ TRADER, COMERCIAL. SOC. UNIP.LDA</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 14 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>FERRAGEM MAHAMUDO</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 11 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>KHALID SU LDA</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 11 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>AMAL COMERCIAL</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 14 Mins</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>SAIDATA ZALIA</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>ALIN COMERCIAL</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>00 Hrs 22 Mins</t>
         </is>
       </c>
     </row>
